--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1363,7 +1363,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128376258</v>
+        <v>128375168</v>
       </c>
       <c r="B9" t="n">
         <v>79031</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471292</v>
+        <v>471139</v>
       </c>
       <c r="R9" t="n">
-        <v>6866805</v>
+        <v>6866821</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128376197</v>
+        <v>128375190</v>
       </c>
       <c r="B10" t="n">
-        <v>78790</v>
+        <v>79031</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471280</v>
+        <v>471145</v>
       </c>
       <c r="R10" t="n">
-        <v>6866807</v>
+        <v>6866802</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128375168</v>
+        <v>128376258</v>
       </c>
       <c r="B11" t="n">
         <v>79031</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471139</v>
+        <v>471292</v>
       </c>
       <c r="R11" t="n">
-        <v>6866821</v>
+        <v>6866805</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128375190</v>
+        <v>128376197</v>
       </c>
       <c r="B12" t="n">
-        <v>79031</v>
+        <v>78790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471145</v>
+        <v>471280</v>
       </c>
       <c r="R12" t="n">
-        <v>6866802</v>
+        <v>6866807</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128376712</v>
+        <v>128374662</v>
       </c>
       <c r="B15" t="n">
-        <v>79621</v>
+        <v>79031</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471282</v>
+        <v>471145</v>
       </c>
       <c r="R15" t="n">
-        <v>6866780</v>
+        <v>6866824</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128374662</v>
+        <v>128376712</v>
       </c>
       <c r="B18" t="n">
-        <v>79031</v>
+        <v>79621</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471145</v>
+        <v>471282</v>
       </c>
       <c r="R18" t="n">
-        <v>6866824</v>
+        <v>6866780</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3987,7 +3987,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128376382</v>
+        <v>128374814</v>
       </c>
       <c r="B36" t="n">
         <v>79031</v>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471342</v>
+        <v>471137</v>
       </c>
       <c r="R36" t="n">
-        <v>6866780</v>
+        <v>6866828</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4058,6 +4058,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4084,7 +4089,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128374814</v>
+        <v>128376382</v>
       </c>
       <c r="B37" t="n">
         <v>79031</v>
@@ -4119,10 +4124,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471137</v>
+        <v>471342</v>
       </c>
       <c r="R37" t="n">
-        <v>6866828</v>
+        <v>6866780</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4155,11 +4160,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4389,10 +4389,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374500</v>
+        <v>128376649</v>
       </c>
       <c r="B40" t="n">
-        <v>79063</v>
+        <v>79031</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4400,21 +4400,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471134</v>
+        <v>471300</v>
       </c>
       <c r="R40" t="n">
-        <v>6866834</v>
+        <v>6866735</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4486,10 +4486,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128375508</v>
+        <v>128374500</v>
       </c>
       <c r="B41" t="n">
-        <v>79031</v>
+        <v>79063</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4497,21 +4497,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471209</v>
+        <v>471134</v>
       </c>
       <c r="R41" t="n">
-        <v>6866776</v>
+        <v>6866834</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4583,7 +4583,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128376649</v>
+        <v>128375508</v>
       </c>
       <c r="B42" t="n">
         <v>79031</v>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471300</v>
+        <v>471209</v>
       </c>
       <c r="R42" t="n">
-        <v>6866735</v>
+        <v>6866776</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4777,54 +4777,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128376462</v>
+        <v>128375498</v>
       </c>
       <c r="B44" t="n">
-        <v>91929</v>
+        <v>79031</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471351</v>
+        <v>471198</v>
       </c>
       <c r="R44" t="n">
-        <v>6866748</v>
+        <v>6866776</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4857,11 +4848,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4888,45 +4874,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128375498</v>
+        <v>128376462</v>
       </c>
       <c r="B45" t="n">
-        <v>79031</v>
+        <v>91929</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471198</v>
+        <v>471351</v>
       </c>
       <c r="R45" t="n">
-        <v>6866776</v>
+        <v>6866748</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4959,6 +4954,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5274,6 +5274,4615 @@
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128387779</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>470744</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6866736</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128388103</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>470763</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6866753</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128388207</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>470789</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6866739</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128387977</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>470754</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6866755</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128387828</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>470743</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6866698</v>
+      </c>
+      <c r="S53" t="n">
+        <v>20</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128387790</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>470732</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6866727</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128389894</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>471207</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6866729</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128389953</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>471200</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6866759</v>
+      </c>
+      <c r="S56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128388996</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>471118</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6866746</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128388496</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>470869</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6866723</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128389324</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79621</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>471177</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6866639</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128387936</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>470750</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6866754</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128388778</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79111</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>864</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>470995</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6866711</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128389329</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>471172</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6866632</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128389511</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>471237</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6866588</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128389262</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80136</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>471168</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6866647</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128389855</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>471241</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6866622</v>
+      </c>
+      <c r="S65" t="n">
+        <v>20</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128387286</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>470551</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6866872</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128387227</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>470551</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6866892</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128388804</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79064</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>185</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>470987</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6866706</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128389187</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>471196</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6866706</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128389069</v>
+      </c>
+      <c r="B70" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>471158</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6866734</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128389227</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79064</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>185</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>471156</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6866665</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128389641</v>
+      </c>
+      <c r="B72" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>471241</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6866656</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128388766</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79111</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>864</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>470981</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6866714</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128388646</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79064</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>185</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>470945</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6866709</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128387695</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>470733</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6866772</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128388053</v>
+      </c>
+      <c r="B76" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>470770</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6866780</v>
+      </c>
+      <c r="S76" t="n">
+        <v>20</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128387629</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>470725</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6866764</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128388815</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>470992</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6866696</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128388416</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>470816</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6866722</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128388714</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>470987</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6866714</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128389886</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>471211</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6866717</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128389403</v>
+      </c>
+      <c r="B82" t="n">
+        <v>78791</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>471187</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6866586</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128387736</v>
+      </c>
+      <c r="B83" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>470738</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6866733</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128389124</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>471167</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6866694</v>
+      </c>
+      <c r="S84" t="n">
+        <v>20</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128387659</v>
+      </c>
+      <c r="B85" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>470734</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6866771</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128387292</v>
+      </c>
+      <c r="B86" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>470551</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6866868</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128389213</v>
+      </c>
+      <c r="B87" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>471148</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6866668</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128389901</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>471209</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6866743</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128389351</v>
+      </c>
+      <c r="B89" t="n">
+        <v>78010</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>471215</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6866634</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128388228</v>
+      </c>
+      <c r="B90" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>470788</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6866725</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128388690</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>470982</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6866703</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128388173</v>
+      </c>
+      <c r="B92" t="n">
+        <v>78699</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>353</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>470786</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6866737</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128389587</v>
+      </c>
+      <c r="B93" t="n">
+        <v>80136</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>471274</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6866626</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128389918</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>471210</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6866755</v>
+      </c>
+      <c r="S94" t="n">
+        <v>20</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128389286</v>
+      </c>
+      <c r="B95" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>471168</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6866647</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128376373</v>
+        <v>128373928</v>
       </c>
       <c r="B2" t="n">
-        <v>79031</v>
+        <v>79063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471330</v>
+        <v>471086</v>
       </c>
       <c r="R2" t="n">
-        <v>6866787</v>
+        <v>6866862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128376618</v>
+        <v>128374420</v>
       </c>
       <c r="B3" t="n">
-        <v>79031</v>
+        <v>98473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471331</v>
+        <v>471132</v>
       </c>
       <c r="R3" t="n">
-        <v>6866715</v>
+        <v>6866856</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,54 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128374420</v>
+        <v>128374470</v>
       </c>
       <c r="B4" t="n">
-        <v>98473</v>
+        <v>78789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471132</v>
+        <v>471139</v>
       </c>
       <c r="R4" t="n">
-        <v>6866856</v>
+        <v>6866835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373928</v>
+        <v>128375151</v>
       </c>
       <c r="B5" t="n">
         <v>79063</v>
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471086</v>
+        <v>471135</v>
       </c>
       <c r="R5" t="n">
-        <v>6866862</v>
+        <v>6866819</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128374470</v>
+        <v>128375924</v>
       </c>
       <c r="B6" t="n">
-        <v>78789</v>
+        <v>78790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471139</v>
+        <v>471255</v>
       </c>
       <c r="R6" t="n">
-        <v>6866835</v>
+        <v>6866786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128375924</v>
+        <v>128376373</v>
       </c>
       <c r="B7" t="n">
-        <v>78790</v>
+        <v>79031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471255</v>
+        <v>471330</v>
       </c>
       <c r="R7" t="n">
-        <v>6866786</v>
+        <v>6866787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128375151</v>
+        <v>128376618</v>
       </c>
       <c r="B8" t="n">
-        <v>79063</v>
+        <v>79031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471135</v>
+        <v>471331</v>
       </c>
       <c r="R8" t="n">
-        <v>6866819</v>
+        <v>6866715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128376649</v>
+        <v>128374500</v>
       </c>
       <c r="B40" t="n">
-        <v>79031</v>
+        <v>79063</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4400,21 +4400,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471300</v>
+        <v>471134</v>
       </c>
       <c r="R40" t="n">
-        <v>6866735</v>
+        <v>6866834</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4486,10 +4486,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128374500</v>
+        <v>128375508</v>
       </c>
       <c r="B41" t="n">
-        <v>79063</v>
+        <v>79031</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4497,21 +4497,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471134</v>
+        <v>471209</v>
       </c>
       <c r="R41" t="n">
-        <v>6866834</v>
+        <v>6866776</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4583,7 +4583,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128375508</v>
+        <v>128376649</v>
       </c>
       <c r="B42" t="n">
         <v>79031</v>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471209</v>
+        <v>471300</v>
       </c>
       <c r="R42" t="n">
-        <v>6866776</v>
+        <v>6866735</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128373928</v>
+        <v>128376373</v>
       </c>
       <c r="B2" t="n">
-        <v>79063</v>
+        <v>79031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471086</v>
+        <v>471330</v>
       </c>
       <c r="R2" t="n">
-        <v>6866862</v>
+        <v>6866787</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128374420</v>
+        <v>128376618</v>
       </c>
       <c r="B3" t="n">
-        <v>98473</v>
+        <v>79031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471132</v>
+        <v>471331</v>
       </c>
       <c r="R3" t="n">
-        <v>6866856</v>
+        <v>6866715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,45 +869,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128374470</v>
+        <v>128374420</v>
       </c>
       <c r="B4" t="n">
-        <v>78789</v>
+        <v>98473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471139</v>
+        <v>471132</v>
       </c>
       <c r="R4" t="n">
-        <v>6866835</v>
+        <v>6866856</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128375151</v>
+        <v>128373928</v>
       </c>
       <c r="B5" t="n">
         <v>79063</v>
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471135</v>
+        <v>471086</v>
       </c>
       <c r="R5" t="n">
-        <v>6866819</v>
+        <v>6866862</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128375924</v>
+        <v>128374470</v>
       </c>
       <c r="B6" t="n">
-        <v>78790</v>
+        <v>78789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471255</v>
+        <v>471139</v>
       </c>
       <c r="R6" t="n">
-        <v>6866786</v>
+        <v>6866835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128376373</v>
+        <v>128375924</v>
       </c>
       <c r="B7" t="n">
-        <v>79031</v>
+        <v>78790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471330</v>
+        <v>471255</v>
       </c>
       <c r="R7" t="n">
-        <v>6866787</v>
+        <v>6866786</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128376618</v>
+        <v>128375151</v>
       </c>
       <c r="B8" t="n">
-        <v>79031</v>
+        <v>79063</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471331</v>
+        <v>471135</v>
       </c>
       <c r="R8" t="n">
-        <v>6866715</v>
+        <v>6866819</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3987,7 +3987,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128374814</v>
+        <v>128376382</v>
       </c>
       <c r="B36" t="n">
         <v>79031</v>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471137</v>
+        <v>471342</v>
       </c>
       <c r="R36" t="n">
-        <v>6866828</v>
+        <v>6866780</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4058,11 +4058,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4089,7 +4084,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128376382</v>
+        <v>128374814</v>
       </c>
       <c r="B37" t="n">
         <v>79031</v>
@@ -4124,10 +4119,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471342</v>
+        <v>471137</v>
       </c>
       <c r="R37" t="n">
-        <v>6866780</v>
+        <v>6866828</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4160,6 +4155,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5082,7 +5082,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128375399</v>
+        <v>128376295</v>
       </c>
       <c r="B47" t="n">
         <v>79031</v>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471183</v>
+        <v>471321</v>
       </c>
       <c r="R47" t="n">
-        <v>6866790</v>
+        <v>6866820</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5179,7 +5179,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128376295</v>
+        <v>128375399</v>
       </c>
       <c r="B48" t="n">
         <v>79031</v>
@@ -5214,10 +5214,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>471321</v>
+        <v>471183</v>
       </c>
       <c r="R48" t="n">
-        <v>6866820</v>
+        <v>6866790</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128387828</v>
+        <v>128389894</v>
       </c>
       <c r="B53" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5684,21 +5684,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>470743</v>
+        <v>471207</v>
       </c>
       <c r="R53" t="n">
-        <v>6866698</v>
+        <v>6866729</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5770,32 +5770,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128387790</v>
+        <v>128389953</v>
       </c>
       <c r="B54" t="n">
-        <v>98476</v>
+        <v>79032</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5805,13 +5805,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>470732</v>
+        <v>471200</v>
       </c>
       <c r="R54" t="n">
-        <v>6866727</v>
+        <v>6866759</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5867,10 +5867,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128389894</v>
+        <v>128387828</v>
       </c>
       <c r="B55" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5878,21 +5878,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5902,13 +5902,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>471207</v>
+        <v>470743</v>
       </c>
       <c r="R55" t="n">
-        <v>6866729</v>
+        <v>6866698</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5964,32 +5964,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128389953</v>
+        <v>128387790</v>
       </c>
       <c r="B56" t="n">
-        <v>79032</v>
+        <v>98476</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5999,13 +5999,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>471200</v>
+        <v>470732</v>
       </c>
       <c r="R56" t="n">
-        <v>6866759</v>
+        <v>6866727</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128388996</v>
+        <v>128388496</v>
       </c>
       <c r="B57" t="n">
         <v>79032</v>
@@ -6096,10 +6096,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>471118</v>
+        <v>470869</v>
       </c>
       <c r="R57" t="n">
-        <v>6866746</v>
+        <v>6866723</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6158,7 +6158,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128388496</v>
+        <v>128388996</v>
       </c>
       <c r="B58" t="n">
         <v>79032</v>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>470869</v>
+        <v>471118</v>
       </c>
       <c r="R58" t="n">
-        <v>6866723</v>
+        <v>6866746</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128388778</v>
+        <v>128387286</v>
       </c>
       <c r="B61" t="n">
-        <v>79111</v>
+        <v>80135</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,10 +6493,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>470995</v>
+        <v>470551</v>
       </c>
       <c r="R61" t="n">
-        <v>6866711</v>
+        <v>6866872</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128389329</v>
+        <v>128387227</v>
       </c>
       <c r="B62" t="n">
-        <v>78790</v>
+        <v>80135</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6566,21 +6566,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471172</v>
+        <v>470551</v>
       </c>
       <c r="R62" t="n">
-        <v>6866632</v>
+        <v>6866892</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128389511</v>
+        <v>128388778</v>
       </c>
       <c r="B63" t="n">
-        <v>80135</v>
+        <v>79111</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6663,21 +6663,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471237</v>
+        <v>470995</v>
       </c>
       <c r="R63" t="n">
-        <v>6866588</v>
+        <v>6866711</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128389262</v>
+        <v>128389329</v>
       </c>
       <c r="B64" t="n">
-        <v>80136</v>
+        <v>78790</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471168</v>
+        <v>471172</v>
       </c>
       <c r="R64" t="n">
-        <v>6866647</v>
+        <v>6866632</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128389855</v>
+        <v>128389511</v>
       </c>
       <c r="B65" t="n">
-        <v>57833</v>
+        <v>80135</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,13 +6881,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471241</v>
+        <v>471237</v>
       </c>
       <c r="R65" t="n">
-        <v>6866622</v>
+        <v>6866588</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6917,11 +6917,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6948,10 +6943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128387286</v>
+        <v>128389262</v>
       </c>
       <c r="B66" t="n">
-        <v>80135</v>
+        <v>80136</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6959,21 +6954,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6983,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470551</v>
+        <v>471168</v>
       </c>
       <c r="R66" t="n">
-        <v>6866872</v>
+        <v>6866647</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7045,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128387227</v>
+        <v>128389855</v>
       </c>
       <c r="B67" t="n">
-        <v>80135</v>
+        <v>57833</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7056,21 +7051,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7080,13 +7075,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>470551</v>
+        <v>471241</v>
       </c>
       <c r="R67" t="n">
-        <v>6866892</v>
+        <v>6866622</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7116,6 +7111,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128389641</v>
+        <v>128388766</v>
       </c>
       <c r="B72" t="n">
-        <v>80135</v>
+        <v>79111</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471241</v>
+        <v>470981</v>
       </c>
       <c r="R72" t="n">
-        <v>6866656</v>
+        <v>6866714</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128388766</v>
+        <v>128388646</v>
       </c>
       <c r="B73" t="n">
-        <v>79111</v>
+        <v>79064</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7638,21 +7638,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470981</v>
+        <v>470945</v>
       </c>
       <c r="R73" t="n">
-        <v>6866714</v>
+        <v>6866709</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7724,10 +7724,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128388646</v>
+        <v>128389641</v>
       </c>
       <c r="B74" t="n">
-        <v>79064</v>
+        <v>80135</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>470945</v>
+        <v>471241</v>
       </c>
       <c r="R74" t="n">
-        <v>6866709</v>
+        <v>6866656</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8121,45 +8121,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128388815</v>
+        <v>128388416</v>
       </c>
       <c r="B78" t="n">
-        <v>79032</v>
+        <v>98476</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470992</v>
+        <v>470816</v>
       </c>
       <c r="R78" t="n">
-        <v>6866696</v>
+        <v>6866722</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8218,54 +8227,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128388416</v>
+        <v>128388815</v>
       </c>
       <c r="B79" t="n">
-        <v>98476</v>
+        <v>79032</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>470816</v>
+        <v>470992</v>
       </c>
       <c r="R79" t="n">
-        <v>6866722</v>
+        <v>6866696</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8324,10 +8324,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128388714</v>
+        <v>128389403</v>
       </c>
       <c r="B80" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8335,21 +8335,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8359,10 +8359,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>470987</v>
+        <v>471187</v>
       </c>
       <c r="R80" t="n">
-        <v>6866714</v>
+        <v>6866586</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128389886</v>
+        <v>128388714</v>
       </c>
       <c r="B81" t="n">
         <v>79032</v>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471211</v>
+        <v>470987</v>
       </c>
       <c r="R81" t="n">
-        <v>6866717</v>
+        <v>6866714</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8518,10 +8518,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128389403</v>
+        <v>128389886</v>
       </c>
       <c r="B82" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8529,21 +8529,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471187</v>
+        <v>471211</v>
       </c>
       <c r="R82" t="n">
-        <v>6866586</v>
+        <v>6866717</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9012,10 +9012,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128389213</v>
+        <v>128389901</v>
       </c>
       <c r="B87" t="n">
-        <v>80135</v>
+        <v>79032</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9023,21 +9023,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471148</v>
+        <v>471209</v>
       </c>
       <c r="R87" t="n">
-        <v>6866668</v>
+        <v>6866743</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9109,32 +9109,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128389901</v>
+        <v>128388228</v>
       </c>
       <c r="B88" t="n">
-        <v>79032</v>
+        <v>98476</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471209</v>
+        <v>470788</v>
       </c>
       <c r="R88" t="n">
-        <v>6866743</v>
+        <v>6866725</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9303,32 +9303,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128388228</v>
+        <v>128389213</v>
       </c>
       <c r="B90" t="n">
-        <v>98476</v>
+        <v>80135</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>470788</v>
+        <v>471148</v>
       </c>
       <c r="R90" t="n">
-        <v>6866725</v>
+        <v>6866668</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128376373</v>
+        <v>128373928</v>
       </c>
       <c r="B2" t="n">
-        <v>79031</v>
+        <v>79063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471330</v>
+        <v>471086</v>
       </c>
       <c r="R2" t="n">
-        <v>6866787</v>
+        <v>6866862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128376618</v>
+        <v>128374420</v>
       </c>
       <c r="B3" t="n">
-        <v>79031</v>
+        <v>98473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471331</v>
+        <v>471132</v>
       </c>
       <c r="R3" t="n">
-        <v>6866715</v>
+        <v>6866856</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,54 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128374420</v>
+        <v>128374470</v>
       </c>
       <c r="B4" t="n">
-        <v>98473</v>
+        <v>78789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471132</v>
+        <v>471139</v>
       </c>
       <c r="R4" t="n">
-        <v>6866856</v>
+        <v>6866835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373928</v>
+        <v>128375151</v>
       </c>
       <c r="B5" t="n">
         <v>79063</v>
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471086</v>
+        <v>471135</v>
       </c>
       <c r="R5" t="n">
-        <v>6866862</v>
+        <v>6866819</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128374470</v>
+        <v>128375924</v>
       </c>
       <c r="B6" t="n">
-        <v>78789</v>
+        <v>78790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471139</v>
+        <v>471255</v>
       </c>
       <c r="R6" t="n">
-        <v>6866835</v>
+        <v>6866786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128375924</v>
+        <v>128376373</v>
       </c>
       <c r="B7" t="n">
-        <v>78790</v>
+        <v>79031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471255</v>
+        <v>471330</v>
       </c>
       <c r="R7" t="n">
-        <v>6866786</v>
+        <v>6866787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128375151</v>
+        <v>128376618</v>
       </c>
       <c r="B8" t="n">
-        <v>79063</v>
+        <v>79031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471135</v>
+        <v>471331</v>
       </c>
       <c r="R8" t="n">
-        <v>6866819</v>
+        <v>6866715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,7 +1363,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128375168</v>
+        <v>128376258</v>
       </c>
       <c r="B9" t="n">
         <v>79031</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471139</v>
+        <v>471292</v>
       </c>
       <c r="R9" t="n">
-        <v>6866821</v>
+        <v>6866805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128375190</v>
+        <v>128376197</v>
       </c>
       <c r="B10" t="n">
-        <v>79031</v>
+        <v>78790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471145</v>
+        <v>471280</v>
       </c>
       <c r="R10" t="n">
-        <v>6866802</v>
+        <v>6866807</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128376258</v>
+        <v>128375168</v>
       </c>
       <c r="B11" t="n">
         <v>79031</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471292</v>
+        <v>471139</v>
       </c>
       <c r="R11" t="n">
-        <v>6866805</v>
+        <v>6866821</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128376197</v>
+        <v>128375190</v>
       </c>
       <c r="B12" t="n">
-        <v>78790</v>
+        <v>79031</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471280</v>
+        <v>471145</v>
       </c>
       <c r="R12" t="n">
-        <v>6866807</v>
+        <v>6866802</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128374662</v>
+        <v>128375275</v>
       </c>
       <c r="B15" t="n">
-        <v>79031</v>
+        <v>79063</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471145</v>
+        <v>471162</v>
       </c>
       <c r="R15" t="n">
-        <v>6866824</v>
+        <v>6866793</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128375275</v>
+        <v>128375734</v>
       </c>
       <c r="B16" t="n">
-        <v>79063</v>
+        <v>79031</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471162</v>
+        <v>471234</v>
       </c>
       <c r="R16" t="n">
-        <v>6866793</v>
+        <v>6866765</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128375734</v>
+        <v>128374662</v>
       </c>
       <c r="B17" t="n">
         <v>79031</v>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471234</v>
+        <v>471145</v>
       </c>
       <c r="R17" t="n">
-        <v>6866765</v>
+        <v>6866824</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128375214</v>
+        <v>128375358</v>
       </c>
       <c r="B21" t="n">
         <v>79031</v>
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471144</v>
+        <v>471166</v>
       </c>
       <c r="R21" t="n">
-        <v>6866814</v>
+        <v>6866785</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2624,7 +2624,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128375358</v>
+        <v>128375758</v>
       </c>
       <c r="B22" t="n">
         <v>79031</v>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471166</v>
+        <v>471232</v>
       </c>
       <c r="R22" t="n">
-        <v>6866785</v>
+        <v>6866781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,7 +2721,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128375758</v>
+        <v>128375214</v>
       </c>
       <c r="B23" t="n">
         <v>79031</v>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471232</v>
+        <v>471144</v>
       </c>
       <c r="R23" t="n">
-        <v>6866781</v>
+        <v>6866814</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128375560</v>
+        <v>128376736</v>
       </c>
       <c r="B27" t="n">
-        <v>57832</v>
+        <v>78010</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471219</v>
+        <v>471282</v>
       </c>
       <c r="R27" t="n">
-        <v>6866779</v>
+        <v>6866783</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3180,11 +3180,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3211,10 +3206,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128376736</v>
+        <v>128375560</v>
       </c>
       <c r="B28" t="n">
-        <v>78010</v>
+        <v>57832</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3217,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,13 +3241,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471282</v>
+        <v>471219</v>
       </c>
       <c r="R28" t="n">
-        <v>6866783</v>
+        <v>6866779</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3282,6 +3277,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3987,7 +3987,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128376382</v>
+        <v>128374814</v>
       </c>
       <c r="B36" t="n">
         <v>79031</v>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471342</v>
+        <v>471137</v>
       </c>
       <c r="R36" t="n">
-        <v>6866780</v>
+        <v>6866828</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4058,6 +4058,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4084,7 +4089,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128374814</v>
+        <v>128376382</v>
       </c>
       <c r="B37" t="n">
         <v>79031</v>
@@ -4119,10 +4124,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471137</v>
+        <v>471342</v>
       </c>
       <c r="R37" t="n">
-        <v>6866828</v>
+        <v>6866780</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4155,11 +4160,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4777,45 +4777,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128375498</v>
+        <v>128376462</v>
       </c>
       <c r="B44" t="n">
-        <v>79031</v>
+        <v>91929</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471198</v>
+        <v>471351</v>
       </c>
       <c r="R44" t="n">
-        <v>6866776</v>
+        <v>6866748</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4848,6 +4857,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4874,54 +4888,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128376462</v>
+        <v>128375498</v>
       </c>
       <c r="B45" t="n">
-        <v>91929</v>
+        <v>79031</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471351</v>
+        <v>471198</v>
       </c>
       <c r="R45" t="n">
-        <v>6866748</v>
+        <v>6866776</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4954,11 +4959,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128387779</v>
+        <v>128388207</v>
       </c>
       <c r="B49" t="n">
-        <v>98476</v>
+        <v>78790</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470744</v>
+        <v>470789</v>
       </c>
       <c r="R49" t="n">
-        <v>6866736</v>
+        <v>6866739</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5470,32 +5470,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128388207</v>
+        <v>128387779</v>
       </c>
       <c r="B51" t="n">
-        <v>78790</v>
+        <v>98476</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470789</v>
+        <v>470744</v>
       </c>
       <c r="R51" t="n">
-        <v>6866739</v>
+        <v>6866736</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128387286</v>
+        <v>128389329</v>
       </c>
       <c r="B61" t="n">
-        <v>80135</v>
+        <v>78790</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,10 +6493,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>470551</v>
+        <v>471172</v>
       </c>
       <c r="R61" t="n">
-        <v>6866872</v>
+        <v>6866632</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6555,7 +6555,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128387227</v>
+        <v>128389511</v>
       </c>
       <c r="B62" t="n">
         <v>80135</v>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>470551</v>
+        <v>471237</v>
       </c>
       <c r="R62" t="n">
-        <v>6866892</v>
+        <v>6866588</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128388778</v>
+        <v>128389262</v>
       </c>
       <c r="B63" t="n">
-        <v>79111</v>
+        <v>80136</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6663,21 +6663,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>470995</v>
+        <v>471168</v>
       </c>
       <c r="R63" t="n">
-        <v>6866711</v>
+        <v>6866647</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128389329</v>
+        <v>128389855</v>
       </c>
       <c r="B64" t="n">
-        <v>78790</v>
+        <v>57833</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,13 +6784,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471172</v>
+        <v>471241</v>
       </c>
       <c r="R64" t="n">
-        <v>6866632</v>
+        <v>6866622</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6820,6 +6820,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6846,7 +6851,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128389511</v>
+        <v>128387286</v>
       </c>
       <c r="B65" t="n">
         <v>80135</v>
@@ -6881,10 +6886,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471237</v>
+        <v>470551</v>
       </c>
       <c r="R65" t="n">
-        <v>6866588</v>
+        <v>6866872</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,10 +6948,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128389262</v>
+        <v>128387227</v>
       </c>
       <c r="B66" t="n">
-        <v>80136</v>
+        <v>80135</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,21 +6959,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6983,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>471168</v>
+        <v>470551</v>
       </c>
       <c r="R66" t="n">
-        <v>6866647</v>
+        <v>6866892</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7040,10 +7045,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128389855</v>
+        <v>128388778</v>
       </c>
       <c r="B67" t="n">
-        <v>57833</v>
+        <v>79111</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,21 +7056,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,13 +7080,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471241</v>
+        <v>470995</v>
       </c>
       <c r="R67" t="n">
-        <v>6866622</v>
+        <v>6866711</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7111,11 +7116,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9012,10 +9012,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128389901</v>
+        <v>128389213</v>
       </c>
       <c r="B87" t="n">
-        <v>79032</v>
+        <v>80135</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9023,21 +9023,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471209</v>
+        <v>471148</v>
       </c>
       <c r="R87" t="n">
-        <v>6866743</v>
+        <v>6866668</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9206,10 +9206,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128389351</v>
+        <v>128389901</v>
       </c>
       <c r="B89" t="n">
-        <v>78010</v>
+        <v>79032</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9217,21 +9217,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471215</v>
+        <v>471209</v>
       </c>
       <c r="R89" t="n">
-        <v>6866634</v>
+        <v>6866743</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9303,10 +9303,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128389213</v>
+        <v>128389351</v>
       </c>
       <c r="B90" t="n">
-        <v>80135</v>
+        <v>78010</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9314,21 +9314,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471148</v>
+        <v>471215</v>
       </c>
       <c r="R90" t="n">
-        <v>6866668</v>
+        <v>6866634</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128373928</v>
       </c>
       <c r="B2" t="n">
-        <v>79063</v>
+        <v>79064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128374420</v>
+        <v>128375151</v>
       </c>
       <c r="B3" t="n">
-        <v>98473</v>
+        <v>79064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471132</v>
+        <v>471135</v>
       </c>
       <c r="R3" t="n">
-        <v>6866856</v>
+        <v>6866819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128374470</v>
+        <v>128376373</v>
       </c>
       <c r="B4" t="n">
-        <v>78789</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471139</v>
+        <v>471330</v>
       </c>
       <c r="R4" t="n">
-        <v>6866835</v>
+        <v>6866787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128375151</v>
+        <v>128376618</v>
       </c>
       <c r="B5" t="n">
-        <v>79063</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471135</v>
+        <v>471331</v>
       </c>
       <c r="R5" t="n">
-        <v>6866819</v>
+        <v>6866715</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128375924</v>
+        <v>128374470</v>
       </c>
       <c r="B6" t="n">
         <v>78790</v>
@@ -1083,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471255</v>
+        <v>471139</v>
       </c>
       <c r="R6" t="n">
-        <v>6866786</v>
+        <v>6866835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,45 +1160,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128376373</v>
+        <v>128374420</v>
       </c>
       <c r="B7" t="n">
-        <v>79031</v>
+        <v>98478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471330</v>
+        <v>471132</v>
       </c>
       <c r="R7" t="n">
-        <v>6866787</v>
+        <v>6866856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128376618</v>
+        <v>128375924</v>
       </c>
       <c r="B8" t="n">
-        <v>79031</v>
+        <v>78791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471331</v>
+        <v>471255</v>
       </c>
       <c r="R8" t="n">
-        <v>6866715</v>
+        <v>6866786</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128376258</v>
+        <v>128375190</v>
       </c>
       <c r="B9" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471292</v>
+        <v>471145</v>
       </c>
       <c r="R9" t="n">
-        <v>6866805</v>
+        <v>6866802</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128376197</v>
+        <v>128376258</v>
       </c>
       <c r="B10" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471280</v>
+        <v>471292</v>
       </c>
       <c r="R10" t="n">
-        <v>6866807</v>
+        <v>6866805</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,7 +1560,7 @@
         <v>128375168</v>
       </c>
       <c r="B11" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128375190</v>
+        <v>128376197</v>
       </c>
       <c r="B12" t="n">
-        <v>79031</v>
+        <v>78791</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471145</v>
+        <v>471280</v>
       </c>
       <c r="R12" t="n">
-        <v>6866802</v>
+        <v>6866807</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128374859</v>
+        <v>128376676</v>
       </c>
       <c r="B13" t="n">
-        <v>80135</v>
+        <v>79032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471125</v>
+        <v>471287</v>
       </c>
       <c r="R13" t="n">
-        <v>6866815</v>
+        <v>6866763</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128376676</v>
+        <v>128374859</v>
       </c>
       <c r="B14" t="n">
-        <v>79031</v>
+        <v>80136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471287</v>
+        <v>471125</v>
       </c>
       <c r="R14" t="n">
-        <v>6866763</v>
+        <v>6866815</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
         <v>128375275</v>
       </c>
       <c r="B15" t="n">
-        <v>79063</v>
+        <v>79064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>128375734</v>
       </c>
       <c r="B16" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>128374662</v>
       </c>
       <c r="B17" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128375959</v>
+        <v>128375989</v>
       </c>
       <c r="B19" t="n">
-        <v>79031</v>
+        <v>78010</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471266</v>
+        <v>471276</v>
       </c>
       <c r="R19" t="n">
-        <v>6866792</v>
+        <v>6866805</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128375989</v>
+        <v>128375959</v>
       </c>
       <c r="B20" t="n">
-        <v>78009</v>
+        <v>79032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471276</v>
+        <v>471266</v>
       </c>
       <c r="R20" t="n">
-        <v>6866805</v>
+        <v>6866792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>128375358</v>
       </c>
       <c r="B21" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128375758</v>
       </c>
       <c r="B22" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128375214</v>
       </c>
       <c r="B23" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>128376206</v>
       </c>
       <c r="B24" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128374452</v>
       </c>
       <c r="B25" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128375464</v>
       </c>
       <c r="B26" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128376736</v>
+        <v>128375560</v>
       </c>
       <c r="B27" t="n">
-        <v>78010</v>
+        <v>57833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471282</v>
+        <v>471219</v>
       </c>
       <c r="R27" t="n">
-        <v>6866783</v>
+        <v>6866779</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3180,6 +3180,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3206,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128375560</v>
+        <v>128376736</v>
       </c>
       <c r="B28" t="n">
-        <v>57832</v>
+        <v>78010</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3217,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3241,13 +3246,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471219</v>
+        <v>471282</v>
       </c>
       <c r="R28" t="n">
-        <v>6866779</v>
+        <v>6866783</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3277,11 +3282,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128374116</v>
+        <v>128376636</v>
       </c>
       <c r="B29" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471107</v>
+        <v>471320</v>
       </c>
       <c r="R29" t="n">
-        <v>6866853</v>
+        <v>6866734</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128376636</v>
+        <v>128376702</v>
       </c>
       <c r="B30" t="n">
-        <v>79031</v>
+        <v>78438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471320</v>
+        <v>471287</v>
       </c>
       <c r="R30" t="n">
-        <v>6866734</v>
+        <v>6866773</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128376574</v>
+        <v>128374116</v>
       </c>
       <c r="B31" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,13 +3537,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471364</v>
+        <v>471107</v>
       </c>
       <c r="R31" t="n">
-        <v>6866709</v>
+        <v>6866853</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128376702</v>
+        <v>128376574</v>
       </c>
       <c r="B32" t="n">
-        <v>78437</v>
+        <v>78791</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471287</v>
+        <v>471364</v>
       </c>
       <c r="R32" t="n">
-        <v>6866773</v>
+        <v>6866709</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128375794</v>
+        <v>128375289</v>
       </c>
       <c r="B33" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471241</v>
+        <v>471165</v>
       </c>
       <c r="R33" t="n">
-        <v>6866786</v>
+        <v>6866794</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128375289</v>
+        <v>128375249</v>
       </c>
       <c r="B34" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471165</v>
+        <v>471158</v>
       </c>
       <c r="R34" t="n">
-        <v>6866794</v>
+        <v>6866800</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128375249</v>
+        <v>128375794</v>
       </c>
       <c r="B35" t="n">
-        <v>79031</v>
+        <v>78791</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471158</v>
+        <v>471241</v>
       </c>
       <c r="R35" t="n">
-        <v>6866800</v>
+        <v>6866786</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
         <v>128374814</v>
       </c>
       <c r="B36" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>128376382</v>
       </c>
       <c r="B37" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>128373989</v>
       </c>
       <c r="B38" t="n">
-        <v>80134</v>
+        <v>80135</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>128374436</v>
       </c>
       <c r="B39" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>128374500</v>
       </c>
       <c r="B40" t="n">
-        <v>79063</v>
+        <v>79064</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4486,10 +4486,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128375508</v>
+        <v>128376649</v>
       </c>
       <c r="B41" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471209</v>
+        <v>471300</v>
       </c>
       <c r="R41" t="n">
-        <v>6866776</v>
+        <v>6866735</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4583,10 +4583,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128376649</v>
+        <v>128375508</v>
       </c>
       <c r="B42" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471300</v>
+        <v>471209</v>
       </c>
       <c r="R42" t="n">
-        <v>6866735</v>
+        <v>6866776</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128375808</v>
+        <v>128375498</v>
       </c>
       <c r="B43" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471247</v>
+        <v>471198</v>
       </c>
       <c r="R43" t="n">
-        <v>6866787</v>
+        <v>6866776</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4777,54 +4777,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128376462</v>
+        <v>128375808</v>
       </c>
       <c r="B44" t="n">
-        <v>91929</v>
+        <v>79032</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471351</v>
+        <v>471247</v>
       </c>
       <c r="R44" t="n">
-        <v>6866748</v>
+        <v>6866787</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4857,11 +4848,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4888,45 +4874,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128375498</v>
+        <v>128376462</v>
       </c>
       <c r="B45" t="n">
-        <v>79031</v>
+        <v>91934</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471198</v>
+        <v>471351</v>
       </c>
       <c r="R45" t="n">
-        <v>6866776</v>
+        <v>6866748</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4959,6 +4954,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4988,7 +4988,7 @@
         <v>128375307</v>
       </c>
       <c r="B46" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>128376295</v>
       </c>
       <c r="B47" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>128375399</v>
       </c>
       <c r="B48" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128388103</v>
+        <v>128387779</v>
       </c>
       <c r="B50" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470763</v>
+        <v>470744</v>
       </c>
       <c r="R50" t="n">
-        <v>6866753</v>
+        <v>6866736</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,10 +5470,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128387779</v>
+        <v>128388103</v>
       </c>
       <c r="B51" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470744</v>
+        <v>470763</v>
       </c>
       <c r="R51" t="n">
-        <v>6866736</v>
+        <v>6866753</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5570,7 +5570,7 @@
         <v>128387977</v>
       </c>
       <c r="B52" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>128387790</v>
       </c>
       <c r="B56" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128388496</v>
+        <v>128388996</v>
       </c>
       <c r="B57" t="n">
         <v>79032</v>
@@ -6096,10 +6096,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>470869</v>
+        <v>471118</v>
       </c>
       <c r="R57" t="n">
-        <v>6866723</v>
+        <v>6866746</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6158,7 +6158,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128388996</v>
+        <v>128388496</v>
       </c>
       <c r="B58" t="n">
         <v>79032</v>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>471118</v>
+        <v>470869</v>
       </c>
       <c r="R58" t="n">
-        <v>6866746</v>
+        <v>6866723</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6355,7 +6355,7 @@
         <v>128387936</v>
       </c>
       <c r="B60" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128389329</v>
+        <v>128389511</v>
       </c>
       <c r="B61" t="n">
-        <v>78790</v>
+        <v>80135</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,10 +6493,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471172</v>
+        <v>471237</v>
       </c>
       <c r="R61" t="n">
-        <v>6866632</v>
+        <v>6866588</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128389511</v>
+        <v>128389329</v>
       </c>
       <c r="B62" t="n">
-        <v>80135</v>
+        <v>78790</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6566,21 +6566,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471237</v>
+        <v>471172</v>
       </c>
       <c r="R62" t="n">
-        <v>6866588</v>
+        <v>6866632</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128389262</v>
+        <v>128387227</v>
       </c>
       <c r="B63" t="n">
-        <v>80136</v>
+        <v>80135</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6663,21 +6663,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471168</v>
+        <v>470551</v>
       </c>
       <c r="R63" t="n">
-        <v>6866647</v>
+        <v>6866892</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128389855</v>
+        <v>128387286</v>
       </c>
       <c r="B64" t="n">
-        <v>57833</v>
+        <v>80135</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,13 +6784,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471241</v>
+        <v>470551</v>
       </c>
       <c r="R64" t="n">
-        <v>6866622</v>
+        <v>6866872</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6820,11 +6820,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6851,10 +6846,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128387286</v>
+        <v>128389262</v>
       </c>
       <c r="B65" t="n">
-        <v>80135</v>
+        <v>80136</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6862,21 +6857,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6886,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>470551</v>
+        <v>471168</v>
       </c>
       <c r="R65" t="n">
-        <v>6866872</v>
+        <v>6866647</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6948,10 +6943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128387227</v>
+        <v>128388778</v>
       </c>
       <c r="B66" t="n">
-        <v>80135</v>
+        <v>79111</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6959,21 +6954,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6983,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470551</v>
+        <v>470995</v>
       </c>
       <c r="R66" t="n">
-        <v>6866892</v>
+        <v>6866711</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7045,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128388778</v>
+        <v>128389855</v>
       </c>
       <c r="B67" t="n">
-        <v>79111</v>
+        <v>57833</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7056,21 +7051,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>864</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7080,13 +7075,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>470995</v>
+        <v>471241</v>
       </c>
       <c r="R67" t="n">
-        <v>6866711</v>
+        <v>6866622</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7116,6 +7111,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128389187</v>
+        <v>128389227</v>
       </c>
       <c r="B69" t="n">
-        <v>78790</v>
+        <v>79064</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,10 +7274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471196</v>
+        <v>471156</v>
       </c>
       <c r="R69" t="n">
-        <v>6866706</v>
+        <v>6866665</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128389227</v>
+        <v>128389187</v>
       </c>
       <c r="B71" t="n">
-        <v>79064</v>
+        <v>78790</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471156</v>
+        <v>471196</v>
       </c>
       <c r="R71" t="n">
-        <v>6866665</v>
+        <v>6866706</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128388766</v>
+        <v>128389641</v>
       </c>
       <c r="B72" t="n">
-        <v>79111</v>
+        <v>80135</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470981</v>
+        <v>471241</v>
       </c>
       <c r="R72" t="n">
-        <v>6866714</v>
+        <v>6866656</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128388646</v>
+        <v>128388766</v>
       </c>
       <c r="B73" t="n">
-        <v>79064</v>
+        <v>79111</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7638,21 +7638,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470945</v>
+        <v>470981</v>
       </c>
       <c r="R73" t="n">
-        <v>6866709</v>
+        <v>6866714</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7724,10 +7724,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128389641</v>
+        <v>128388646</v>
       </c>
       <c r="B74" t="n">
-        <v>80135</v>
+        <v>79064</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471241</v>
+        <v>470945</v>
       </c>
       <c r="R74" t="n">
-        <v>6866656</v>
+        <v>6866709</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7821,32 +7821,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128387695</v>
+        <v>128388053</v>
       </c>
       <c r="B75" t="n">
-        <v>98476</v>
+        <v>78791</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7856,13 +7856,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>470733</v>
+        <v>470770</v>
       </c>
       <c r="R75" t="n">
-        <v>6866772</v>
+        <v>6866780</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7918,32 +7918,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128388053</v>
+        <v>128387695</v>
       </c>
       <c r="B76" t="n">
-        <v>78791</v>
+        <v>98478</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7953,13 +7953,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>470770</v>
+        <v>470733</v>
       </c>
       <c r="R76" t="n">
-        <v>6866780</v>
+        <v>6866772</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>128387629</v>
       </c>
       <c r="B77" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8121,54 +8121,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128388416</v>
+        <v>128388714</v>
       </c>
       <c r="B78" t="n">
-        <v>98476</v>
+        <v>79032</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470816</v>
+        <v>470987</v>
       </c>
       <c r="R78" t="n">
-        <v>6866722</v>
+        <v>6866714</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8324,10 +8315,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128389403</v>
+        <v>128389886</v>
       </c>
       <c r="B80" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8335,21 +8326,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8359,10 +8350,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471187</v>
+        <v>471211</v>
       </c>
       <c r="R80" t="n">
-        <v>6866586</v>
+        <v>6866717</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8421,10 +8412,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128388714</v>
+        <v>128389403</v>
       </c>
       <c r="B81" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8432,21 +8423,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8456,10 +8447,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>470987</v>
+        <v>471187</v>
       </c>
       <c r="R81" t="n">
-        <v>6866714</v>
+        <v>6866586</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8518,45 +8509,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128389886</v>
+        <v>128388416</v>
       </c>
       <c r="B82" t="n">
-        <v>79032</v>
+        <v>98478</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471211</v>
+        <v>470816</v>
       </c>
       <c r="R82" t="n">
-        <v>6866717</v>
+        <v>6866722</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8812,7 +8812,7 @@
         <v>128387659</v>
       </c>
       <c r="B85" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128389213</v>
+        <v>128388228</v>
       </c>
       <c r="B87" t="n">
-        <v>80135</v>
+        <v>98478</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471148</v>
+        <v>470788</v>
       </c>
       <c r="R87" t="n">
-        <v>6866668</v>
+        <v>6866725</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9109,32 +9109,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128388228</v>
+        <v>128389213</v>
       </c>
       <c r="B88" t="n">
-        <v>98476</v>
+        <v>80135</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>470788</v>
+        <v>471148</v>
       </c>
       <c r="R88" t="n">
-        <v>6866725</v>
+        <v>6866668</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128388173</v>
+        <v>128389587</v>
       </c>
       <c r="B92" t="n">
-        <v>78699</v>
+        <v>80136</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>470786</v>
+        <v>471274</v>
       </c>
       <c r="R92" t="n">
-        <v>6866737</v>
+        <v>6866626</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128389587</v>
+        <v>128389918</v>
       </c>
       <c r="B93" t="n">
-        <v>80136</v>
+        <v>79032</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471274</v>
+        <v>471210</v>
       </c>
       <c r="R93" t="n">
-        <v>6866626</v>
+        <v>6866755</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9691,10 +9691,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128389918</v>
+        <v>128388173</v>
       </c>
       <c r="B94" t="n">
-        <v>79032</v>
+        <v>78699</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9702,21 +9702,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9726,13 +9726,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471210</v>
+        <v>470786</v>
       </c>
       <c r="R94" t="n">
-        <v>6866755</v>
+        <v>6866737</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128376636</v>
+        <v>128376574</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,21 +3319,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,13 +3343,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471320</v>
+        <v>471364</v>
       </c>
       <c r="R29" t="n">
-        <v>6866734</v>
+        <v>6866709</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128376702</v>
+        <v>128376636</v>
       </c>
       <c r="B30" t="n">
-        <v>78438</v>
+        <v>79032</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471287</v>
+        <v>471320</v>
       </c>
       <c r="R30" t="n">
-        <v>6866773</v>
+        <v>6866734</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374116</v>
+        <v>128376702</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>78438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,13 +3537,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471107</v>
+        <v>471287</v>
       </c>
       <c r="R31" t="n">
-        <v>6866853</v>
+        <v>6866773</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128376574</v>
+        <v>128374116</v>
       </c>
       <c r="B32" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471364</v>
+        <v>471107</v>
       </c>
       <c r="R32" t="n">
-        <v>6866709</v>
+        <v>6866853</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -8121,10 +8121,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128388714</v>
+        <v>128389403</v>
       </c>
       <c r="B78" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8132,21 +8132,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470987</v>
+        <v>471187</v>
       </c>
       <c r="R78" t="n">
-        <v>6866714</v>
+        <v>6866586</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8218,45 +8218,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128388815</v>
+        <v>128388416</v>
       </c>
       <c r="B79" t="n">
-        <v>79032</v>
+        <v>98478</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>470992</v>
+        <v>470816</v>
       </c>
       <c r="R79" t="n">
-        <v>6866696</v>
+        <v>6866722</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8315,7 +8324,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128389886</v>
+        <v>128388714</v>
       </c>
       <c r="B80" t="n">
         <v>79032</v>
@@ -8350,10 +8359,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471211</v>
+        <v>470987</v>
       </c>
       <c r="R80" t="n">
-        <v>6866717</v>
+        <v>6866714</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8412,10 +8421,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128389403</v>
+        <v>128388815</v>
       </c>
       <c r="B81" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8423,21 +8432,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8447,10 +8456,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471187</v>
+        <v>470992</v>
       </c>
       <c r="R81" t="n">
-        <v>6866586</v>
+        <v>6866696</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8509,54 +8518,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128388416</v>
+        <v>128389886</v>
       </c>
       <c r="B82" t="n">
-        <v>98478</v>
+        <v>79032</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>470816</v>
+        <v>471211</v>
       </c>
       <c r="R82" t="n">
-        <v>6866722</v>
+        <v>6866717</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128373928</v>
       </c>
       <c r="B2" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128375151</v>
       </c>
       <c r="B3" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128376373</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128376618</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,45 +1063,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128374470</v>
+        <v>128374420</v>
       </c>
       <c r="B6" t="n">
-        <v>78790</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471139</v>
+        <v>471132</v>
       </c>
       <c r="R6" t="n">
-        <v>6866835</v>
+        <v>6866856</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,54 +1169,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128374420</v>
+        <v>128375924</v>
       </c>
       <c r="B7" t="n">
-        <v>98478</v>
+        <v>78841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471132</v>
+        <v>471255</v>
       </c>
       <c r="R7" t="n">
-        <v>6866856</v>
+        <v>6866786</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128375924</v>
+        <v>128374470</v>
       </c>
       <c r="B8" t="n">
-        <v>78791</v>
+        <v>78840</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471255</v>
+        <v>471139</v>
       </c>
       <c r="R8" t="n">
-        <v>6866786</v>
+        <v>6866835</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128375190</v>
+        <v>128376258</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471145</v>
+        <v>471292</v>
       </c>
       <c r="R9" t="n">
-        <v>6866802</v>
+        <v>6866805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128376258</v>
+        <v>128375168</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471292</v>
+        <v>471139</v>
       </c>
       <c r="R10" t="n">
-        <v>6866805</v>
+        <v>6866821</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128375168</v>
+        <v>128375190</v>
       </c>
       <c r="B11" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471139</v>
+        <v>471145</v>
       </c>
       <c r="R11" t="n">
-        <v>6866821</v>
+        <v>6866802</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,7 +1657,7 @@
         <v>128376197</v>
       </c>
       <c r="B12" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128376676</v>
+        <v>128374859</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>80189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471287</v>
+        <v>471125</v>
       </c>
       <c r="R13" t="n">
-        <v>6866763</v>
+        <v>6866815</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128374859</v>
+        <v>128376676</v>
       </c>
       <c r="B14" t="n">
-        <v>80136</v>
+        <v>79083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471125</v>
+        <v>471287</v>
       </c>
       <c r="R14" t="n">
-        <v>6866815</v>
+        <v>6866763</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128375275</v>
+        <v>128374662</v>
       </c>
       <c r="B15" t="n">
-        <v>79064</v>
+        <v>79083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471162</v>
+        <v>471145</v>
       </c>
       <c r="R15" t="n">
-        <v>6866793</v>
+        <v>6866824</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2045,7 +2045,7 @@
         <v>128375734</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128374662</v>
+        <v>128375275</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>79115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471145</v>
+        <v>471162</v>
       </c>
       <c r="R17" t="n">
-        <v>6866824</v>
+        <v>6866793</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2239,7 +2239,7 @@
         <v>128376712</v>
       </c>
       <c r="B18" t="n">
-        <v>79621</v>
+        <v>79673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128375989</v>
+        <v>128375959</v>
       </c>
       <c r="B19" t="n">
-        <v>78010</v>
+        <v>79083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471276</v>
+        <v>471266</v>
       </c>
       <c r="R19" t="n">
-        <v>6866805</v>
+        <v>6866792</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128375959</v>
+        <v>128375989</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>78055</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471266</v>
+        <v>471276</v>
       </c>
       <c r="R20" t="n">
-        <v>6866792</v>
+        <v>6866805</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2527,10 +2527,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128375358</v>
+        <v>128375758</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471166</v>
+        <v>471232</v>
       </c>
       <c r="R21" t="n">
-        <v>6866785</v>
+        <v>6866781</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2624,10 +2624,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128375758</v>
+        <v>128375214</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471232</v>
+        <v>471144</v>
       </c>
       <c r="R22" t="n">
-        <v>6866781</v>
+        <v>6866814</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,10 +2721,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128375214</v>
+        <v>128375358</v>
       </c>
       <c r="B23" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471144</v>
+        <v>471166</v>
       </c>
       <c r="R23" t="n">
-        <v>6866814</v>
+        <v>6866785</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2821,7 +2821,7 @@
         <v>128376206</v>
       </c>
       <c r="B24" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128374452</v>
       </c>
       <c r="B25" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128375464</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128375560</v>
+        <v>128376736</v>
       </c>
       <c r="B27" t="n">
-        <v>57833</v>
+        <v>78055</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471219</v>
+        <v>471282</v>
       </c>
       <c r="R27" t="n">
-        <v>6866779</v>
+        <v>6866783</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3180,11 +3180,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3211,10 +3206,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128376736</v>
+        <v>128375560</v>
       </c>
       <c r="B28" t="n">
-        <v>78010</v>
+        <v>57845</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3217,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,13 +3241,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471282</v>
+        <v>471219</v>
       </c>
       <c r="R28" t="n">
-        <v>6866783</v>
+        <v>6866779</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3282,6 +3277,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128376574</v>
+        <v>128376636</v>
       </c>
       <c r="B29" t="n">
-        <v>78791</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,21 +3319,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,13 +3343,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471364</v>
+        <v>471320</v>
       </c>
       <c r="R29" t="n">
-        <v>6866709</v>
+        <v>6866734</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128376636</v>
+        <v>128376702</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>78486</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471320</v>
+        <v>471287</v>
       </c>
       <c r="R30" t="n">
-        <v>6866734</v>
+        <v>6866773</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128376702</v>
+        <v>128376574</v>
       </c>
       <c r="B31" t="n">
-        <v>78438</v>
+        <v>78841</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471287</v>
+        <v>471364</v>
       </c>
       <c r="R31" t="n">
-        <v>6866773</v>
+        <v>6866709</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3602,7 +3602,7 @@
         <v>128374116</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128375289</v>
+        <v>128375249</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471165</v>
+        <v>471158</v>
       </c>
       <c r="R33" t="n">
-        <v>6866794</v>
+        <v>6866800</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128375249</v>
+        <v>128375794</v>
       </c>
       <c r="B34" t="n">
-        <v>79032</v>
+        <v>78841</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3804,21 +3804,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471158</v>
+        <v>471241</v>
       </c>
       <c r="R34" t="n">
-        <v>6866800</v>
+        <v>6866786</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128375794</v>
+        <v>128375289</v>
       </c>
       <c r="B35" t="n">
-        <v>78791</v>
+        <v>79083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471241</v>
+        <v>471165</v>
       </c>
       <c r="R35" t="n">
-        <v>6866786</v>
+        <v>6866794</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3987,10 +3987,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128374814</v>
+        <v>128373989</v>
       </c>
       <c r="B36" t="n">
-        <v>79032</v>
+        <v>80188</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3998,21 +3998,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471137</v>
+        <v>471102</v>
       </c>
       <c r="R36" t="n">
-        <v>6866828</v>
+        <v>6866857</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4058,11 +4058,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4089,10 +4084,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128376382</v>
+        <v>128374814</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4124,10 +4119,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471342</v>
+        <v>471137</v>
       </c>
       <c r="R37" t="n">
-        <v>6866780</v>
+        <v>6866828</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4160,6 +4155,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4186,10 +4186,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373989</v>
+        <v>128376382</v>
       </c>
       <c r="B38" t="n">
-        <v>80135</v>
+        <v>79083</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4197,21 +4197,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4221,10 +4221,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>471102</v>
+        <v>471342</v>
       </c>
       <c r="R38" t="n">
-        <v>6866857</v>
+        <v>6866780</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4286,7 +4286,7 @@
         <v>128374436</v>
       </c>
       <c r="B39" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>128374500</v>
       </c>
       <c r="B40" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>128376649</v>
       </c>
       <c r="B41" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>128375508</v>
       </c>
       <c r="B42" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>128375498</v>
       </c>
       <c r="B43" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>128375808</v>
       </c>
       <c r="B44" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>128376462</v>
       </c>
       <c r="B45" t="n">
-        <v>91934</v>
+        <v>92026</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>128375307</v>
       </c>
       <c r="B46" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>128376295</v>
       </c>
       <c r="B47" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>128375399</v>
       </c>
       <c r="B48" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5276,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128388207</v>
+        <v>128387779</v>
       </c>
       <c r="B49" t="n">
-        <v>78790</v>
+        <v>98571</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470789</v>
+        <v>470744</v>
       </c>
       <c r="R49" t="n">
-        <v>6866739</v>
+        <v>6866736</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128387779</v>
+        <v>128388103</v>
       </c>
       <c r="B50" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470744</v>
+        <v>470763</v>
       </c>
       <c r="R50" t="n">
-        <v>6866736</v>
+        <v>6866753</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,32 +5470,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128388103</v>
+        <v>128388207</v>
       </c>
       <c r="B51" t="n">
-        <v>98478</v>
+        <v>78840</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470763</v>
+        <v>470789</v>
       </c>
       <c r="R51" t="n">
-        <v>6866753</v>
+        <v>6866739</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5570,7 +5570,7 @@
         <v>128387977</v>
       </c>
       <c r="B52" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128389894</v>
+        <v>128387828</v>
       </c>
       <c r="B53" t="n">
-        <v>79032</v>
+        <v>78841</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5684,21 +5684,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>471207</v>
+        <v>470743</v>
       </c>
       <c r="R53" t="n">
-        <v>6866729</v>
+        <v>6866698</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>128389953</v>
       </c>
       <c r="B54" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5867,10 +5867,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128387828</v>
+        <v>128389894</v>
       </c>
       <c r="B55" t="n">
-        <v>78791</v>
+        <v>79083</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5878,21 +5878,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5902,13 +5902,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470743</v>
+        <v>471207</v>
       </c>
       <c r="R55" t="n">
-        <v>6866698</v>
+        <v>6866729</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>128387790</v>
       </c>
       <c r="B56" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>128388996</v>
       </c>
       <c r="B57" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>128388496</v>
       </c>
       <c r="B58" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>128389324</v>
       </c>
       <c r="B59" t="n">
-        <v>79621</v>
+        <v>79673</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>128387936</v>
       </c>
       <c r="B60" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128389511</v>
+        <v>128389855</v>
       </c>
       <c r="B61" t="n">
-        <v>80135</v>
+        <v>57845</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471237</v>
+        <v>471241</v>
       </c>
       <c r="R61" t="n">
-        <v>6866588</v>
+        <v>6866622</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6529,6 +6529,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6555,10 +6560,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128389329</v>
+        <v>128388778</v>
       </c>
       <c r="B62" t="n">
-        <v>78790</v>
+        <v>79162</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6566,21 +6571,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6595,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471172</v>
+        <v>470995</v>
       </c>
       <c r="R62" t="n">
-        <v>6866632</v>
+        <v>6866711</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6652,10 +6657,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128387227</v>
+        <v>128389262</v>
       </c>
       <c r="B63" t="n">
-        <v>80135</v>
+        <v>80189</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6663,21 +6668,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6692,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>470551</v>
+        <v>471168</v>
       </c>
       <c r="R63" t="n">
-        <v>6866892</v>
+        <v>6866647</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,10 +6754,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128387286</v>
+        <v>128389511</v>
       </c>
       <c r="B64" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6784,10 +6789,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>470551</v>
+        <v>471237</v>
       </c>
       <c r="R64" t="n">
-        <v>6866872</v>
+        <v>6866588</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,10 +6851,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128389262</v>
+        <v>128389329</v>
       </c>
       <c r="B65" t="n">
-        <v>80136</v>
+        <v>78840</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6857,21 +6862,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6886,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471168</v>
+        <v>471172</v>
       </c>
       <c r="R65" t="n">
-        <v>6866647</v>
+        <v>6866632</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,10 +6948,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128388778</v>
+        <v>128387227</v>
       </c>
       <c r="B66" t="n">
-        <v>79111</v>
+        <v>80188</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,21 +6959,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6983,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470995</v>
+        <v>470551</v>
       </c>
       <c r="R66" t="n">
-        <v>6866711</v>
+        <v>6866892</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7040,10 +7045,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128389855</v>
+        <v>128387286</v>
       </c>
       <c r="B67" t="n">
-        <v>57833</v>
+        <v>80188</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,21 +7056,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,13 +7080,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471241</v>
+        <v>470551</v>
       </c>
       <c r="R67" t="n">
-        <v>6866622</v>
+        <v>6866872</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7111,11 +7116,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7145,7 +7145,7 @@
         <v>128388804</v>
       </c>
       <c r="B68" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>128389227</v>
       </c>
       <c r="B69" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>128389069</v>
       </c>
       <c r="B70" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>128389187</v>
       </c>
       <c r="B71" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128389641</v>
+        <v>128388766</v>
       </c>
       <c r="B72" t="n">
-        <v>80135</v>
+        <v>79162</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471241</v>
+        <v>470981</v>
       </c>
       <c r="R72" t="n">
-        <v>6866656</v>
+        <v>6866714</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128388766</v>
+        <v>128388646</v>
       </c>
       <c r="B73" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7638,21 +7638,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470981</v>
+        <v>470945</v>
       </c>
       <c r="R73" t="n">
-        <v>6866714</v>
+        <v>6866709</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7724,10 +7724,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128388646</v>
+        <v>128389641</v>
       </c>
       <c r="B74" t="n">
-        <v>79064</v>
+        <v>80188</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>470945</v>
+        <v>471241</v>
       </c>
       <c r="R74" t="n">
-        <v>6866709</v>
+        <v>6866656</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7821,32 +7821,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128388053</v>
+        <v>128387695</v>
       </c>
       <c r="B75" t="n">
-        <v>78791</v>
+        <v>98571</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7856,13 +7856,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>470770</v>
+        <v>470733</v>
       </c>
       <c r="R75" t="n">
-        <v>6866780</v>
+        <v>6866772</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7918,32 +7918,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128387695</v>
+        <v>128388053</v>
       </c>
       <c r="B76" t="n">
-        <v>98478</v>
+        <v>78841</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7953,13 +7953,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>470733</v>
+        <v>470770</v>
       </c>
       <c r="R76" t="n">
-        <v>6866772</v>
+        <v>6866780</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>128387629</v>
       </c>
       <c r="B77" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8121,10 +8121,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128389403</v>
+        <v>128388815</v>
       </c>
       <c r="B78" t="n">
-        <v>78791</v>
+        <v>79083</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8132,21 +8132,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471187</v>
+        <v>470992</v>
       </c>
       <c r="R78" t="n">
-        <v>6866586</v>
+        <v>6866696</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8218,54 +8218,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128388416</v>
+        <v>128388714</v>
       </c>
       <c r="B79" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>470816</v>
+        <v>470987</v>
       </c>
       <c r="R79" t="n">
-        <v>6866722</v>
+        <v>6866714</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8324,10 +8315,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128388714</v>
+        <v>128389886</v>
       </c>
       <c r="B80" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8359,10 +8350,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>470987</v>
+        <v>471211</v>
       </c>
       <c r="R80" t="n">
-        <v>6866714</v>
+        <v>6866717</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8421,45 +8412,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128388815</v>
+        <v>128388416</v>
       </c>
       <c r="B81" t="n">
-        <v>79032</v>
+        <v>98571</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>470992</v>
+        <v>470816</v>
       </c>
       <c r="R81" t="n">
-        <v>6866696</v>
+        <v>6866722</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8518,10 +8518,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128389886</v>
+        <v>128389403</v>
       </c>
       <c r="B82" t="n">
-        <v>79032</v>
+        <v>78841</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8529,21 +8529,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471211</v>
+        <v>471187</v>
       </c>
       <c r="R82" t="n">
-        <v>6866717</v>
+        <v>6866586</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8618,7 +8618,7 @@
         <v>128387736</v>
       </c>
       <c r="B83" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>128389124</v>
       </c>
       <c r="B84" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>128387659</v>
       </c>
       <c r="B85" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>128387292</v>
       </c>
       <c r="B86" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128388228</v>
+        <v>128389213</v>
       </c>
       <c r="B87" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>470788</v>
+        <v>471148</v>
       </c>
       <c r="R87" t="n">
-        <v>6866725</v>
+        <v>6866668</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128389213</v>
+        <v>128389351</v>
       </c>
       <c r="B88" t="n">
-        <v>80135</v>
+        <v>78055</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471148</v>
+        <v>471215</v>
       </c>
       <c r="R88" t="n">
-        <v>6866668</v>
+        <v>6866634</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9209,7 +9209,7 @@
         <v>128389901</v>
       </c>
       <c r="B89" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9303,32 +9303,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128389351</v>
+        <v>128388228</v>
       </c>
       <c r="B90" t="n">
-        <v>78010</v>
+        <v>98571</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471215</v>
+        <v>470788</v>
       </c>
       <c r="R90" t="n">
-        <v>6866634</v>
+        <v>6866725</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9403,7 +9403,7 @@
         <v>128388690</v>
       </c>
       <c r="B91" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128389587</v>
+        <v>128388173</v>
       </c>
       <c r="B92" t="n">
-        <v>80136</v>
+        <v>78749</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471274</v>
+        <v>470786</v>
       </c>
       <c r="R92" t="n">
-        <v>6866626</v>
+        <v>6866737</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128389918</v>
+        <v>128389587</v>
       </c>
       <c r="B93" t="n">
-        <v>79032</v>
+        <v>80189</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471210</v>
+        <v>471274</v>
       </c>
       <c r="R93" t="n">
-        <v>6866755</v>
+        <v>6866626</v>
       </c>
       <c r="S93" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9691,10 +9691,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128388173</v>
+        <v>128389918</v>
       </c>
       <c r="B94" t="n">
-        <v>78699</v>
+        <v>79083</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9702,21 +9702,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9726,13 +9726,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>470786</v>
+        <v>471210</v>
       </c>
       <c r="R94" t="n">
-        <v>6866737</v>
+        <v>6866755</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>128389286</v>
       </c>
       <c r="B95" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9882,6 +9882,2916 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128502263</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>471328</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6866612</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128502381</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>185</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>471311</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6866616</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>128501285</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>185</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>471269</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6866648</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128501083</v>
+      </c>
+      <c r="B99" t="n">
+        <v>78840</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>471219</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6866725</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>128501140</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>471253</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6866704</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>128502704</v>
+      </c>
+      <c r="B101" t="n">
+        <v>91417</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>471366</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6866720</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128501794</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>471329</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6866557</v>
+      </c>
+      <c r="S102" t="n">
+        <v>20</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128502548</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>185</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>471325</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6866680</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128501127</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>471245</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6866708</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128501181</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>471251</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6866689</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>128501144</v>
+      </c>
+      <c r="B106" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>471257</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6866697</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>128501480</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>185</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>471273</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6866589</v>
+      </c>
+      <c r="S107" t="n">
+        <v>20</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>128502802</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>471256</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6866728</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>128501209</v>
+      </c>
+      <c r="B109" t="n">
+        <v>78840</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>471244</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6866687</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>128502100</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>185</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>471347</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6866584</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>128502866</v>
+      </c>
+      <c r="B111" t="n">
+        <v>98488</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>471139</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6866727</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>128502259</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>185</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>471327</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6866603</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128501973</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>185</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>471363</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6866544</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>128501347</v>
+      </c>
+      <c r="B114" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>471275</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6866627</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>128502509</v>
+      </c>
+      <c r="B115" t="n">
+        <v>78840</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>471315</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6866670</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>128501097</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>471224</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6866707</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>128502607</v>
+      </c>
+      <c r="B117" t="n">
+        <v>78840</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>471349</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6866695</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>128501927</v>
+      </c>
+      <c r="B118" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>185</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>471340</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6866563</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>128501224</v>
+      </c>
+      <c r="B119" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>185</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>471253</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6866666</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>128502212</v>
+      </c>
+      <c r="B120" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>471325</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6866592</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>128502291</v>
+      </c>
+      <c r="B121" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>185</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>471320</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6866609</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>128502189</v>
+      </c>
+      <c r="B122" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>185</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>471327</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6866591</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>128501253</v>
+      </c>
+      <c r="B123" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>185</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>471267</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6866658</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>128502309</v>
+      </c>
+      <c r="B124" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>471311</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6866598</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>128502178</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>471326</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6866583</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128373928</v>
+        <v>128374470</v>
       </c>
       <c r="B2" t="n">
-        <v>79115</v>
+        <v>78840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471086</v>
+        <v>471139</v>
       </c>
       <c r="R2" t="n">
-        <v>6866862</v>
+        <v>6866835</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128375151</v>
+        <v>128376373</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471135</v>
+        <v>471330</v>
       </c>
       <c r="R3" t="n">
-        <v>6866819</v>
+        <v>6866787</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128376373</v>
+        <v>128376618</v>
       </c>
       <c r="B4" t="n">
         <v>79083</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471330</v>
+        <v>471331</v>
       </c>
       <c r="R4" t="n">
-        <v>6866787</v>
+        <v>6866715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128376618</v>
+        <v>128373928</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471331</v>
+        <v>471086</v>
       </c>
       <c r="R5" t="n">
-        <v>6866715</v>
+        <v>6866862</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,54 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128374420</v>
+        <v>128375151</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>79115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471132</v>
+        <v>471135</v>
       </c>
       <c r="R6" t="n">
-        <v>6866856</v>
+        <v>6866819</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,45 +1257,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128374470</v>
+        <v>128374420</v>
       </c>
       <c r="B8" t="n">
-        <v>78840</v>
+        <v>98571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471139</v>
+        <v>471132</v>
       </c>
       <c r="R8" t="n">
-        <v>6866835</v>
+        <v>6866856</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128376258</v>
+        <v>128376197</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471292</v>
+        <v>471280</v>
       </c>
       <c r="R9" t="n">
-        <v>6866805</v>
+        <v>6866807</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128375168</v>
+        <v>128376258</v>
       </c>
       <c r="B10" t="n">
         <v>79083</v>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471139</v>
+        <v>471292</v>
       </c>
       <c r="R10" t="n">
-        <v>6866821</v>
+        <v>6866805</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128375190</v>
+        <v>128375168</v>
       </c>
       <c r="B11" t="n">
         <v>79083</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471145</v>
+        <v>471139</v>
       </c>
       <c r="R11" t="n">
-        <v>6866802</v>
+        <v>6866821</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128376197</v>
+        <v>128375190</v>
       </c>
       <c r="B12" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471280</v>
+        <v>471145</v>
       </c>
       <c r="R12" t="n">
-        <v>6866807</v>
+        <v>6866802</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128374662</v>
+        <v>128375275</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471145</v>
+        <v>471162</v>
       </c>
       <c r="R15" t="n">
-        <v>6866824</v>
+        <v>6866793</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128375275</v>
+        <v>128374662</v>
       </c>
       <c r="B17" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471162</v>
+        <v>471145</v>
       </c>
       <c r="R17" t="n">
-        <v>6866793</v>
+        <v>6866824</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128375758</v>
+        <v>128375214</v>
       </c>
       <c r="B21" t="n">
         <v>79083</v>
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471232</v>
+        <v>471144</v>
       </c>
       <c r="R21" t="n">
-        <v>6866781</v>
+        <v>6866814</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2624,7 +2624,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128375214</v>
+        <v>128375358</v>
       </c>
       <c r="B22" t="n">
         <v>79083</v>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471144</v>
+        <v>471166</v>
       </c>
       <c r="R22" t="n">
-        <v>6866814</v>
+        <v>6866785</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,7 +2721,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128375358</v>
+        <v>128375758</v>
       </c>
       <c r="B23" t="n">
         <v>79083</v>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471166</v>
+        <v>471232</v>
       </c>
       <c r="R23" t="n">
-        <v>6866785</v>
+        <v>6866781</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128376636</v>
+        <v>128376702</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>78486</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,21 +3319,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,13 +3343,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471320</v>
+        <v>471287</v>
       </c>
       <c r="R29" t="n">
-        <v>6866734</v>
+        <v>6866773</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128376702</v>
+        <v>128376636</v>
       </c>
       <c r="B30" t="n">
-        <v>78486</v>
+        <v>79083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471287</v>
+        <v>471320</v>
       </c>
       <c r="R30" t="n">
-        <v>6866773</v>
+        <v>6866734</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128376574</v>
+        <v>128374116</v>
       </c>
       <c r="B31" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,13 +3537,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471364</v>
+        <v>471107</v>
       </c>
       <c r="R31" t="n">
-        <v>6866709</v>
+        <v>6866853</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374116</v>
+        <v>128376574</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471107</v>
+        <v>471364</v>
       </c>
       <c r="R32" t="n">
-        <v>6866853</v>
+        <v>6866709</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128375249</v>
+        <v>128375794</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471158</v>
+        <v>471241</v>
       </c>
       <c r="R33" t="n">
-        <v>6866800</v>
+        <v>6866786</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128375794</v>
+        <v>128375289</v>
       </c>
       <c r="B34" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3804,21 +3804,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471241</v>
+        <v>471165</v>
       </c>
       <c r="R34" t="n">
-        <v>6866786</v>
+        <v>6866794</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128375289</v>
+        <v>128375249</v>
       </c>
       <c r="B35" t="n">
         <v>79083</v>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471165</v>
+        <v>471158</v>
       </c>
       <c r="R35" t="n">
-        <v>6866794</v>
+        <v>6866800</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4680,45 +4680,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128375498</v>
+        <v>128376462</v>
       </c>
       <c r="B43" t="n">
-        <v>79083</v>
+        <v>92026</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471198</v>
+        <v>471351</v>
       </c>
       <c r="R43" t="n">
-        <v>6866776</v>
+        <v>6866748</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4751,6 +4760,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4874,54 +4888,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128376462</v>
+        <v>128375498</v>
       </c>
       <c r="B45" t="n">
-        <v>92026</v>
+        <v>79083</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471351</v>
+        <v>471198</v>
       </c>
       <c r="R45" t="n">
-        <v>6866748</v>
+        <v>6866776</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4954,11 +4959,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128387779</v>
+        <v>128388207</v>
       </c>
       <c r="B49" t="n">
-        <v>98571</v>
+        <v>78840</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470744</v>
+        <v>470789</v>
       </c>
       <c r="R49" t="n">
-        <v>6866736</v>
+        <v>6866739</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5373,7 +5373,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128388103</v>
+        <v>128387779</v>
       </c>
       <c r="B50" t="n">
         <v>98571</v>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470763</v>
+        <v>470744</v>
       </c>
       <c r="R50" t="n">
-        <v>6866753</v>
+        <v>6866736</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,32 +5470,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128388207</v>
+        <v>128388103</v>
       </c>
       <c r="B51" t="n">
-        <v>78840</v>
+        <v>98571</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470789</v>
+        <v>470763</v>
       </c>
       <c r="R51" t="n">
-        <v>6866739</v>
+        <v>6866753</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128387828</v>
+        <v>128389894</v>
       </c>
       <c r="B53" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5684,21 +5684,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>470743</v>
+        <v>471207</v>
       </c>
       <c r="R53" t="n">
-        <v>6866698</v>
+        <v>6866729</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5867,32 +5867,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128389894</v>
+        <v>128387790</v>
       </c>
       <c r="B55" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>471207</v>
+        <v>470732</v>
       </c>
       <c r="R55" t="n">
-        <v>6866729</v>
+        <v>6866727</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5964,32 +5964,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128387790</v>
+        <v>128387828</v>
       </c>
       <c r="B56" t="n">
-        <v>98571</v>
+        <v>78841</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5999,13 +5999,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>470732</v>
+        <v>470743</v>
       </c>
       <c r="R56" t="n">
-        <v>6866727</v>
+        <v>6866698</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128389855</v>
+        <v>128389262</v>
       </c>
       <c r="B61" t="n">
-        <v>57845</v>
+        <v>80189</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471241</v>
+        <v>471168</v>
       </c>
       <c r="R61" t="n">
-        <v>6866622</v>
+        <v>6866647</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6529,11 +6529,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6657,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128389262</v>
+        <v>128389855</v>
       </c>
       <c r="B63" t="n">
-        <v>80189</v>
+        <v>57845</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6668,21 +6663,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6692,13 +6687,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471168</v>
+        <v>471241</v>
       </c>
       <c r="R63" t="n">
-        <v>6866647</v>
+        <v>6866622</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6728,6 +6723,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7142,7 +7142,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128388804</v>
+        <v>128389227</v>
       </c>
       <c r="B68" t="n">
         <v>79115</v>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>470987</v>
+        <v>471156</v>
       </c>
       <c r="R68" t="n">
-        <v>6866706</v>
+        <v>6866665</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,7 +7239,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128389227</v>
+        <v>128388804</v>
       </c>
       <c r="B69" t="n">
         <v>79115</v>
@@ -7274,10 +7274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471156</v>
+        <v>470987</v>
       </c>
       <c r="R69" t="n">
-        <v>6866665</v>
+        <v>6866706</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128388766</v>
+        <v>128388646</v>
       </c>
       <c r="B72" t="n">
-        <v>79162</v>
+        <v>79115</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470981</v>
+        <v>470945</v>
       </c>
       <c r="R72" t="n">
-        <v>6866714</v>
+        <v>6866709</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128388646</v>
+        <v>128388766</v>
       </c>
       <c r="B73" t="n">
-        <v>79115</v>
+        <v>79162</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7638,21 +7638,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470945</v>
+        <v>470981</v>
       </c>
       <c r="R73" t="n">
-        <v>6866709</v>
+        <v>6866714</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8121,10 +8121,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128388815</v>
+        <v>128389403</v>
       </c>
       <c r="B78" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8132,21 +8132,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470992</v>
+        <v>471187</v>
       </c>
       <c r="R78" t="n">
-        <v>6866696</v>
+        <v>6866586</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8218,7 +8218,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128388714</v>
+        <v>128388815</v>
       </c>
       <c r="B79" t="n">
         <v>79083</v>
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>470987</v>
+        <v>470992</v>
       </c>
       <c r="R79" t="n">
-        <v>6866714</v>
+        <v>6866696</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8412,54 +8412,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128388416</v>
+        <v>128388714</v>
       </c>
       <c r="B81" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>470816</v>
+        <v>470987</v>
       </c>
       <c r="R81" t="n">
-        <v>6866722</v>
+        <v>6866714</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8518,45 +8509,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128389403</v>
+        <v>128388416</v>
       </c>
       <c r="B82" t="n">
-        <v>78841</v>
+        <v>98571</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471187</v>
+        <v>470816</v>
       </c>
       <c r="R82" t="n">
-        <v>6866586</v>
+        <v>6866722</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128389351</v>
+        <v>128389901</v>
       </c>
       <c r="B88" t="n">
-        <v>78055</v>
+        <v>79083</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471215</v>
+        <v>471209</v>
       </c>
       <c r="R88" t="n">
-        <v>6866634</v>
+        <v>6866743</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9206,10 +9206,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128389901</v>
+        <v>128389351</v>
       </c>
       <c r="B89" t="n">
-        <v>79083</v>
+        <v>78055</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9217,21 +9217,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471209</v>
+        <v>471215</v>
       </c>
       <c r="R89" t="n">
-        <v>6866743</v>
+        <v>6866634</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128388173</v>
+        <v>128389587</v>
       </c>
       <c r="B92" t="n">
-        <v>78749</v>
+        <v>80189</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>470786</v>
+        <v>471274</v>
       </c>
       <c r="R92" t="n">
-        <v>6866737</v>
+        <v>6866626</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128389587</v>
+        <v>128388173</v>
       </c>
       <c r="B93" t="n">
-        <v>80189</v>
+        <v>78749</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9629,10 +9629,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471274</v>
+        <v>470786</v>
       </c>
       <c r="R93" t="n">
-        <v>6866626</v>
+        <v>6866737</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9885,10 +9885,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128502263</v>
+        <v>128502381</v>
       </c>
       <c r="B96" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9896,21 +9896,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9920,10 +9920,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471328</v>
+        <v>471311</v>
       </c>
       <c r="R96" t="n">
-        <v>6866612</v>
+        <v>6866616</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9982,10 +9982,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128502381</v>
+        <v>128502263</v>
       </c>
       <c r="B97" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9993,21 +9993,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471311</v>
+        <v>471328</v>
       </c>
       <c r="R97" t="n">
-        <v>6866616</v>
+        <v>6866612</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10855,10 +10855,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128501144</v>
+        <v>128501480</v>
       </c>
       <c r="B106" t="n">
-        <v>78841</v>
+        <v>79115</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10866,21 +10866,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10890,13 +10890,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471257</v>
+        <v>471273</v>
       </c>
       <c r="R106" t="n">
-        <v>6866697</v>
+        <v>6866589</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10952,10 +10952,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128501480</v>
+        <v>128501144</v>
       </c>
       <c r="B107" t="n">
-        <v>79115</v>
+        <v>78841</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10963,21 +10963,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471273</v>
+        <v>471257</v>
       </c>
       <c r="R107" t="n">
-        <v>6866589</v>
+        <v>6866697</v>
       </c>
       <c r="S107" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11146,10 +11146,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128501209</v>
+        <v>128502100</v>
       </c>
       <c r="B109" t="n">
-        <v>78840</v>
+        <v>79115</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11157,21 +11157,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11181,10 +11181,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471244</v>
+        <v>471347</v>
       </c>
       <c r="R109" t="n">
-        <v>6866687</v>
+        <v>6866584</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11243,10 +11243,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128502100</v>
+        <v>128501209</v>
       </c>
       <c r="B110" t="n">
-        <v>79115</v>
+        <v>78840</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11254,21 +11254,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471347</v>
+        <v>471244</v>
       </c>
       <c r="R110" t="n">
-        <v>6866584</v>
+        <v>6866687</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11534,10 +11534,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128501973</v>
+        <v>128502509</v>
       </c>
       <c r="B113" t="n">
-        <v>79115</v>
+        <v>78840</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11545,21 +11545,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471363</v>
+        <v>471315</v>
       </c>
       <c r="R113" t="n">
-        <v>6866544</v>
+        <v>6866670</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11631,10 +11631,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128501347</v>
+        <v>128501097</v>
       </c>
       <c r="B114" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11642,21 +11642,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471275</v>
+        <v>471224</v>
       </c>
       <c r="R114" t="n">
-        <v>6866627</v>
+        <v>6866707</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11728,10 +11728,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128502509</v>
+        <v>128501973</v>
       </c>
       <c r="B115" t="n">
-        <v>78840</v>
+        <v>79115</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11739,21 +11739,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11763,10 +11763,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471315</v>
+        <v>471363</v>
       </c>
       <c r="R115" t="n">
-        <v>6866670</v>
+        <v>6866544</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128501097</v>
+        <v>128502607</v>
       </c>
       <c r="B116" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11836,21 +11836,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471224</v>
+        <v>471349</v>
       </c>
       <c r="R116" t="n">
-        <v>6866707</v>
+        <v>6866695</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11922,10 +11922,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128502607</v>
+        <v>128501347</v>
       </c>
       <c r="B117" t="n">
-        <v>78840</v>
+        <v>80188</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11933,21 +11933,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11957,10 +11957,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471349</v>
+        <v>471275</v>
       </c>
       <c r="R117" t="n">
-        <v>6866695</v>
+        <v>6866627</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128374470</v>
+        <v>128376373</v>
       </c>
       <c r="B2" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471139</v>
+        <v>471330</v>
       </c>
       <c r="R2" t="n">
-        <v>6866835</v>
+        <v>6866787</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128376373</v>
+        <v>128374470</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471330</v>
+        <v>471139</v>
       </c>
       <c r="R3" t="n">
-        <v>6866787</v>
+        <v>6866835</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1160,45 +1160,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128375924</v>
+        <v>128374420</v>
       </c>
       <c r="B7" t="n">
-        <v>78841</v>
+        <v>98571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471255</v>
+        <v>471132</v>
       </c>
       <c r="R7" t="n">
-        <v>6866786</v>
+        <v>6866856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,54 +1266,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128374420</v>
+        <v>128375924</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>78841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471132</v>
+        <v>471255</v>
       </c>
       <c r="R8" t="n">
-        <v>6866856</v>
+        <v>6866786</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128375959</v>
+        <v>128375989</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>78055</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471266</v>
+        <v>471276</v>
       </c>
       <c r="R19" t="n">
-        <v>6866792</v>
+        <v>6866805</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128375989</v>
+        <v>128375959</v>
       </c>
       <c r="B20" t="n">
-        <v>78055</v>
+        <v>79083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471276</v>
+        <v>471266</v>
       </c>
       <c r="R20" t="n">
-        <v>6866805</v>
+        <v>6866792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128376736</v>
+        <v>128375560</v>
       </c>
       <c r="B27" t="n">
-        <v>78055</v>
+        <v>57845</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471282</v>
+        <v>471219</v>
       </c>
       <c r="R27" t="n">
-        <v>6866783</v>
+        <v>6866779</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3180,6 +3180,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3206,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128375560</v>
+        <v>128376736</v>
       </c>
       <c r="B28" t="n">
-        <v>57845</v>
+        <v>78055</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3217,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3241,13 +3246,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471219</v>
+        <v>471282</v>
       </c>
       <c r="R28" t="n">
-        <v>6866779</v>
+        <v>6866783</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3277,11 +3282,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128376702</v>
+        <v>128376636</v>
       </c>
       <c r="B29" t="n">
-        <v>78486</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,21 +3319,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,13 +3343,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471287</v>
+        <v>471320</v>
       </c>
       <c r="R29" t="n">
-        <v>6866773</v>
+        <v>6866734</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128376636</v>
+        <v>128376702</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>78486</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471320</v>
+        <v>471287</v>
       </c>
       <c r="R30" t="n">
-        <v>6866734</v>
+        <v>6866773</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128375794</v>
+        <v>128375289</v>
       </c>
       <c r="B33" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471241</v>
+        <v>471165</v>
       </c>
       <c r="R33" t="n">
-        <v>6866786</v>
+        <v>6866794</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128375289</v>
+        <v>128375249</v>
       </c>
       <c r="B34" t="n">
         <v>79083</v>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471165</v>
+        <v>471158</v>
       </c>
       <c r="R34" t="n">
-        <v>6866794</v>
+        <v>6866800</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128375249</v>
+        <v>128375794</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471158</v>
+        <v>471241</v>
       </c>
       <c r="R35" t="n">
-        <v>6866800</v>
+        <v>6866786</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3987,10 +3987,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128373989</v>
+        <v>128374814</v>
       </c>
       <c r="B36" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3998,21 +3998,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471102</v>
+        <v>471137</v>
       </c>
       <c r="R36" t="n">
-        <v>6866857</v>
+        <v>6866828</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4058,6 +4058,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4084,7 +4089,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128374814</v>
+        <v>128376382</v>
       </c>
       <c r="B37" t="n">
         <v>79083</v>
@@ -4119,10 +4124,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471137</v>
+        <v>471342</v>
       </c>
       <c r="R37" t="n">
-        <v>6866828</v>
+        <v>6866780</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4155,11 +4160,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4186,10 +4186,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128376382</v>
+        <v>128373989</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4197,21 +4197,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4221,10 +4221,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>471342</v>
+        <v>471102</v>
       </c>
       <c r="R38" t="n">
-        <v>6866780</v>
+        <v>6866857</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128389262</v>
+        <v>128389855</v>
       </c>
       <c r="B61" t="n">
-        <v>80189</v>
+        <v>57845</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471168</v>
+        <v>471241</v>
       </c>
       <c r="R61" t="n">
-        <v>6866647</v>
+        <v>6866622</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6529,6 +6529,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6555,10 +6560,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128388778</v>
+        <v>128389262</v>
       </c>
       <c r="B62" t="n">
-        <v>79162</v>
+        <v>80189</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6566,21 +6571,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6595,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>470995</v>
+        <v>471168</v>
       </c>
       <c r="R62" t="n">
-        <v>6866711</v>
+        <v>6866647</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6652,10 +6657,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128389855</v>
+        <v>128388778</v>
       </c>
       <c r="B63" t="n">
-        <v>57845</v>
+        <v>79162</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6663,21 +6668,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,13 +6692,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471241</v>
+        <v>470995</v>
       </c>
       <c r="R63" t="n">
-        <v>6866622</v>
+        <v>6866711</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6723,11 +6728,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7142,10 +7142,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128389227</v>
+        <v>128389069</v>
       </c>
       <c r="B68" t="n">
-        <v>79115</v>
+        <v>80188</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471156</v>
+        <v>471158</v>
       </c>
       <c r="R68" t="n">
-        <v>6866665</v>
+        <v>6866734</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128388804</v>
+        <v>128389187</v>
       </c>
       <c r="B69" t="n">
-        <v>79115</v>
+        <v>78840</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>470987</v>
+        <v>471196</v>
       </c>
       <c r="R69" t="n">
         <v>6866706</v>
@@ -7336,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128389069</v>
+        <v>128389227</v>
       </c>
       <c r="B70" t="n">
-        <v>80188</v>
+        <v>79115</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7347,21 +7347,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471158</v>
+        <v>471156</v>
       </c>
       <c r="R70" t="n">
-        <v>6866734</v>
+        <v>6866665</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128389187</v>
+        <v>128388804</v>
       </c>
       <c r="B71" t="n">
-        <v>78840</v>
+        <v>79115</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471196</v>
+        <v>470987</v>
       </c>
       <c r="R71" t="n">
         <v>6866706</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128389213</v>
+        <v>128388228</v>
       </c>
       <c r="B87" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471148</v>
+        <v>470788</v>
       </c>
       <c r="R87" t="n">
-        <v>6866668</v>
+        <v>6866725</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128389901</v>
+        <v>128389213</v>
       </c>
       <c r="B88" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471209</v>
+        <v>471148</v>
       </c>
       <c r="R88" t="n">
-        <v>6866743</v>
+        <v>6866668</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9206,10 +9206,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128389351</v>
+        <v>128389901</v>
       </c>
       <c r="B89" t="n">
-        <v>78055</v>
+        <v>79083</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9217,21 +9217,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471215</v>
+        <v>471209</v>
       </c>
       <c r="R89" t="n">
-        <v>6866634</v>
+        <v>6866743</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9303,32 +9303,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128388228</v>
+        <v>128389351</v>
       </c>
       <c r="B90" t="n">
-        <v>98571</v>
+        <v>78055</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>470788</v>
+        <v>471215</v>
       </c>
       <c r="R90" t="n">
-        <v>6866725</v>
+        <v>6866634</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128389587</v>
+        <v>128388173</v>
       </c>
       <c r="B92" t="n">
-        <v>80189</v>
+        <v>78749</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471274</v>
+        <v>470786</v>
       </c>
       <c r="R92" t="n">
-        <v>6866626</v>
+        <v>6866737</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128388173</v>
+        <v>128389587</v>
       </c>
       <c r="B93" t="n">
-        <v>78749</v>
+        <v>80189</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9629,10 +9629,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>470786</v>
+        <v>471274</v>
       </c>
       <c r="R93" t="n">
-        <v>6866737</v>
+        <v>6866626</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11049,10 +11049,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128502802</v>
+        <v>128502100</v>
       </c>
       <c r="B108" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11060,21 +11060,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471256</v>
+        <v>471347</v>
       </c>
       <c r="R108" t="n">
-        <v>6866728</v>
+        <v>6866584</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11146,10 +11146,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128502100</v>
+        <v>128502802</v>
       </c>
       <c r="B109" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11157,21 +11157,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11181,10 +11181,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471347</v>
+        <v>471256</v>
       </c>
       <c r="R109" t="n">
-        <v>6866584</v>
+        <v>6866728</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -4389,10 +4389,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374500</v>
+        <v>128376649</v>
       </c>
       <c r="B40" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4400,21 +4400,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471134</v>
+        <v>471300</v>
       </c>
       <c r="R40" t="n">
-        <v>6866834</v>
+        <v>6866735</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4486,7 +4486,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128376649</v>
+        <v>128375508</v>
       </c>
       <c r="B41" t="n">
         <v>79083</v>
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471300</v>
+        <v>471209</v>
       </c>
       <c r="R41" t="n">
-        <v>6866735</v>
+        <v>6866776</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4583,10 +4583,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128375508</v>
+        <v>128374500</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4594,21 +4594,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471209</v>
+        <v>471134</v>
       </c>
       <c r="R42" t="n">
-        <v>6866776</v>
+        <v>6866834</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128389855</v>
+        <v>128389511</v>
       </c>
       <c r="B61" t="n">
-        <v>57845</v>
+        <v>80188</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471241</v>
+        <v>471237</v>
       </c>
       <c r="R61" t="n">
-        <v>6866622</v>
+        <v>6866588</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6529,11 +6529,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6560,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128389262</v>
+        <v>128389329</v>
       </c>
       <c r="B62" t="n">
-        <v>80189</v>
+        <v>78840</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6571,21 +6566,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6595,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471168</v>
+        <v>471172</v>
       </c>
       <c r="R62" t="n">
-        <v>6866647</v>
+        <v>6866632</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6657,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128388778</v>
+        <v>128387227</v>
       </c>
       <c r="B63" t="n">
-        <v>79162</v>
+        <v>80188</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6668,21 +6663,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6692,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>470995</v>
+        <v>470551</v>
       </c>
       <c r="R63" t="n">
-        <v>6866711</v>
+        <v>6866892</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6754,7 +6749,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128389511</v>
+        <v>128387286</v>
       </c>
       <c r="B64" t="n">
         <v>80188</v>
@@ -6789,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471237</v>
+        <v>470551</v>
       </c>
       <c r="R64" t="n">
-        <v>6866588</v>
+        <v>6866872</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6851,10 +6846,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128389329</v>
+        <v>128389262</v>
       </c>
       <c r="B65" t="n">
-        <v>78840</v>
+        <v>80189</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6862,21 +6857,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6886,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471172</v>
+        <v>471168</v>
       </c>
       <c r="R65" t="n">
-        <v>6866632</v>
+        <v>6866647</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6948,10 +6943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128387227</v>
+        <v>128388778</v>
       </c>
       <c r="B66" t="n">
-        <v>80188</v>
+        <v>79162</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6959,21 +6954,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6983,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470551</v>
+        <v>470995</v>
       </c>
       <c r="R66" t="n">
-        <v>6866892</v>
+        <v>6866711</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7045,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128387286</v>
+        <v>128389855</v>
       </c>
       <c r="B67" t="n">
-        <v>80188</v>
+        <v>57845</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7056,21 +7051,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7080,13 +7075,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>470551</v>
+        <v>471241</v>
       </c>
       <c r="R67" t="n">
-        <v>6866872</v>
+        <v>6866622</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7116,6 +7111,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128388646</v>
+        <v>128388766</v>
       </c>
       <c r="B72" t="n">
-        <v>79115</v>
+        <v>79162</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470945</v>
+        <v>470981</v>
       </c>
       <c r="R72" t="n">
-        <v>6866709</v>
+        <v>6866714</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128388766</v>
+        <v>128388646</v>
       </c>
       <c r="B73" t="n">
-        <v>79162</v>
+        <v>79115</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7638,21 +7638,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470981</v>
+        <v>470945</v>
       </c>
       <c r="R73" t="n">
-        <v>6866714</v>
+        <v>6866709</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8121,10 +8121,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128389403</v>
+        <v>128388815</v>
       </c>
       <c r="B78" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8132,21 +8132,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471187</v>
+        <v>470992</v>
       </c>
       <c r="R78" t="n">
-        <v>6866586</v>
+        <v>6866696</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8218,7 +8218,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128388815</v>
+        <v>128389886</v>
       </c>
       <c r="B79" t="n">
         <v>79083</v>
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>470992</v>
+        <v>471211</v>
       </c>
       <c r="R79" t="n">
-        <v>6866696</v>
+        <v>6866717</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8315,7 +8315,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128389886</v>
+        <v>128388714</v>
       </c>
       <c r="B80" t="n">
         <v>79083</v>
@@ -8350,10 +8350,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471211</v>
+        <v>470987</v>
       </c>
       <c r="R80" t="n">
-        <v>6866717</v>
+        <v>6866714</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8412,45 +8412,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128388714</v>
+        <v>128388416</v>
       </c>
       <c r="B81" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>470987</v>
+        <v>470816</v>
       </c>
       <c r="R81" t="n">
-        <v>6866714</v>
+        <v>6866722</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8509,54 +8518,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128388416</v>
+        <v>128389403</v>
       </c>
       <c r="B82" t="n">
-        <v>98571</v>
+        <v>78841</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>470816</v>
+        <v>471187</v>
       </c>
       <c r="R82" t="n">
-        <v>6866722</v>
+        <v>6866586</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9885,10 +9885,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128502381</v>
+        <v>128502263</v>
       </c>
       <c r="B96" t="n">
-        <v>79115</v>
+        <v>79087</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9896,21 +9896,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9920,10 +9920,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471311</v>
+        <v>471328</v>
       </c>
       <c r="R96" t="n">
-        <v>6866616</v>
+        <v>6866612</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9982,10 +9982,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128502263</v>
+        <v>128502381</v>
       </c>
       <c r="B97" t="n">
-        <v>79083</v>
+        <v>79119</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9993,21 +9993,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471328</v>
+        <v>471311</v>
       </c>
       <c r="R97" t="n">
-        <v>6866612</v>
+        <v>6866616</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10082,7 +10082,7 @@
         <v>128501285</v>
       </c>
       <c r="B98" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>128501083</v>
       </c>
       <c r="B99" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10273,32 +10273,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128501140</v>
+        <v>128502704</v>
       </c>
       <c r="B100" t="n">
-        <v>79083</v>
+        <v>91423</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471253</v>
+        <v>471366</v>
       </c>
       <c r="R100" t="n">
-        <v>6866704</v>
+        <v>6866720</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10370,32 +10370,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128502704</v>
+        <v>128501140</v>
       </c>
       <c r="B101" t="n">
-        <v>91417</v>
+        <v>79087</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471366</v>
+        <v>471253</v>
       </c>
       <c r="R101" t="n">
-        <v>6866720</v>
+        <v>6866704</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10470,7 +10470,7 @@
         <v>128501794</v>
       </c>
       <c r="B102" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>128502548</v>
       </c>
       <c r="B103" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>128501127</v>
       </c>
       <c r="B104" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>128501181</v>
       </c>
       <c r="B105" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10855,10 +10855,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128501480</v>
+        <v>128501144</v>
       </c>
       <c r="B106" t="n">
-        <v>79115</v>
+        <v>78845</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10866,21 +10866,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10890,13 +10890,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471273</v>
+        <v>471257</v>
       </c>
       <c r="R106" t="n">
-        <v>6866589</v>
+        <v>6866697</v>
       </c>
       <c r="S106" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10952,10 +10952,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128501144</v>
+        <v>128501480</v>
       </c>
       <c r="B107" t="n">
-        <v>78841</v>
+        <v>79119</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10963,21 +10963,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471257</v>
+        <v>471273</v>
       </c>
       <c r="R107" t="n">
-        <v>6866697</v>
+        <v>6866589</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>128502100</v>
       </c>
       <c r="B108" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>128502802</v>
       </c>
       <c r="B109" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>128501209</v>
       </c>
       <c r="B110" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>128502866</v>
       </c>
       <c r="B111" t="n">
-        <v>98488</v>
+        <v>98496</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>128502259</v>
       </c>
       <c r="B112" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11534,10 +11534,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128502509</v>
+        <v>128501973</v>
       </c>
       <c r="B113" t="n">
-        <v>78840</v>
+        <v>79119</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11545,21 +11545,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471315</v>
+        <v>471363</v>
       </c>
       <c r="R113" t="n">
-        <v>6866670</v>
+        <v>6866544</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11631,10 +11631,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128501097</v>
+        <v>128502509</v>
       </c>
       <c r="B114" t="n">
-        <v>79083</v>
+        <v>78844</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11642,21 +11642,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471224</v>
+        <v>471315</v>
       </c>
       <c r="R114" t="n">
-        <v>6866707</v>
+        <v>6866670</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11728,10 +11728,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128501973</v>
+        <v>128501097</v>
       </c>
       <c r="B115" t="n">
-        <v>79115</v>
+        <v>79087</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11739,21 +11739,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11763,10 +11763,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471363</v>
+        <v>471224</v>
       </c>
       <c r="R115" t="n">
-        <v>6866544</v>
+        <v>6866707</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11828,7 +11828,7 @@
         <v>128502607</v>
       </c>
       <c r="B116" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>128501347</v>
       </c>
       <c r="B117" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>128501927</v>
       </c>
       <c r="B118" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>128501224</v>
       </c>
       <c r="B119" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>128502212</v>
       </c>
       <c r="B120" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>128502291</v>
       </c>
       <c r="B121" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>128502189</v>
       </c>
       <c r="B122" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>128501253</v>
       </c>
       <c r="B123" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>128502309</v>
       </c>
       <c r="B124" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>128502178</v>
       </c>
       <c r="B125" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128376373</v>
+        <v>128374470</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>78844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471330</v>
+        <v>471139</v>
       </c>
       <c r="R2" t="n">
-        <v>6866787</v>
+        <v>6866835</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128374470</v>
+        <v>128376618</v>
       </c>
       <c r="B3" t="n">
-        <v>78840</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471139</v>
+        <v>471331</v>
       </c>
       <c r="R3" t="n">
-        <v>6866835</v>
+        <v>6866715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128376618</v>
+        <v>128373928</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79119</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471331</v>
+        <v>471086</v>
       </c>
       <c r="R4" t="n">
-        <v>6866715</v>
+        <v>6866862</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373928</v>
+        <v>128375151</v>
       </c>
       <c r="B5" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471086</v>
+        <v>471135</v>
       </c>
       <c r="R5" t="n">
-        <v>6866862</v>
+        <v>6866819</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128375151</v>
+        <v>128376373</v>
       </c>
       <c r="B6" t="n">
-        <v>79115</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471135</v>
+        <v>471330</v>
       </c>
       <c r="R6" t="n">
-        <v>6866819</v>
+        <v>6866787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>128374420</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128375924</v>
       </c>
       <c r="B8" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128376197</v>
+        <v>128376258</v>
       </c>
       <c r="B9" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471280</v>
+        <v>471292</v>
       </c>
       <c r="R9" t="n">
-        <v>6866807</v>
+        <v>6866805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128376258</v>
+        <v>128375168</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471292</v>
+        <v>471139</v>
       </c>
       <c r="R10" t="n">
-        <v>6866805</v>
+        <v>6866821</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128375168</v>
+        <v>128375190</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471139</v>
+        <v>471145</v>
       </c>
       <c r="R11" t="n">
-        <v>6866821</v>
+        <v>6866802</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128375190</v>
+        <v>128376197</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>78845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471145</v>
+        <v>471280</v>
       </c>
       <c r="R12" t="n">
-        <v>6866802</v>
+        <v>6866807</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,7 +1754,7 @@
         <v>128374859</v>
       </c>
       <c r="B13" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>128376676</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128375275</v>
+        <v>128375734</v>
       </c>
       <c r="B15" t="n">
-        <v>79115</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471162</v>
+        <v>471234</v>
       </c>
       <c r="R15" t="n">
-        <v>6866793</v>
+        <v>6866765</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128375734</v>
+        <v>128374662</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471234</v>
+        <v>471145</v>
       </c>
       <c r="R16" t="n">
-        <v>6866765</v>
+        <v>6866824</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128374662</v>
+        <v>128376712</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>79677</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471145</v>
+        <v>471282</v>
       </c>
       <c r="R17" t="n">
-        <v>6866824</v>
+        <v>6866780</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128376712</v>
+        <v>128375275</v>
       </c>
       <c r="B18" t="n">
-        <v>79673</v>
+        <v>79119</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471282</v>
+        <v>471162</v>
       </c>
       <c r="R18" t="n">
-        <v>6866780</v>
+        <v>6866793</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2336,7 +2336,7 @@
         <v>128375989</v>
       </c>
       <c r="B19" t="n">
-        <v>78055</v>
+        <v>78059</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128375959</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128375214</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128375358</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128375758</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>128376206</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128374452</v>
       </c>
       <c r="B25" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128375464</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128375560</v>
       </c>
       <c r="B27" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>128376736</v>
       </c>
       <c r="B28" t="n">
-        <v>78055</v>
+        <v>78059</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128376636</v>
+        <v>128376702</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>78490</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,21 +3319,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,13 +3343,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471320</v>
+        <v>471287</v>
       </c>
       <c r="R29" t="n">
-        <v>6866734</v>
+        <v>6866773</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128376702</v>
+        <v>128376574</v>
       </c>
       <c r="B30" t="n">
-        <v>78486</v>
+        <v>78845</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471287</v>
+        <v>471364</v>
       </c>
       <c r="R30" t="n">
-        <v>6866773</v>
+        <v>6866709</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374116</v>
+        <v>128376636</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471107</v>
+        <v>471320</v>
       </c>
       <c r="R31" t="n">
-        <v>6866853</v>
+        <v>6866734</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128376574</v>
+        <v>128374116</v>
       </c>
       <c r="B32" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471364</v>
+        <v>471107</v>
       </c>
       <c r="R32" t="n">
-        <v>6866709</v>
+        <v>6866853</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128375289</v>
+        <v>128375249</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471165</v>
+        <v>471158</v>
       </c>
       <c r="R33" t="n">
-        <v>6866794</v>
+        <v>6866800</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128375249</v>
+        <v>128375289</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471158</v>
+        <v>471165</v>
       </c>
       <c r="R34" t="n">
-        <v>6866800</v>
+        <v>6866794</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,7 +3893,7 @@
         <v>128375794</v>
       </c>
       <c r="B35" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>128374814</v>
       </c>
       <c r="B36" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>128376382</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>128373989</v>
       </c>
       <c r="B38" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>128374436</v>
       </c>
       <c r="B39" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>128376649</v>
       </c>
       <c r="B40" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>128375508</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>128374500</v>
       </c>
       <c r="B42" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4680,54 +4680,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128376462</v>
+        <v>128375808</v>
       </c>
       <c r="B43" t="n">
-        <v>92026</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471351</v>
+        <v>471247</v>
       </c>
       <c r="R43" t="n">
-        <v>6866748</v>
+        <v>6866787</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4760,11 +4751,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4791,10 +4777,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128375808</v>
+        <v>128375498</v>
       </c>
       <c r="B44" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4826,10 +4812,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471247</v>
+        <v>471198</v>
       </c>
       <c r="R44" t="n">
-        <v>6866787</v>
+        <v>6866776</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4888,45 +4874,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128375498</v>
+        <v>128376462</v>
       </c>
       <c r="B45" t="n">
-        <v>79083</v>
+        <v>92038</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471198</v>
+        <v>471351</v>
       </c>
       <c r="R45" t="n">
-        <v>6866776</v>
+        <v>6866748</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4959,6 +4954,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4988,7 +4988,7 @@
         <v>128375307</v>
       </c>
       <c r="B46" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>128376295</v>
       </c>
       <c r="B47" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>128375399</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>128388207</v>
       </c>
       <c r="B49" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>128387779</v>
       </c>
       <c r="B50" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>128388103</v>
       </c>
       <c r="B51" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>128387977</v>
       </c>
       <c r="B52" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>128389894</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>128389953</v>
       </c>
       <c r="B54" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>128387790</v>
       </c>
       <c r="B55" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>128387828</v>
       </c>
       <c r="B56" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>128388996</v>
       </c>
       <c r="B57" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>128388496</v>
       </c>
       <c r="B58" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>128389324</v>
       </c>
       <c r="B59" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>128387936</v>
       </c>
       <c r="B60" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128389511</v>
+        <v>128389262</v>
       </c>
       <c r="B61" t="n">
-        <v>80188</v>
+        <v>80193</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,10 +6493,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471237</v>
+        <v>471168</v>
       </c>
       <c r="R61" t="n">
-        <v>6866588</v>
+        <v>6866647</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128389329</v>
+        <v>128389511</v>
       </c>
       <c r="B62" t="n">
-        <v>78840</v>
+        <v>80192</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6566,21 +6566,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471172</v>
+        <v>471237</v>
       </c>
       <c r="R62" t="n">
-        <v>6866632</v>
+        <v>6866588</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128387227</v>
+        <v>128389329</v>
       </c>
       <c r="B63" t="n">
-        <v>80188</v>
+        <v>78844</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6663,21 +6663,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>470551</v>
+        <v>471172</v>
       </c>
       <c r="R63" t="n">
-        <v>6866892</v>
+        <v>6866632</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128387286</v>
+        <v>128387227</v>
       </c>
       <c r="B64" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>470551</v>
       </c>
       <c r="R64" t="n">
-        <v>6866872</v>
+        <v>6866892</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128389262</v>
+        <v>128387286</v>
       </c>
       <c r="B65" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471168</v>
+        <v>470551</v>
       </c>
       <c r="R65" t="n">
-        <v>6866647</v>
+        <v>6866872</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128388778</v>
+        <v>128389855</v>
       </c>
       <c r="B66" t="n">
-        <v>79162</v>
+        <v>57849</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,21 +6954,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>864</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470995</v>
+        <v>471241</v>
       </c>
       <c r="R66" t="n">
-        <v>6866711</v>
+        <v>6866622</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7014,6 +7014,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7040,10 +7045,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128389855</v>
+        <v>128388778</v>
       </c>
       <c r="B67" t="n">
-        <v>57845</v>
+        <v>79166</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,21 +7056,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,13 +7080,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471241</v>
+        <v>470995</v>
       </c>
       <c r="R67" t="n">
-        <v>6866622</v>
+        <v>6866711</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7111,11 +7116,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7142,10 +7142,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128389069</v>
+        <v>128389187</v>
       </c>
       <c r="B68" t="n">
-        <v>80188</v>
+        <v>78844</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471158</v>
+        <v>471196</v>
       </c>
       <c r="R68" t="n">
-        <v>6866734</v>
+        <v>6866706</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128389187</v>
+        <v>128389227</v>
       </c>
       <c r="B69" t="n">
-        <v>78840</v>
+        <v>79119</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,10 +7274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471196</v>
+        <v>471156</v>
       </c>
       <c r="R69" t="n">
-        <v>6866706</v>
+        <v>6866665</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7336,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128389227</v>
+        <v>128388804</v>
       </c>
       <c r="B70" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471156</v>
+        <v>470987</v>
       </c>
       <c r="R70" t="n">
-        <v>6866665</v>
+        <v>6866706</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128388804</v>
+        <v>128389069</v>
       </c>
       <c r="B71" t="n">
-        <v>79115</v>
+        <v>80192</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>470987</v>
+        <v>471158</v>
       </c>
       <c r="R71" t="n">
-        <v>6866706</v>
+        <v>6866734</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128388766</v>
+        <v>128389641</v>
       </c>
       <c r="B72" t="n">
-        <v>79162</v>
+        <v>80192</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470981</v>
+        <v>471241</v>
       </c>
       <c r="R72" t="n">
-        <v>6866714</v>
+        <v>6866656</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7630,7 +7630,7 @@
         <v>128388646</v>
       </c>
       <c r="B73" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7724,10 +7724,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128389641</v>
+        <v>128388766</v>
       </c>
       <c r="B74" t="n">
-        <v>80188</v>
+        <v>79166</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471241</v>
+        <v>470981</v>
       </c>
       <c r="R74" t="n">
-        <v>6866656</v>
+        <v>6866714</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7824,7 +7824,7 @@
         <v>128387695</v>
       </c>
       <c r="B75" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>128388053</v>
       </c>
       <c r="B76" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>128387629</v>
       </c>
       <c r="B77" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>128388815</v>
       </c>
       <c r="B78" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>128389886</v>
       </c>
       <c r="B79" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>128388714</v>
       </c>
       <c r="B80" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>128388416</v>
       </c>
       <c r="B81" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>128389403</v>
       </c>
       <c r="B82" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>128387736</v>
       </c>
       <c r="B83" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>128389124</v>
       </c>
       <c r="B84" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>128387659</v>
       </c>
       <c r="B85" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>128387292</v>
       </c>
       <c r="B86" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>128388228</v>
       </c>
       <c r="B87" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>128389213</v>
       </c>
       <c r="B88" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>128389901</v>
       </c>
       <c r="B89" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>128389351</v>
       </c>
       <c r="B90" t="n">
-        <v>78055</v>
+        <v>78059</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>128388690</v>
       </c>
       <c r="B91" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128388173</v>
+        <v>128389587</v>
       </c>
       <c r="B92" t="n">
-        <v>78749</v>
+        <v>80193</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>470786</v>
+        <v>471274</v>
       </c>
       <c r="R92" t="n">
-        <v>6866737</v>
+        <v>6866626</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128389587</v>
+        <v>128389918</v>
       </c>
       <c r="B93" t="n">
-        <v>80189</v>
+        <v>79087</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471274</v>
+        <v>471210</v>
       </c>
       <c r="R93" t="n">
-        <v>6866626</v>
+        <v>6866755</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9691,10 +9691,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128389918</v>
+        <v>128388173</v>
       </c>
       <c r="B94" t="n">
-        <v>79083</v>
+        <v>78753</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9702,21 +9702,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9726,13 +9726,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471210</v>
+        <v>470786</v>
       </c>
       <c r="R94" t="n">
-        <v>6866755</v>
+        <v>6866737</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>128389286</v>
       </c>
       <c r="B95" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9885,10 +9885,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128502263</v>
+        <v>128502381</v>
       </c>
       <c r="B96" t="n">
-        <v>79087</v>
+        <v>79119</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9896,21 +9896,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9920,10 +9920,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471328</v>
+        <v>471311</v>
       </c>
       <c r="R96" t="n">
-        <v>6866612</v>
+        <v>6866616</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9982,10 +9982,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128502381</v>
+        <v>128502263</v>
       </c>
       <c r="B97" t="n">
-        <v>79119</v>
+        <v>79087</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9993,21 +9993,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471311</v>
+        <v>471328</v>
       </c>
       <c r="R97" t="n">
-        <v>6866616</v>
+        <v>6866612</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10276,7 +10276,7 @@
         <v>128502704</v>
       </c>
       <c r="B100" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10855,10 +10855,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128501144</v>
+        <v>128501480</v>
       </c>
       <c r="B106" t="n">
-        <v>78845</v>
+        <v>79119</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10866,21 +10866,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10890,13 +10890,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471257</v>
+        <v>471273</v>
       </c>
       <c r="R106" t="n">
-        <v>6866697</v>
+        <v>6866589</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10952,10 +10952,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128501480</v>
+        <v>128501144</v>
       </c>
       <c r="B107" t="n">
-        <v>79119</v>
+        <v>78845</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10963,21 +10963,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471273</v>
+        <v>471257</v>
       </c>
       <c r="R107" t="n">
-        <v>6866589</v>
+        <v>6866697</v>
       </c>
       <c r="S107" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11049,32 +11049,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128502100</v>
+        <v>128502866</v>
       </c>
       <c r="B108" t="n">
-        <v>79119</v>
+        <v>98502</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471347</v>
+        <v>471139</v>
       </c>
       <c r="R108" t="n">
-        <v>6866584</v>
+        <v>6866727</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11146,10 +11146,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128502802</v>
+        <v>128502100</v>
       </c>
       <c r="B109" t="n">
-        <v>79087</v>
+        <v>79119</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11157,21 +11157,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11181,10 +11181,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471256</v>
+        <v>471347</v>
       </c>
       <c r="R109" t="n">
-        <v>6866728</v>
+        <v>6866584</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11243,10 +11243,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128501209</v>
+        <v>128502802</v>
       </c>
       <c r="B110" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11254,21 +11254,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471244</v>
+        <v>471256</v>
       </c>
       <c r="R110" t="n">
-        <v>6866687</v>
+        <v>6866728</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11340,32 +11340,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128502866</v>
+        <v>128501209</v>
       </c>
       <c r="B111" t="n">
-        <v>98496</v>
+        <v>78844</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11375,10 +11375,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471139</v>
+        <v>471244</v>
       </c>
       <c r="R111" t="n">
-        <v>6866727</v>
+        <v>6866687</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11534,10 +11534,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128501973</v>
+        <v>128501097</v>
       </c>
       <c r="B113" t="n">
-        <v>79119</v>
+        <v>79087</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11545,21 +11545,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471363</v>
+        <v>471224</v>
       </c>
       <c r="R113" t="n">
-        <v>6866544</v>
+        <v>6866707</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11631,10 +11631,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128502509</v>
+        <v>128501973</v>
       </c>
       <c r="B114" t="n">
-        <v>78844</v>
+        <v>79119</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11642,21 +11642,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471315</v>
+        <v>471363</v>
       </c>
       <c r="R114" t="n">
-        <v>6866670</v>
+        <v>6866544</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11728,10 +11728,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128501097</v>
+        <v>128502509</v>
       </c>
       <c r="B115" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11739,21 +11739,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11763,10 +11763,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471224</v>
+        <v>471315</v>
       </c>
       <c r="R115" t="n">
-        <v>6866707</v>
+        <v>6866670</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -1363,7 +1363,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128376258</v>
+        <v>128375168</v>
       </c>
       <c r="B9" t="n">
         <v>79087</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471292</v>
+        <v>471139</v>
       </c>
       <c r="R9" t="n">
-        <v>6866805</v>
+        <v>6866821</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128375168</v>
+        <v>128375190</v>
       </c>
       <c r="B10" t="n">
         <v>79087</v>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471139</v>
+        <v>471145</v>
       </c>
       <c r="R10" t="n">
-        <v>6866821</v>
+        <v>6866802</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128375190</v>
+        <v>128376258</v>
       </c>
       <c r="B11" t="n">
         <v>79087</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471145</v>
+        <v>471292</v>
       </c>
       <c r="R11" t="n">
-        <v>6866802</v>
+        <v>6866805</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128375734</v>
+        <v>128375275</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79119</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471234</v>
+        <v>471162</v>
       </c>
       <c r="R15" t="n">
-        <v>6866765</v>
+        <v>6866793</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128374662</v>
+        <v>128376712</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471145</v>
+        <v>471282</v>
       </c>
       <c r="R16" t="n">
-        <v>6866824</v>
+        <v>6866780</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128376712</v>
+        <v>128375734</v>
       </c>
       <c r="B17" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471282</v>
+        <v>471234</v>
       </c>
       <c r="R17" t="n">
-        <v>6866780</v>
+        <v>6866765</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128375275</v>
+        <v>128374662</v>
       </c>
       <c r="B18" t="n">
-        <v>79119</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471162</v>
+        <v>471145</v>
       </c>
       <c r="R18" t="n">
-        <v>6866793</v>
+        <v>6866824</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3696,7 +3696,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128375249</v>
+        <v>128375289</v>
       </c>
       <c r="B33" t="n">
         <v>79087</v>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471158</v>
+        <v>471165</v>
       </c>
       <c r="R33" t="n">
-        <v>6866800</v>
+        <v>6866794</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128375289</v>
+        <v>128375249</v>
       </c>
       <c r="B34" t="n">
         <v>79087</v>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471165</v>
+        <v>471158</v>
       </c>
       <c r="R34" t="n">
-        <v>6866794</v>
+        <v>6866800</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128389262</v>
+        <v>128389511</v>
       </c>
       <c r="B61" t="n">
-        <v>80193</v>
+        <v>80192</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,10 +6493,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471168</v>
+        <v>471237</v>
       </c>
       <c r="R61" t="n">
-        <v>6866647</v>
+        <v>6866588</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128389511</v>
+        <v>128389329</v>
       </c>
       <c r="B62" t="n">
-        <v>80192</v>
+        <v>78844</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6566,21 +6566,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471237</v>
+        <v>471172</v>
       </c>
       <c r="R62" t="n">
-        <v>6866588</v>
+        <v>6866632</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128389329</v>
+        <v>128387227</v>
       </c>
       <c r="B63" t="n">
-        <v>78844</v>
+        <v>80192</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6663,21 +6663,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471172</v>
+        <v>470551</v>
       </c>
       <c r="R63" t="n">
-        <v>6866632</v>
+        <v>6866892</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,7 +6749,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128387227</v>
+        <v>128387286</v>
       </c>
       <c r="B64" t="n">
         <v>80192</v>
@@ -6787,7 +6787,7 @@
         <v>470551</v>
       </c>
       <c r="R64" t="n">
-        <v>6866892</v>
+        <v>6866872</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128387286</v>
+        <v>128388778</v>
       </c>
       <c r="B65" t="n">
-        <v>80192</v>
+        <v>79166</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>470551</v>
+        <v>470995</v>
       </c>
       <c r="R65" t="n">
-        <v>6866872</v>
+        <v>6866711</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7045,10 +7045,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128388778</v>
+        <v>128389262</v>
       </c>
       <c r="B67" t="n">
-        <v>79166</v>
+        <v>80193</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7056,21 +7056,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7080,10 +7080,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>470995</v>
+        <v>471168</v>
       </c>
       <c r="R67" t="n">
-        <v>6866711</v>
+        <v>6866647</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7142,10 +7142,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128389187</v>
+        <v>128389069</v>
       </c>
       <c r="B68" t="n">
-        <v>78844</v>
+        <v>80192</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471196</v>
+        <v>471158</v>
       </c>
       <c r="R68" t="n">
-        <v>6866706</v>
+        <v>6866734</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128389227</v>
+        <v>128389187</v>
       </c>
       <c r="B69" t="n">
-        <v>79119</v>
+        <v>78844</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,10 +7274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471156</v>
+        <v>471196</v>
       </c>
       <c r="R69" t="n">
-        <v>6866665</v>
+        <v>6866706</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7336,7 +7336,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128388804</v>
+        <v>128389227</v>
       </c>
       <c r="B70" t="n">
         <v>79119</v>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>470987</v>
+        <v>471156</v>
       </c>
       <c r="R70" t="n">
-        <v>6866706</v>
+        <v>6866665</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128389069</v>
+        <v>128388804</v>
       </c>
       <c r="B71" t="n">
-        <v>80192</v>
+        <v>79119</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471158</v>
+        <v>470987</v>
       </c>
       <c r="R71" t="n">
-        <v>6866734</v>
+        <v>6866706</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128388228</v>
+        <v>128389213</v>
       </c>
       <c r="B87" t="n">
-        <v>98585</v>
+        <v>80192</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>470788</v>
+        <v>471148</v>
       </c>
       <c r="R87" t="n">
-        <v>6866725</v>
+        <v>6866668</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128389213</v>
+        <v>128389901</v>
       </c>
       <c r="B88" t="n">
-        <v>80192</v>
+        <v>79087</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471148</v>
+        <v>471209</v>
       </c>
       <c r="R88" t="n">
-        <v>6866668</v>
+        <v>6866743</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9206,10 +9206,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128389901</v>
+        <v>128389351</v>
       </c>
       <c r="B89" t="n">
-        <v>79087</v>
+        <v>78059</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9217,21 +9217,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471209</v>
+        <v>471215</v>
       </c>
       <c r="R89" t="n">
-        <v>6866743</v>
+        <v>6866634</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9303,32 +9303,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128389351</v>
+        <v>128388228</v>
       </c>
       <c r="B90" t="n">
-        <v>78059</v>
+        <v>98585</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471215</v>
+        <v>470788</v>
       </c>
       <c r="R90" t="n">
-        <v>6866634</v>
+        <v>6866725</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11049,32 +11049,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128502866</v>
+        <v>128502100</v>
       </c>
       <c r="B108" t="n">
-        <v>98502</v>
+        <v>79119</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471139</v>
+        <v>471347</v>
       </c>
       <c r="R108" t="n">
-        <v>6866727</v>
+        <v>6866584</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11146,10 +11146,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128502100</v>
+        <v>128501209</v>
       </c>
       <c r="B109" t="n">
-        <v>79119</v>
+        <v>78844</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11157,21 +11157,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11181,10 +11181,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471347</v>
+        <v>471244</v>
       </c>
       <c r="R109" t="n">
-        <v>6866584</v>
+        <v>6866687</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11243,32 +11243,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128502802</v>
+        <v>128502866</v>
       </c>
       <c r="B110" t="n">
-        <v>79087</v>
+        <v>98502</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471256</v>
+        <v>471139</v>
       </c>
       <c r="R110" t="n">
-        <v>6866728</v>
+        <v>6866727</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11340,10 +11340,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128501209</v>
+        <v>128502802</v>
       </c>
       <c r="B111" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11351,21 +11351,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11375,10 +11375,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471244</v>
+        <v>471256</v>
       </c>
       <c r="R111" t="n">
-        <v>6866687</v>
+        <v>6866728</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11534,10 +11534,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128501097</v>
+        <v>128501973</v>
       </c>
       <c r="B113" t="n">
-        <v>79087</v>
+        <v>79119</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11545,21 +11545,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471224</v>
+        <v>471363</v>
       </c>
       <c r="R113" t="n">
-        <v>6866707</v>
+        <v>6866544</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11631,10 +11631,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128501973</v>
+        <v>128501097</v>
       </c>
       <c r="B114" t="n">
-        <v>79119</v>
+        <v>79087</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11642,21 +11642,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471363</v>
+        <v>471224</v>
       </c>
       <c r="R114" t="n">
-        <v>6866544</v>
+        <v>6866707</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12504,10 +12504,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128501253</v>
+        <v>128502309</v>
       </c>
       <c r="B123" t="n">
-        <v>79119</v>
+        <v>78845</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12515,21 +12515,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12539,10 +12539,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471267</v>
+        <v>471311</v>
       </c>
       <c r="R123" t="n">
-        <v>6866658</v>
+        <v>6866598</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12601,10 +12601,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128502309</v>
+        <v>128501253</v>
       </c>
       <c r="B124" t="n">
-        <v>78845</v>
+        <v>79119</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12612,21 +12612,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>471311</v>
+        <v>471267</v>
       </c>
       <c r="R124" t="n">
-        <v>6866598</v>
+        <v>6866658</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128374470</v>
+        <v>128373928</v>
       </c>
       <c r="B2" t="n">
-        <v>78844</v>
+        <v>79121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471139</v>
+        <v>471086</v>
       </c>
       <c r="R2" t="n">
-        <v>6866835</v>
+        <v>6866862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128376618</v>
+        <v>128375151</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471331</v>
+        <v>471135</v>
       </c>
       <c r="R3" t="n">
-        <v>6866715</v>
+        <v>6866819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128373928</v>
+        <v>128376373</v>
       </c>
       <c r="B4" t="n">
-        <v>79119</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471086</v>
+        <v>471330</v>
       </c>
       <c r="R4" t="n">
-        <v>6866862</v>
+        <v>6866787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128375151</v>
+        <v>128374470</v>
       </c>
       <c r="B5" t="n">
-        <v>79119</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471135</v>
+        <v>471139</v>
       </c>
       <c r="R5" t="n">
-        <v>6866819</v>
+        <v>6866835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128376373</v>
+        <v>128376618</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471330</v>
+        <v>471331</v>
       </c>
       <c r="R6" t="n">
-        <v>6866787</v>
+        <v>6866715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>128374420</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128375924</v>
       </c>
       <c r="B8" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128375168</v>
+        <v>128376197</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>78847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471139</v>
+        <v>471280</v>
       </c>
       <c r="R9" t="n">
-        <v>6866821</v>
+        <v>6866807</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128375190</v>
+        <v>128376258</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471145</v>
+        <v>471292</v>
       </c>
       <c r="R10" t="n">
-        <v>6866802</v>
+        <v>6866805</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128376258</v>
+        <v>128375168</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471292</v>
+        <v>471139</v>
       </c>
       <c r="R11" t="n">
-        <v>6866805</v>
+        <v>6866821</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128376197</v>
+        <v>128375190</v>
       </c>
       <c r="B12" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471280</v>
+        <v>471145</v>
       </c>
       <c r="R12" t="n">
-        <v>6866807</v>
+        <v>6866802</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,7 +1754,7 @@
         <v>128374859</v>
       </c>
       <c r="B13" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>128376676</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>128375275</v>
       </c>
       <c r="B15" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128376712</v>
+        <v>128375734</v>
       </c>
       <c r="B16" t="n">
-        <v>79677</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471282</v>
+        <v>471234</v>
       </c>
       <c r="R16" t="n">
-        <v>6866780</v>
+        <v>6866765</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128375734</v>
+        <v>128374662</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471234</v>
+        <v>471145</v>
       </c>
       <c r="R17" t="n">
-        <v>6866765</v>
+        <v>6866824</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128374662</v>
+        <v>128376712</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79679</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471145</v>
+        <v>471282</v>
       </c>
       <c r="R18" t="n">
-        <v>6866824</v>
+        <v>6866780</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2336,7 +2336,7 @@
         <v>128375989</v>
       </c>
       <c r="B19" t="n">
-        <v>78059</v>
+        <v>78061</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128375959</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128375214</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128375358</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128375758</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>128376206</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128374452</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128375464</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128375560</v>
+        <v>128376736</v>
       </c>
       <c r="B27" t="n">
-        <v>57849</v>
+        <v>78061</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471219</v>
+        <v>471282</v>
       </c>
       <c r="R27" t="n">
-        <v>6866779</v>
+        <v>6866783</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3180,11 +3180,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3211,10 +3206,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128376736</v>
+        <v>128375560</v>
       </c>
       <c r="B28" t="n">
-        <v>78059</v>
+        <v>57849</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3217,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,13 +3241,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471282</v>
+        <v>471219</v>
       </c>
       <c r="R28" t="n">
-        <v>6866783</v>
+        <v>6866779</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3282,6 +3277,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128376702</v>
+        <v>128376636</v>
       </c>
       <c r="B29" t="n">
-        <v>78490</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,21 +3319,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,13 +3343,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471287</v>
+        <v>471320</v>
       </c>
       <c r="R29" t="n">
-        <v>6866773</v>
+        <v>6866734</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128376574</v>
+        <v>128376702</v>
       </c>
       <c r="B30" t="n">
-        <v>78845</v>
+        <v>78492</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471364</v>
+        <v>471287</v>
       </c>
       <c r="R30" t="n">
-        <v>6866709</v>
+        <v>6866773</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128376636</v>
+        <v>128374116</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471320</v>
+        <v>471107</v>
       </c>
       <c r="R31" t="n">
-        <v>6866734</v>
+        <v>6866853</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374116</v>
+        <v>128376574</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>78847</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471107</v>
+        <v>471364</v>
       </c>
       <c r="R32" t="n">
-        <v>6866853</v>
+        <v>6866709</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>128375289</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>128375249</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>128375794</v>
       </c>
       <c r="B35" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3987,10 +3987,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128374814</v>
+        <v>128376382</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471137</v>
+        <v>471342</v>
       </c>
       <c r="R36" t="n">
-        <v>6866828</v>
+        <v>6866780</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4058,11 +4058,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4089,10 +4084,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128376382</v>
+        <v>128373989</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>80194</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4100,21 +4095,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4124,10 +4119,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471342</v>
+        <v>471102</v>
       </c>
       <c r="R37" t="n">
-        <v>6866780</v>
+        <v>6866857</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4186,10 +4181,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373989</v>
+        <v>128374814</v>
       </c>
       <c r="B38" t="n">
-        <v>80192</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4197,21 +4192,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4221,10 +4216,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>471102</v>
+        <v>471137</v>
       </c>
       <c r="R38" t="n">
-        <v>6866857</v>
+        <v>6866828</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4257,6 +4252,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4286,7 +4286,7 @@
         <v>128374436</v>
       </c>
       <c r="B39" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>128376649</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>128375508</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>128374500</v>
       </c>
       <c r="B42" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4680,45 +4680,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128375808</v>
+        <v>128376462</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>92040</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471247</v>
+        <v>471351</v>
       </c>
       <c r="R43" t="n">
-        <v>6866787</v>
+        <v>6866748</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4751,6 +4760,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4777,10 +4791,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128375498</v>
+        <v>128375808</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4812,10 +4826,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471198</v>
+        <v>471247</v>
       </c>
       <c r="R44" t="n">
-        <v>6866776</v>
+        <v>6866787</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4874,54 +4888,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128376462</v>
+        <v>128375498</v>
       </c>
       <c r="B45" t="n">
-        <v>92038</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471351</v>
+        <v>471198</v>
       </c>
       <c r="R45" t="n">
-        <v>6866748</v>
+        <v>6866776</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4954,11 +4959,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4988,7 +4988,7 @@
         <v>128375307</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>128376295</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>128375399</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>128388207</v>
       </c>
       <c r="B49" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>128387779</v>
       </c>
       <c r="B50" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>128388103</v>
       </c>
       <c r="B51" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>128387977</v>
       </c>
       <c r="B52" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>128389894</v>
       </c>
       <c r="B53" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>128389953</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>128387790</v>
       </c>
       <c r="B55" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>128387828</v>
       </c>
       <c r="B56" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>128388996</v>
       </c>
       <c r="B57" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>128388496</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>128389324</v>
       </c>
       <c r="B59" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>128387936</v>
       </c>
       <c r="B60" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128389511</v>
+        <v>128388778</v>
       </c>
       <c r="B61" t="n">
-        <v>80192</v>
+        <v>79168</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,10 +6493,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471237</v>
+        <v>470995</v>
       </c>
       <c r="R61" t="n">
-        <v>6866588</v>
+        <v>6866711</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128389329</v>
+        <v>128389262</v>
       </c>
       <c r="B62" t="n">
-        <v>78844</v>
+        <v>80195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6566,21 +6566,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471172</v>
+        <v>471168</v>
       </c>
       <c r="R62" t="n">
-        <v>6866632</v>
+        <v>6866647</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128387227</v>
+        <v>128389511</v>
       </c>
       <c r="B63" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>470551</v>
+        <v>471237</v>
       </c>
       <c r="R63" t="n">
-        <v>6866892</v>
+        <v>6866588</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128387286</v>
+        <v>128389329</v>
       </c>
       <c r="B64" t="n">
-        <v>80192</v>
+        <v>78846</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>470551</v>
+        <v>471172</v>
       </c>
       <c r="R64" t="n">
-        <v>6866872</v>
+        <v>6866632</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128388778</v>
+        <v>128387227</v>
       </c>
       <c r="B65" t="n">
-        <v>79166</v>
+        <v>80194</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>470995</v>
+        <v>470551</v>
       </c>
       <c r="R65" t="n">
-        <v>6866711</v>
+        <v>6866892</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128389855</v>
+        <v>128387286</v>
       </c>
       <c r="B66" t="n">
-        <v>57849</v>
+        <v>80194</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,21 +6954,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>471241</v>
+        <v>470551</v>
       </c>
       <c r="R66" t="n">
-        <v>6866622</v>
+        <v>6866872</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7014,11 +7014,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7045,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128389262</v>
+        <v>128389855</v>
       </c>
       <c r="B67" t="n">
-        <v>80193</v>
+        <v>57849</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7056,21 +7051,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7080,13 +7075,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471168</v>
+        <v>471241</v>
       </c>
       <c r="R67" t="n">
-        <v>6866647</v>
+        <v>6866622</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7116,6 +7111,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7142,10 +7142,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128389069</v>
+        <v>128389227</v>
       </c>
       <c r="B68" t="n">
-        <v>80192</v>
+        <v>79121</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471158</v>
+        <v>471156</v>
       </c>
       <c r="R68" t="n">
-        <v>6866734</v>
+        <v>6866665</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128389187</v>
+        <v>128388804</v>
       </c>
       <c r="B69" t="n">
-        <v>78844</v>
+        <v>79121</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471196</v>
+        <v>470987</v>
       </c>
       <c r="R69" t="n">
         <v>6866706</v>
@@ -7336,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128389227</v>
+        <v>128389069</v>
       </c>
       <c r="B70" t="n">
-        <v>79119</v>
+        <v>80194</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7347,21 +7347,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471156</v>
+        <v>471158</v>
       </c>
       <c r="R70" t="n">
-        <v>6866665</v>
+        <v>6866734</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128388804</v>
+        <v>128389187</v>
       </c>
       <c r="B71" t="n">
-        <v>79119</v>
+        <v>78846</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>470987</v>
+        <v>471196</v>
       </c>
       <c r="R71" t="n">
         <v>6866706</v>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128389641</v>
+        <v>128388766</v>
       </c>
       <c r="B72" t="n">
-        <v>80192</v>
+        <v>79168</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471241</v>
+        <v>470981</v>
       </c>
       <c r="R72" t="n">
-        <v>6866656</v>
+        <v>6866714</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7630,7 +7630,7 @@
         <v>128388646</v>
       </c>
       <c r="B73" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7724,10 +7724,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128388766</v>
+        <v>128389641</v>
       </c>
       <c r="B74" t="n">
-        <v>79166</v>
+        <v>80194</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>470981</v>
+        <v>471241</v>
       </c>
       <c r="R74" t="n">
-        <v>6866714</v>
+        <v>6866656</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7824,7 +7824,7 @@
         <v>128387695</v>
       </c>
       <c r="B75" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>128388053</v>
       </c>
       <c r="B76" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>128387629</v>
       </c>
       <c r="B77" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8121,45 +8121,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128388815</v>
+        <v>128388416</v>
       </c>
       <c r="B78" t="n">
-        <v>79087</v>
+        <v>98588</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470992</v>
+        <v>470816</v>
       </c>
       <c r="R78" t="n">
-        <v>6866696</v>
+        <v>6866722</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8218,10 +8227,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128389886</v>
+        <v>128388815</v>
       </c>
       <c r="B79" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8253,10 +8262,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471211</v>
+        <v>470992</v>
       </c>
       <c r="R79" t="n">
-        <v>6866717</v>
+        <v>6866696</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8315,10 +8324,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128388714</v>
+        <v>128389886</v>
       </c>
       <c r="B80" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8350,10 +8359,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>470987</v>
+        <v>471211</v>
       </c>
       <c r="R80" t="n">
-        <v>6866714</v>
+        <v>6866717</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8412,54 +8421,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128388416</v>
+        <v>128388714</v>
       </c>
       <c r="B81" t="n">
-        <v>98585</v>
+        <v>79089</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>470816</v>
+        <v>470987</v>
       </c>
       <c r="R81" t="n">
-        <v>6866722</v>
+        <v>6866714</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8521,7 +8521,7 @@
         <v>128389403</v>
       </c>
       <c r="B82" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>128387736</v>
       </c>
       <c r="B83" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>128389124</v>
       </c>
       <c r="B84" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>128387659</v>
       </c>
       <c r="B85" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>128387292</v>
       </c>
       <c r="B86" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>128389213</v>
       </c>
       <c r="B87" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>128389901</v>
       </c>
       <c r="B88" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>128389351</v>
       </c>
       <c r="B89" t="n">
-        <v>78059</v>
+        <v>78061</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>128388228</v>
       </c>
       <c r="B90" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>128388690</v>
       </c>
       <c r="B91" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128389587</v>
+        <v>128388173</v>
       </c>
       <c r="B92" t="n">
-        <v>80193</v>
+        <v>78755</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471274</v>
+        <v>470786</v>
       </c>
       <c r="R92" t="n">
-        <v>6866626</v>
+        <v>6866737</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128389918</v>
+        <v>128389587</v>
       </c>
       <c r="B93" t="n">
-        <v>79087</v>
+        <v>80195</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471210</v>
+        <v>471274</v>
       </c>
       <c r="R93" t="n">
-        <v>6866755</v>
+        <v>6866626</v>
       </c>
       <c r="S93" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9691,10 +9691,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128388173</v>
+        <v>128389918</v>
       </c>
       <c r="B94" t="n">
-        <v>78753</v>
+        <v>79089</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9702,21 +9702,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9726,13 +9726,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>470786</v>
+        <v>471210</v>
       </c>
       <c r="R94" t="n">
-        <v>6866737</v>
+        <v>6866755</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>128389286</v>
       </c>
       <c r="B95" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>128502381</v>
       </c>
       <c r="B96" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>128502263</v>
       </c>
       <c r="B97" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>128501285</v>
       </c>
       <c r="B98" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>128501083</v>
       </c>
       <c r="B99" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>128502704</v>
       </c>
       <c r="B100" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>128501140</v>
       </c>
       <c r="B101" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>128501794</v>
       </c>
       <c r="B102" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>128502548</v>
       </c>
       <c r="B103" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>128501127</v>
       </c>
       <c r="B104" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>128501181</v>
       </c>
       <c r="B105" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>128501480</v>
       </c>
       <c r="B106" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>128501144</v>
       </c>
       <c r="B107" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11049,32 +11049,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128502100</v>
+        <v>128502866</v>
       </c>
       <c r="B108" t="n">
-        <v>79119</v>
+        <v>98505</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471347</v>
+        <v>471139</v>
       </c>
       <c r="R108" t="n">
-        <v>6866584</v>
+        <v>6866727</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11146,10 +11146,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128501209</v>
+        <v>128502100</v>
       </c>
       <c r="B109" t="n">
-        <v>78844</v>
+        <v>79121</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11157,21 +11157,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11181,10 +11181,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471244</v>
+        <v>471347</v>
       </c>
       <c r="R109" t="n">
-        <v>6866687</v>
+        <v>6866584</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11243,32 +11243,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128502866</v>
+        <v>128502802</v>
       </c>
       <c r="B110" t="n">
-        <v>98502</v>
+        <v>79089</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471139</v>
+        <v>471256</v>
       </c>
       <c r="R110" t="n">
-        <v>6866727</v>
+        <v>6866728</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11340,10 +11340,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128502802</v>
+        <v>128501209</v>
       </c>
       <c r="B111" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11351,21 +11351,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11375,10 +11375,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471256</v>
+        <v>471244</v>
       </c>
       <c r="R111" t="n">
-        <v>6866728</v>
+        <v>6866687</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11440,7 +11440,7 @@
         <v>128502259</v>
       </c>
       <c r="B112" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>128501973</v>
       </c>
       <c r="B113" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11631,10 +11631,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128501097</v>
+        <v>128502607</v>
       </c>
       <c r="B114" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11642,21 +11642,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471224</v>
+        <v>471349</v>
       </c>
       <c r="R114" t="n">
-        <v>6866707</v>
+        <v>6866695</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11728,10 +11728,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128502509</v>
+        <v>128501347</v>
       </c>
       <c r="B115" t="n">
-        <v>78844</v>
+        <v>80194</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11739,21 +11739,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11763,10 +11763,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471315</v>
+        <v>471275</v>
       </c>
       <c r="R115" t="n">
-        <v>6866670</v>
+        <v>6866627</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128502607</v>
+        <v>128502509</v>
       </c>
       <c r="B116" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471349</v>
+        <v>471315</v>
       </c>
       <c r="R116" t="n">
-        <v>6866695</v>
+        <v>6866670</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11922,10 +11922,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128501347</v>
+        <v>128501097</v>
       </c>
       <c r="B117" t="n">
-        <v>80192</v>
+        <v>79089</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11933,21 +11933,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11957,10 +11957,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471275</v>
+        <v>471224</v>
       </c>
       <c r="R117" t="n">
-        <v>6866627</v>
+        <v>6866707</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12022,7 +12022,7 @@
         <v>128501927</v>
       </c>
       <c r="B118" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>128501224</v>
       </c>
       <c r="B119" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>128502212</v>
       </c>
       <c r="B120" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>128502291</v>
       </c>
       <c r="B121" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>128502189</v>
       </c>
       <c r="B122" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12504,10 +12504,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128502309</v>
+        <v>128501253</v>
       </c>
       <c r="B123" t="n">
-        <v>78845</v>
+        <v>79121</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12515,21 +12515,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12539,10 +12539,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471311</v>
+        <v>471267</v>
       </c>
       <c r="R123" t="n">
-        <v>6866598</v>
+        <v>6866658</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12601,10 +12601,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128501253</v>
+        <v>128502309</v>
       </c>
       <c r="B124" t="n">
-        <v>79119</v>
+        <v>78847</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12612,21 +12612,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>471267</v>
+        <v>471311</v>
       </c>
       <c r="R124" t="n">
-        <v>6866658</v>
+        <v>6866598</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12701,7 +12701,7 @@
         <v>128502178</v>
       </c>
       <c r="B125" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>128374420</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128376197</v>
+        <v>128376258</v>
       </c>
       <c r="B9" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471280</v>
+        <v>471292</v>
       </c>
       <c r="R9" t="n">
-        <v>6866807</v>
+        <v>6866805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128376258</v>
+        <v>128375168</v>
       </c>
       <c r="B10" t="n">
         <v>79089</v>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471292</v>
+        <v>471139</v>
       </c>
       <c r="R10" t="n">
-        <v>6866805</v>
+        <v>6866821</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128375168</v>
+        <v>128375190</v>
       </c>
       <c r="B11" t="n">
         <v>79089</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471139</v>
+        <v>471145</v>
       </c>
       <c r="R11" t="n">
-        <v>6866821</v>
+        <v>6866802</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128375190</v>
+        <v>128376197</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471145</v>
+        <v>471280</v>
       </c>
       <c r="R12" t="n">
-        <v>6866802</v>
+        <v>6866807</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128374859</v>
+        <v>128376676</v>
       </c>
       <c r="B13" t="n">
-        <v>80195</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471125</v>
+        <v>471287</v>
       </c>
       <c r="R13" t="n">
-        <v>6866815</v>
+        <v>6866763</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128376676</v>
+        <v>128374859</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>80195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471287</v>
+        <v>471125</v>
       </c>
       <c r="R14" t="n">
-        <v>6866763</v>
+        <v>6866815</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128375734</v>
+        <v>128376712</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79679</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471234</v>
+        <v>471282</v>
       </c>
       <c r="R16" t="n">
-        <v>6866765</v>
+        <v>6866780</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128374662</v>
+        <v>128375734</v>
       </c>
       <c r="B17" t="n">
         <v>79089</v>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471145</v>
+        <v>471234</v>
       </c>
       <c r="R17" t="n">
-        <v>6866824</v>
+        <v>6866765</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128376712</v>
+        <v>128374662</v>
       </c>
       <c r="B18" t="n">
-        <v>79679</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471282</v>
+        <v>471145</v>
       </c>
       <c r="R18" t="n">
-        <v>6866780</v>
+        <v>6866824</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3696,7 +3696,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128375289</v>
+        <v>128375249</v>
       </c>
       <c r="B33" t="n">
         <v>79089</v>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471165</v>
+        <v>471158</v>
       </c>
       <c r="R33" t="n">
-        <v>6866794</v>
+        <v>6866800</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128375249</v>
+        <v>128375794</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3804,21 +3804,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471158</v>
+        <v>471241</v>
       </c>
       <c r="R34" t="n">
-        <v>6866800</v>
+        <v>6866786</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128375794</v>
+        <v>128375289</v>
       </c>
       <c r="B35" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471241</v>
+        <v>471165</v>
       </c>
       <c r="R35" t="n">
-        <v>6866786</v>
+        <v>6866794</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3987,7 +3987,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128376382</v>
+        <v>128374814</v>
       </c>
       <c r="B36" t="n">
         <v>79089</v>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471342</v>
+        <v>471137</v>
       </c>
       <c r="R36" t="n">
-        <v>6866780</v>
+        <v>6866828</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4058,6 +4058,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4084,10 +4089,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128373989</v>
+        <v>128376382</v>
       </c>
       <c r="B37" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4095,21 +4100,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4119,10 +4124,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471102</v>
+        <v>471342</v>
       </c>
       <c r="R37" t="n">
-        <v>6866857</v>
+        <v>6866780</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,10 +4186,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128374814</v>
+        <v>128373989</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4192,21 +4197,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4216,10 +4221,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>471137</v>
+        <v>471102</v>
       </c>
       <c r="R38" t="n">
-        <v>6866828</v>
+        <v>6866857</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4252,11 +4257,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4286,7 +4286,7 @@
         <v>128374436</v>
       </c>
       <c r="B39" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128376649</v>
+        <v>128374500</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>79121</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4400,21 +4400,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471300</v>
+        <v>471134</v>
       </c>
       <c r="R40" t="n">
-        <v>6866735</v>
+        <v>6866834</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4486,7 +4486,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128375508</v>
+        <v>128376649</v>
       </c>
       <c r="B41" t="n">
         <v>79089</v>
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471209</v>
+        <v>471300</v>
       </c>
       <c r="R41" t="n">
-        <v>6866776</v>
+        <v>6866735</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4583,10 +4583,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128374500</v>
+        <v>128375508</v>
       </c>
       <c r="B42" t="n">
-        <v>79121</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4594,21 +4594,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471134</v>
+        <v>471209</v>
       </c>
       <c r="R42" t="n">
-        <v>6866834</v>
+        <v>6866776</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5376,7 +5376,7 @@
         <v>128387779</v>
       </c>
       <c r="B50" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>128388103</v>
       </c>
       <c r="B51" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>128387977</v>
       </c>
       <c r="B52" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128389894</v>
+        <v>128387828</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5684,21 +5684,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>471207</v>
+        <v>470743</v>
       </c>
       <c r="R53" t="n">
-        <v>6866729</v>
+        <v>6866698</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128389953</v>
+        <v>128389894</v>
       </c>
       <c r="B54" t="n">
         <v>79089</v>
@@ -5805,13 +5805,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>471200</v>
+        <v>471207</v>
       </c>
       <c r="R54" t="n">
-        <v>6866759</v>
+        <v>6866729</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5867,32 +5867,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128387790</v>
+        <v>128389953</v>
       </c>
       <c r="B55" t="n">
-        <v>98588</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5902,13 +5902,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470732</v>
+        <v>471200</v>
       </c>
       <c r="R55" t="n">
-        <v>6866727</v>
+        <v>6866759</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5964,32 +5964,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128387828</v>
+        <v>128387790</v>
       </c>
       <c r="B56" t="n">
-        <v>78847</v>
+        <v>98591</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5999,13 +5999,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>470743</v>
+        <v>470732</v>
       </c>
       <c r="R56" t="n">
-        <v>6866698</v>
+        <v>6866727</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>128387936</v>
       </c>
       <c r="B60" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7142,10 +7142,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128389227</v>
+        <v>128389069</v>
       </c>
       <c r="B68" t="n">
-        <v>79121</v>
+        <v>80194</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471156</v>
+        <v>471158</v>
       </c>
       <c r="R68" t="n">
-        <v>6866665</v>
+        <v>6866734</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128388804</v>
+        <v>128389187</v>
       </c>
       <c r="B69" t="n">
-        <v>79121</v>
+        <v>78846</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>470987</v>
+        <v>471196</v>
       </c>
       <c r="R69" t="n">
         <v>6866706</v>
@@ -7336,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128389069</v>
+        <v>128389227</v>
       </c>
       <c r="B70" t="n">
-        <v>80194</v>
+        <v>79121</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7347,21 +7347,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471158</v>
+        <v>471156</v>
       </c>
       <c r="R70" t="n">
-        <v>6866734</v>
+        <v>6866665</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128389187</v>
+        <v>128388804</v>
       </c>
       <c r="B71" t="n">
-        <v>78846</v>
+        <v>79121</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471196</v>
+        <v>470987</v>
       </c>
       <c r="R71" t="n">
         <v>6866706</v>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128388766</v>
+        <v>128389641</v>
       </c>
       <c r="B72" t="n">
-        <v>79168</v>
+        <v>80194</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470981</v>
+        <v>471241</v>
       </c>
       <c r="R72" t="n">
-        <v>6866714</v>
+        <v>6866656</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128388646</v>
+        <v>128388766</v>
       </c>
       <c r="B73" t="n">
-        <v>79121</v>
+        <v>79168</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7638,21 +7638,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470945</v>
+        <v>470981</v>
       </c>
       <c r="R73" t="n">
-        <v>6866709</v>
+        <v>6866714</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7724,10 +7724,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128389641</v>
+        <v>128388646</v>
       </c>
       <c r="B74" t="n">
-        <v>80194</v>
+        <v>79121</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471241</v>
+        <v>470945</v>
       </c>
       <c r="R74" t="n">
-        <v>6866656</v>
+        <v>6866709</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7824,7 +7824,7 @@
         <v>128387695</v>
       </c>
       <c r="B75" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>128387629</v>
       </c>
       <c r="B77" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8121,54 +8121,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128388416</v>
+        <v>128388815</v>
       </c>
       <c r="B78" t="n">
-        <v>98588</v>
+        <v>79089</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470816</v>
+        <v>470992</v>
       </c>
       <c r="R78" t="n">
-        <v>6866722</v>
+        <v>6866696</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8227,7 +8218,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128388815</v>
+        <v>128389886</v>
       </c>
       <c r="B79" t="n">
         <v>79089</v>
@@ -8262,10 +8253,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>470992</v>
+        <v>471211</v>
       </c>
       <c r="R79" t="n">
-        <v>6866696</v>
+        <v>6866717</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8324,7 +8315,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128389886</v>
+        <v>128388714</v>
       </c>
       <c r="B80" t="n">
         <v>79089</v>
@@ -8359,10 +8350,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471211</v>
+        <v>470987</v>
       </c>
       <c r="R80" t="n">
-        <v>6866717</v>
+        <v>6866714</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8421,45 +8412,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128388714</v>
+        <v>128388416</v>
       </c>
       <c r="B81" t="n">
-        <v>79089</v>
+        <v>98591</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>470987</v>
+        <v>470816</v>
       </c>
       <c r="R81" t="n">
-        <v>6866714</v>
+        <v>6866722</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8812,7 +8812,7 @@
         <v>128387659</v>
       </c>
       <c r="B85" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128389213</v>
+        <v>128388228</v>
       </c>
       <c r="B87" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471148</v>
+        <v>470788</v>
       </c>
       <c r="R87" t="n">
-        <v>6866668</v>
+        <v>6866725</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128389901</v>
+        <v>128389213</v>
       </c>
       <c r="B88" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471209</v>
+        <v>471148</v>
       </c>
       <c r="R88" t="n">
-        <v>6866743</v>
+        <v>6866668</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9206,10 +9206,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128389351</v>
+        <v>128389901</v>
       </c>
       <c r="B89" t="n">
-        <v>78061</v>
+        <v>79089</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9217,21 +9217,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471215</v>
+        <v>471209</v>
       </c>
       <c r="R89" t="n">
-        <v>6866634</v>
+        <v>6866743</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9303,32 +9303,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128388228</v>
+        <v>128389351</v>
       </c>
       <c r="B90" t="n">
-        <v>98588</v>
+        <v>78061</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>470788</v>
+        <v>471215</v>
       </c>
       <c r="R90" t="n">
-        <v>6866725</v>
+        <v>6866634</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128388173</v>
+        <v>128389918</v>
       </c>
       <c r="B92" t="n">
-        <v>78755</v>
+        <v>79089</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9532,13 +9532,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>470786</v>
+        <v>471210</v>
       </c>
       <c r="R92" t="n">
-        <v>6866737</v>
+        <v>6866755</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128389587</v>
+        <v>128388173</v>
       </c>
       <c r="B93" t="n">
-        <v>80195</v>
+        <v>78755</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9629,10 +9629,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471274</v>
+        <v>470786</v>
       </c>
       <c r="R93" t="n">
-        <v>6866626</v>
+        <v>6866737</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9691,10 +9691,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128389918</v>
+        <v>128389587</v>
       </c>
       <c r="B94" t="n">
-        <v>79089</v>
+        <v>80195</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9702,21 +9702,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9726,13 +9726,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471210</v>
+        <v>471274</v>
       </c>
       <c r="R94" t="n">
-        <v>6866755</v>
+        <v>6866626</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10273,32 +10273,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128502704</v>
+        <v>128501140</v>
       </c>
       <c r="B100" t="n">
-        <v>91431</v>
+        <v>79089</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471366</v>
+        <v>471253</v>
       </c>
       <c r="R100" t="n">
-        <v>6866720</v>
+        <v>6866704</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10370,32 +10370,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128501140</v>
+        <v>128502704</v>
       </c>
       <c r="B101" t="n">
-        <v>79089</v>
+        <v>91431</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471253</v>
+        <v>471366</v>
       </c>
       <c r="R101" t="n">
-        <v>6866704</v>
+        <v>6866720</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11049,32 +11049,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128502866</v>
+        <v>128501209</v>
       </c>
       <c r="B108" t="n">
-        <v>98505</v>
+        <v>78846</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471139</v>
+        <v>471244</v>
       </c>
       <c r="R108" t="n">
-        <v>6866727</v>
+        <v>6866687</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11146,32 +11146,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128502100</v>
+        <v>128502866</v>
       </c>
       <c r="B109" t="n">
-        <v>79121</v>
+        <v>98508</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11181,10 +11181,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471347</v>
+        <v>471139</v>
       </c>
       <c r="R109" t="n">
-        <v>6866584</v>
+        <v>6866727</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11243,10 +11243,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128502802</v>
+        <v>128502100</v>
       </c>
       <c r="B110" t="n">
-        <v>79089</v>
+        <v>79121</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11254,21 +11254,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471256</v>
+        <v>471347</v>
       </c>
       <c r="R110" t="n">
-        <v>6866728</v>
+        <v>6866584</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11340,10 +11340,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128501209</v>
+        <v>128502802</v>
       </c>
       <c r="B111" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11351,21 +11351,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11375,10 +11375,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471244</v>
+        <v>471256</v>
       </c>
       <c r="R111" t="n">
-        <v>6866687</v>
+        <v>6866728</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11534,10 +11534,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128501973</v>
+        <v>128501097</v>
       </c>
       <c r="B113" t="n">
-        <v>79121</v>
+        <v>79089</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11545,21 +11545,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471363</v>
+        <v>471224</v>
       </c>
       <c r="R113" t="n">
-        <v>6866544</v>
+        <v>6866707</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11631,7 +11631,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128502607</v>
+        <v>128502509</v>
       </c>
       <c r="B114" t="n">
         <v>78846</v>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471349</v>
+        <v>471315</v>
       </c>
       <c r="R114" t="n">
-        <v>6866695</v>
+        <v>6866670</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11728,10 +11728,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128501347</v>
+        <v>128502607</v>
       </c>
       <c r="B115" t="n">
-        <v>80194</v>
+        <v>78846</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11739,21 +11739,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11763,10 +11763,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471275</v>
+        <v>471349</v>
       </c>
       <c r="R115" t="n">
-        <v>6866627</v>
+        <v>6866695</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128502509</v>
+        <v>128501347</v>
       </c>
       <c r="B116" t="n">
-        <v>78846</v>
+        <v>80194</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11836,21 +11836,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471315</v>
+        <v>471275</v>
       </c>
       <c r="R116" t="n">
-        <v>6866670</v>
+        <v>6866627</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11922,10 +11922,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128501097</v>
+        <v>128501973</v>
       </c>
       <c r="B117" t="n">
-        <v>79089</v>
+        <v>79121</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11933,21 +11933,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11957,10 +11957,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471224</v>
+        <v>471363</v>
       </c>
       <c r="R117" t="n">
-        <v>6866707</v>
+        <v>6866544</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -869,45 +869,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128376373</v>
+        <v>128374420</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471330</v>
+        <v>471132</v>
       </c>
       <c r="R4" t="n">
-        <v>6866787</v>
+        <v>6866856</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128374470</v>
+        <v>128375924</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +986,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471139</v>
+        <v>471255</v>
       </c>
       <c r="R5" t="n">
-        <v>6866835</v>
+        <v>6866786</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1072,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128376618</v>
+        <v>128376373</v>
       </c>
       <c r="B6" t="n">
         <v>79089</v>
@@ -1098,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471331</v>
+        <v>471330</v>
       </c>
       <c r="R6" t="n">
-        <v>6866715</v>
+        <v>6866787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,54 +1169,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128374420</v>
+        <v>128374470</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471132</v>
+        <v>471139</v>
       </c>
       <c r="R7" t="n">
-        <v>6866856</v>
+        <v>6866835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128375924</v>
+        <v>128376618</v>
       </c>
       <c r="B8" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471255</v>
+        <v>471331</v>
       </c>
       <c r="R8" t="n">
-        <v>6866786</v>
+        <v>6866715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128376676</v>
+        <v>128374859</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>80195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471287</v>
+        <v>471125</v>
       </c>
       <c r="R13" t="n">
-        <v>6866763</v>
+        <v>6866815</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128374859</v>
+        <v>128376676</v>
       </c>
       <c r="B14" t="n">
-        <v>80195</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471125</v>
+        <v>471287</v>
       </c>
       <c r="R14" t="n">
-        <v>6866815</v>
+        <v>6866763</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -4680,54 +4680,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128376462</v>
+        <v>128375808</v>
       </c>
       <c r="B43" t="n">
-        <v>92040</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471351</v>
+        <v>471247</v>
       </c>
       <c r="R43" t="n">
-        <v>6866748</v>
+        <v>6866787</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4760,11 +4751,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4791,7 +4777,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128375808</v>
+        <v>128375498</v>
       </c>
       <c r="B44" t="n">
         <v>79089</v>
@@ -4826,10 +4812,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471247</v>
+        <v>471198</v>
       </c>
       <c r="R44" t="n">
-        <v>6866787</v>
+        <v>6866776</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4888,45 +4874,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128375498</v>
+        <v>128376462</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>92040</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471198</v>
+        <v>471351</v>
       </c>
       <c r="R45" t="n">
-        <v>6866776</v>
+        <v>6866748</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4959,6 +4954,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128388207</v>
+        <v>128387779</v>
       </c>
       <c r="B49" t="n">
-        <v>78846</v>
+        <v>98591</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470789</v>
+        <v>470744</v>
       </c>
       <c r="R49" t="n">
-        <v>6866739</v>
+        <v>6866736</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5373,7 +5373,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128387779</v>
+        <v>128388103</v>
       </c>
       <c r="B50" t="n">
         <v>98591</v>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470744</v>
+        <v>470763</v>
       </c>
       <c r="R50" t="n">
-        <v>6866736</v>
+        <v>6866753</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,32 +5470,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128388103</v>
+        <v>128388207</v>
       </c>
       <c r="B51" t="n">
-        <v>98591</v>
+        <v>78846</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470763</v>
+        <v>470789</v>
       </c>
       <c r="R51" t="n">
-        <v>6866753</v>
+        <v>6866739</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128389262</v>
+        <v>128389511</v>
       </c>
       <c r="B62" t="n">
-        <v>80195</v>
+        <v>80194</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6566,21 +6566,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471168</v>
+        <v>471237</v>
       </c>
       <c r="R62" t="n">
-        <v>6866647</v>
+        <v>6866588</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128389511</v>
+        <v>128389329</v>
       </c>
       <c r="B63" t="n">
-        <v>80194</v>
+        <v>78846</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6663,21 +6663,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471237</v>
+        <v>471172</v>
       </c>
       <c r="R63" t="n">
-        <v>6866588</v>
+        <v>6866632</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128389329</v>
+        <v>128387227</v>
       </c>
       <c r="B64" t="n">
-        <v>78846</v>
+        <v>80194</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471172</v>
+        <v>470551</v>
       </c>
       <c r="R64" t="n">
-        <v>6866632</v>
+        <v>6866892</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,7 +6846,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128387227</v>
+        <v>128387286</v>
       </c>
       <c r="B65" t="n">
         <v>80194</v>
@@ -6884,7 +6884,7 @@
         <v>470551</v>
       </c>
       <c r="R65" t="n">
-        <v>6866892</v>
+        <v>6866872</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128387286</v>
+        <v>128389262</v>
       </c>
       <c r="B66" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,21 +6954,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470551</v>
+        <v>471168</v>
       </c>
       <c r="R66" t="n">
-        <v>6866872</v>
+        <v>6866647</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7142,10 +7142,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128389069</v>
+        <v>128389227</v>
       </c>
       <c r="B68" t="n">
-        <v>80194</v>
+        <v>79121</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471158</v>
+        <v>471156</v>
       </c>
       <c r="R68" t="n">
-        <v>6866734</v>
+        <v>6866665</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128389187</v>
+        <v>128388804</v>
       </c>
       <c r="B69" t="n">
-        <v>78846</v>
+        <v>79121</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471196</v>
+        <v>470987</v>
       </c>
       <c r="R69" t="n">
         <v>6866706</v>
@@ -7336,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128389227</v>
+        <v>128389069</v>
       </c>
       <c r="B70" t="n">
-        <v>79121</v>
+        <v>80194</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7347,21 +7347,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471156</v>
+        <v>471158</v>
       </c>
       <c r="R70" t="n">
-        <v>6866665</v>
+        <v>6866734</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128388804</v>
+        <v>128389187</v>
       </c>
       <c r="B71" t="n">
-        <v>79121</v>
+        <v>78846</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>470987</v>
+        <v>471196</v>
       </c>
       <c r="R71" t="n">
         <v>6866706</v>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128389641</v>
+        <v>128388766</v>
       </c>
       <c r="B72" t="n">
-        <v>80194</v>
+        <v>79168</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471241</v>
+        <v>470981</v>
       </c>
       <c r="R72" t="n">
-        <v>6866656</v>
+        <v>6866714</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128388766</v>
+        <v>128388646</v>
       </c>
       <c r="B73" t="n">
-        <v>79168</v>
+        <v>79121</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7638,21 +7638,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470981</v>
+        <v>470945</v>
       </c>
       <c r="R73" t="n">
-        <v>6866714</v>
+        <v>6866709</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7724,10 +7724,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128388646</v>
+        <v>128389641</v>
       </c>
       <c r="B74" t="n">
-        <v>79121</v>
+        <v>80194</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>470945</v>
+        <v>471241</v>
       </c>
       <c r="R74" t="n">
-        <v>6866709</v>
+        <v>6866656</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -11049,10 +11049,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128501209</v>
+        <v>128502100</v>
       </c>
       <c r="B108" t="n">
-        <v>78846</v>
+        <v>79121</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11060,21 +11060,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471244</v>
+        <v>471347</v>
       </c>
       <c r="R108" t="n">
-        <v>6866687</v>
+        <v>6866584</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11146,32 +11146,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128502866</v>
+        <v>128502802</v>
       </c>
       <c r="B109" t="n">
-        <v>98508</v>
+        <v>79089</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11181,10 +11181,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471139</v>
+        <v>471256</v>
       </c>
       <c r="R109" t="n">
-        <v>6866727</v>
+        <v>6866728</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11243,10 +11243,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128502100</v>
+        <v>128501209</v>
       </c>
       <c r="B110" t="n">
-        <v>79121</v>
+        <v>78846</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11254,21 +11254,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471347</v>
+        <v>471244</v>
       </c>
       <c r="R110" t="n">
-        <v>6866584</v>
+        <v>6866687</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11340,32 +11340,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128502802</v>
+        <v>128502866</v>
       </c>
       <c r="B111" t="n">
-        <v>79089</v>
+        <v>98508</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11375,10 +11375,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471256</v>
+        <v>471139</v>
       </c>
       <c r="R111" t="n">
-        <v>6866728</v>
+        <v>6866727</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -869,54 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128374420</v>
+        <v>128376373</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471132</v>
+        <v>471330</v>
       </c>
       <c r="R4" t="n">
-        <v>6866856</v>
+        <v>6866787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128375924</v>
+        <v>128376618</v>
       </c>
       <c r="B5" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471255</v>
+        <v>471331</v>
       </c>
       <c r="R5" t="n">
-        <v>6866786</v>
+        <v>6866715</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128376373</v>
+        <v>128374470</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471330</v>
+        <v>471139</v>
       </c>
       <c r="R6" t="n">
-        <v>6866787</v>
+        <v>6866835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,45 +1160,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128374470</v>
+        <v>128374420</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471139</v>
+        <v>471132</v>
       </c>
       <c r="R7" t="n">
-        <v>6866835</v>
+        <v>6866856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128376618</v>
+        <v>128375924</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471331</v>
+        <v>471255</v>
       </c>
       <c r="R8" t="n">
-        <v>6866715</v>
+        <v>6866786</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,7 +1363,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128376258</v>
+        <v>128375190</v>
       </c>
       <c r="B9" t="n">
         <v>79089</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471292</v>
+        <v>471145</v>
       </c>
       <c r="R9" t="n">
-        <v>6866805</v>
+        <v>6866802</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128375168</v>
+        <v>128376258</v>
       </c>
       <c r="B10" t="n">
         <v>79089</v>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471139</v>
+        <v>471292</v>
       </c>
       <c r="R10" t="n">
-        <v>6866821</v>
+        <v>6866805</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128375190</v>
+        <v>128375168</v>
       </c>
       <c r="B11" t="n">
         <v>79089</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471145</v>
+        <v>471139</v>
       </c>
       <c r="R11" t="n">
-        <v>6866802</v>
+        <v>6866821</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128376712</v>
+        <v>128374662</v>
       </c>
       <c r="B16" t="n">
-        <v>79679</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471282</v>
+        <v>471145</v>
       </c>
       <c r="R16" t="n">
-        <v>6866780</v>
+        <v>6866824</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128374662</v>
+        <v>128376712</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79679</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471145</v>
+        <v>471282</v>
       </c>
       <c r="R18" t="n">
-        <v>6866824</v>
+        <v>6866780</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128375989</v>
+        <v>128375959</v>
       </c>
       <c r="B19" t="n">
-        <v>78061</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471276</v>
+        <v>471266</v>
       </c>
       <c r="R19" t="n">
-        <v>6866805</v>
+        <v>6866792</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128375959</v>
+        <v>128375989</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>78061</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471266</v>
+        <v>471276</v>
       </c>
       <c r="R20" t="n">
-        <v>6866792</v>
+        <v>6866805</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128375214</v>
+        <v>128375358</v>
       </c>
       <c r="B21" t="n">
         <v>79089</v>
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471144</v>
+        <v>471166</v>
       </c>
       <c r="R21" t="n">
-        <v>6866814</v>
+        <v>6866785</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2624,7 +2624,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128375358</v>
+        <v>128375214</v>
       </c>
       <c r="B22" t="n">
         <v>79089</v>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471166</v>
+        <v>471144</v>
       </c>
       <c r="R22" t="n">
-        <v>6866785</v>
+        <v>6866814</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3308,7 +3308,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128376636</v>
+        <v>128374116</v>
       </c>
       <c r="B29" t="n">
         <v>79089</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471320</v>
+        <v>471107</v>
       </c>
       <c r="R29" t="n">
-        <v>6866734</v>
+        <v>6866853</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374116</v>
+        <v>128376636</v>
       </c>
       <c r="B31" t="n">
         <v>79089</v>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471107</v>
+        <v>471320</v>
       </c>
       <c r="R31" t="n">
-        <v>6866853</v>
+        <v>6866734</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3696,7 +3696,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128375249</v>
+        <v>128375289</v>
       </c>
       <c r="B33" t="n">
         <v>79089</v>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471158</v>
+        <v>471165</v>
       </c>
       <c r="R33" t="n">
-        <v>6866800</v>
+        <v>6866794</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128375794</v>
+        <v>128375249</v>
       </c>
       <c r="B34" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3804,21 +3804,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471241</v>
+        <v>471158</v>
       </c>
       <c r="R34" t="n">
-        <v>6866786</v>
+        <v>6866800</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128375289</v>
+        <v>128375794</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471165</v>
+        <v>471241</v>
       </c>
       <c r="R35" t="n">
-        <v>6866794</v>
+        <v>6866786</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3987,7 +3987,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128374814</v>
+        <v>128376382</v>
       </c>
       <c r="B36" t="n">
         <v>79089</v>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471137</v>
+        <v>471342</v>
       </c>
       <c r="R36" t="n">
-        <v>6866828</v>
+        <v>6866780</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4058,11 +4058,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4089,7 +4084,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128376382</v>
+        <v>128374814</v>
       </c>
       <c r="B37" t="n">
         <v>79089</v>
@@ -4124,10 +4119,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471342</v>
+        <v>471137</v>
       </c>
       <c r="R37" t="n">
-        <v>6866780</v>
+        <v>6866828</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4160,6 +4155,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4286,7 +4286,7 @@
         <v>128374436</v>
       </c>
       <c r="B39" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4680,45 +4680,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128375808</v>
+        <v>128376462</v>
       </c>
       <c r="B43" t="n">
-        <v>79089</v>
+        <v>92041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471247</v>
+        <v>471351</v>
       </c>
       <c r="R43" t="n">
-        <v>6866787</v>
+        <v>6866748</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4751,6 +4760,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4777,7 +4791,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128375498</v>
+        <v>128375808</v>
       </c>
       <c r="B44" t="n">
         <v>79089</v>
@@ -4812,10 +4826,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471198</v>
+        <v>471247</v>
       </c>
       <c r="R44" t="n">
-        <v>6866776</v>
+        <v>6866787</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4874,54 +4888,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128376462</v>
+        <v>128375498</v>
       </c>
       <c r="B45" t="n">
-        <v>92040</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471351</v>
+        <v>471198</v>
       </c>
       <c r="R45" t="n">
-        <v>6866748</v>
+        <v>6866776</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4954,11 +4959,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5082,7 +5082,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128376295</v>
+        <v>128375399</v>
       </c>
       <c r="B47" t="n">
         <v>79089</v>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471321</v>
+        <v>471183</v>
       </c>
       <c r="R47" t="n">
-        <v>6866820</v>
+        <v>6866790</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5179,7 +5179,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128375399</v>
+        <v>128376295</v>
       </c>
       <c r="B48" t="n">
         <v>79089</v>
@@ -5214,10 +5214,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>471183</v>
+        <v>471321</v>
       </c>
       <c r="R48" t="n">
-        <v>6866790</v>
+        <v>6866820</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5276,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128387779</v>
+        <v>128388207</v>
       </c>
       <c r="B49" t="n">
-        <v>98591</v>
+        <v>78846</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470744</v>
+        <v>470789</v>
       </c>
       <c r="R49" t="n">
-        <v>6866736</v>
+        <v>6866739</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128388103</v>
+        <v>128387779</v>
       </c>
       <c r="B50" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470763</v>
+        <v>470744</v>
       </c>
       <c r="R50" t="n">
-        <v>6866753</v>
+        <v>6866736</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,32 +5470,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128388207</v>
+        <v>128388103</v>
       </c>
       <c r="B51" t="n">
-        <v>78846</v>
+        <v>98592</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470789</v>
+        <v>470763</v>
       </c>
       <c r="R51" t="n">
-        <v>6866739</v>
+        <v>6866753</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5570,7 +5570,7 @@
         <v>128387977</v>
       </c>
       <c r="B52" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128387828</v>
+        <v>128389953</v>
       </c>
       <c r="B53" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5684,21 +5684,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5708,10 +5708,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>470743</v>
+        <v>471200</v>
       </c>
       <c r="R53" t="n">
-        <v>6866698</v>
+        <v>6866759</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5867,10 +5867,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128389953</v>
+        <v>128387828</v>
       </c>
       <c r="B55" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5878,21 +5878,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>471200</v>
+        <v>470743</v>
       </c>
       <c r="R55" t="n">
-        <v>6866759</v>
+        <v>6866698</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -5967,7 +5967,7 @@
         <v>128387790</v>
       </c>
       <c r="B56" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>128387936</v>
       </c>
       <c r="B60" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128389511</v>
+        <v>128389262</v>
       </c>
       <c r="B62" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6566,21 +6566,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471237</v>
+        <v>471168</v>
       </c>
       <c r="R62" t="n">
-        <v>6866588</v>
+        <v>6866647</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6749,7 +6749,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128387227</v>
+        <v>128389511</v>
       </c>
       <c r="B64" t="n">
         <v>80194</v>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>470551</v>
+        <v>471237</v>
       </c>
       <c r="R64" t="n">
-        <v>6866892</v>
+        <v>6866588</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,7 +6846,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128387286</v>
+        <v>128387227</v>
       </c>
       <c r="B65" t="n">
         <v>80194</v>
@@ -6884,7 +6884,7 @@
         <v>470551</v>
       </c>
       <c r="R65" t="n">
-        <v>6866872</v>
+        <v>6866892</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128389262</v>
+        <v>128389855</v>
       </c>
       <c r="B66" t="n">
-        <v>80195</v>
+        <v>57849</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,21 +6954,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>471168</v>
+        <v>471241</v>
       </c>
       <c r="R66" t="n">
-        <v>6866647</v>
+        <v>6866622</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7014,6 +7014,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7040,10 +7045,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128389855</v>
+        <v>128387286</v>
       </c>
       <c r="B67" t="n">
-        <v>57849</v>
+        <v>80194</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,21 +7056,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,13 +7080,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471241</v>
+        <v>470551</v>
       </c>
       <c r="R67" t="n">
-        <v>6866622</v>
+        <v>6866872</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7111,11 +7116,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7142,7 +7142,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128389227</v>
+        <v>128388804</v>
       </c>
       <c r="B68" t="n">
         <v>79121</v>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471156</v>
+        <v>470987</v>
       </c>
       <c r="R68" t="n">
-        <v>6866665</v>
+        <v>6866706</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,7 +7239,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128388804</v>
+        <v>128389227</v>
       </c>
       <c r="B69" t="n">
         <v>79121</v>
@@ -7274,10 +7274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>470987</v>
+        <v>471156</v>
       </c>
       <c r="R69" t="n">
-        <v>6866706</v>
+        <v>6866665</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7336,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128389069</v>
+        <v>128389187</v>
       </c>
       <c r="B70" t="n">
-        <v>80194</v>
+        <v>78846</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7347,21 +7347,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471158</v>
+        <v>471196</v>
       </c>
       <c r="R70" t="n">
-        <v>6866734</v>
+        <v>6866706</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128389187</v>
+        <v>128389069</v>
       </c>
       <c r="B71" t="n">
-        <v>78846</v>
+        <v>80194</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471196</v>
+        <v>471158</v>
       </c>
       <c r="R71" t="n">
-        <v>6866706</v>
+        <v>6866734</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128388766</v>
+        <v>128388646</v>
       </c>
       <c r="B72" t="n">
-        <v>79168</v>
+        <v>79121</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470981</v>
+        <v>470945</v>
       </c>
       <c r="R72" t="n">
-        <v>6866714</v>
+        <v>6866709</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128388646</v>
+        <v>128388766</v>
       </c>
       <c r="B73" t="n">
-        <v>79121</v>
+        <v>79168</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7638,21 +7638,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470945</v>
+        <v>470981</v>
       </c>
       <c r="R73" t="n">
-        <v>6866709</v>
+        <v>6866714</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7824,7 +7824,7 @@
         <v>128387695</v>
       </c>
       <c r="B75" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>128387629</v>
       </c>
       <c r="B77" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128389886</v>
+        <v>128388714</v>
       </c>
       <c r="B79" t="n">
         <v>79089</v>
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471211</v>
+        <v>470987</v>
       </c>
       <c r="R79" t="n">
-        <v>6866717</v>
+        <v>6866714</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8315,7 +8315,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128388714</v>
+        <v>128389886</v>
       </c>
       <c r="B80" t="n">
         <v>79089</v>
@@ -8350,10 +8350,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>470987</v>
+        <v>471211</v>
       </c>
       <c r="R80" t="n">
-        <v>6866714</v>
+        <v>6866717</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8412,54 +8412,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128388416</v>
+        <v>128389403</v>
       </c>
       <c r="B81" t="n">
-        <v>98591</v>
+        <v>78847</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>470816</v>
+        <v>471187</v>
       </c>
       <c r="R81" t="n">
-        <v>6866722</v>
+        <v>6866586</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8518,45 +8509,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128389403</v>
+        <v>128388416</v>
       </c>
       <c r="B82" t="n">
-        <v>78847</v>
+        <v>98592</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471187</v>
+        <v>470816</v>
       </c>
       <c r="R82" t="n">
-        <v>6866586</v>
+        <v>6866722</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8812,7 +8812,7 @@
         <v>128387659</v>
       </c>
       <c r="B85" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128388228</v>
+        <v>128389213</v>
       </c>
       <c r="B87" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>470788</v>
+        <v>471148</v>
       </c>
       <c r="R87" t="n">
-        <v>6866725</v>
+        <v>6866668</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128389213</v>
+        <v>128389351</v>
       </c>
       <c r="B88" t="n">
-        <v>80194</v>
+        <v>78061</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471148</v>
+        <v>471215</v>
       </c>
       <c r="R88" t="n">
-        <v>6866668</v>
+        <v>6866634</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9303,32 +9303,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128389351</v>
+        <v>128388228</v>
       </c>
       <c r="B90" t="n">
-        <v>78061</v>
+        <v>98592</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471215</v>
+        <v>470788</v>
       </c>
       <c r="R90" t="n">
-        <v>6866634</v>
+        <v>6866725</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128389918</v>
+        <v>128388173</v>
       </c>
       <c r="B92" t="n">
-        <v>79089</v>
+        <v>78755</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9532,13 +9532,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471210</v>
+        <v>470786</v>
       </c>
       <c r="R92" t="n">
-        <v>6866755</v>
+        <v>6866737</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128388173</v>
+        <v>128389918</v>
       </c>
       <c r="B93" t="n">
-        <v>78755</v>
+        <v>79089</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>470786</v>
+        <v>471210</v>
       </c>
       <c r="R93" t="n">
-        <v>6866737</v>
+        <v>6866755</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9885,10 +9885,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128502381</v>
+        <v>128502263</v>
       </c>
       <c r="B96" t="n">
-        <v>79121</v>
+        <v>79089</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9896,21 +9896,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9920,10 +9920,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471311</v>
+        <v>471328</v>
       </c>
       <c r="R96" t="n">
-        <v>6866616</v>
+        <v>6866612</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9982,10 +9982,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128502263</v>
+        <v>128502381</v>
       </c>
       <c r="B97" t="n">
-        <v>79089</v>
+        <v>79121</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9993,21 +9993,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471328</v>
+        <v>471311</v>
       </c>
       <c r="R97" t="n">
-        <v>6866612</v>
+        <v>6866616</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10273,32 +10273,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128501140</v>
+        <v>128502704</v>
       </c>
       <c r="B100" t="n">
-        <v>79089</v>
+        <v>91432</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471253</v>
+        <v>471366</v>
       </c>
       <c r="R100" t="n">
-        <v>6866704</v>
+        <v>6866720</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10370,32 +10370,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128502704</v>
+        <v>128501140</v>
       </c>
       <c r="B101" t="n">
-        <v>91431</v>
+        <v>79089</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471366</v>
+        <v>471253</v>
       </c>
       <c r="R101" t="n">
-        <v>6866720</v>
+        <v>6866704</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11049,10 +11049,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128502100</v>
+        <v>128502802</v>
       </c>
       <c r="B108" t="n">
-        <v>79121</v>
+        <v>79089</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11060,21 +11060,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471347</v>
+        <v>471256</v>
       </c>
       <c r="R108" t="n">
-        <v>6866584</v>
+        <v>6866728</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11146,10 +11146,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128502802</v>
+        <v>128501209</v>
       </c>
       <c r="B109" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11157,21 +11157,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11181,10 +11181,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471256</v>
+        <v>471244</v>
       </c>
       <c r="R109" t="n">
-        <v>6866728</v>
+        <v>6866687</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11243,10 +11243,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128501209</v>
+        <v>128502100</v>
       </c>
       <c r="B110" t="n">
-        <v>78846</v>
+        <v>79121</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11254,21 +11254,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471244</v>
+        <v>471347</v>
       </c>
       <c r="R110" t="n">
-        <v>6866687</v>
+        <v>6866584</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11343,7 +11343,7 @@
         <v>128502866</v>
       </c>
       <c r="B111" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11534,10 +11534,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128501097</v>
+        <v>128502509</v>
       </c>
       <c r="B113" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11545,21 +11545,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471224</v>
+        <v>471315</v>
       </c>
       <c r="R113" t="n">
-        <v>6866707</v>
+        <v>6866670</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11631,10 +11631,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128502509</v>
+        <v>128501097</v>
       </c>
       <c r="B114" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11642,21 +11642,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471315</v>
+        <v>471224</v>
       </c>
       <c r="R114" t="n">
-        <v>6866670</v>
+        <v>6866707</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128501347</v>
+        <v>128501973</v>
       </c>
       <c r="B116" t="n">
-        <v>80194</v>
+        <v>79121</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11836,21 +11836,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471275</v>
+        <v>471363</v>
       </c>
       <c r="R116" t="n">
-        <v>6866627</v>
+        <v>6866544</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11922,10 +11922,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128501973</v>
+        <v>128501347</v>
       </c>
       <c r="B117" t="n">
-        <v>79121</v>
+        <v>80194</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11933,21 +11933,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11957,10 +11957,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471363</v>
+        <v>471275</v>
       </c>
       <c r="R117" t="n">
-        <v>6866544</v>
+        <v>6866627</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128373928</v>
+        <v>128375924</v>
       </c>
       <c r="B2" t="n">
-        <v>79121</v>
+        <v>78847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471086</v>
+        <v>471255</v>
       </c>
       <c r="R2" t="n">
-        <v>6866862</v>
+        <v>6866786</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128375151</v>
+        <v>128374420</v>
       </c>
       <c r="B3" t="n">
-        <v>79121</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471135</v>
+        <v>471132</v>
       </c>
       <c r="R3" t="n">
-        <v>6866819</v>
+        <v>6866856</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128376373</v>
+        <v>128373928</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471330</v>
+        <v>471086</v>
       </c>
       <c r="R4" t="n">
-        <v>6866787</v>
+        <v>6866862</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128376618</v>
+        <v>128375151</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +986,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471331</v>
+        <v>471135</v>
       </c>
       <c r="R5" t="n">
-        <v>6866715</v>
+        <v>6866819</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,54 +1169,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128374420</v>
+        <v>128376373</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471132</v>
+        <v>471330</v>
       </c>
       <c r="R7" t="n">
-        <v>6866856</v>
+        <v>6866787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128375924</v>
+        <v>128376618</v>
       </c>
       <c r="B8" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471255</v>
+        <v>471331</v>
       </c>
       <c r="R8" t="n">
-        <v>6866786</v>
+        <v>6866715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -4680,54 +4680,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128376462</v>
+        <v>128375808</v>
       </c>
       <c r="B43" t="n">
-        <v>92041</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471351</v>
+        <v>471247</v>
       </c>
       <c r="R43" t="n">
-        <v>6866748</v>
+        <v>6866787</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4760,11 +4751,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4791,7 +4777,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128375808</v>
+        <v>128375498</v>
       </c>
       <c r="B44" t="n">
         <v>79089</v>
@@ -4826,10 +4812,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471247</v>
+        <v>471198</v>
       </c>
       <c r="R44" t="n">
-        <v>6866787</v>
+        <v>6866776</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4888,45 +4874,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128375498</v>
+        <v>128376462</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>92041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471198</v>
+        <v>471351</v>
       </c>
       <c r="R45" t="n">
-        <v>6866776</v>
+        <v>6866748</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4959,6 +4954,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128388207</v>
+        <v>128387779</v>
       </c>
       <c r="B49" t="n">
-        <v>78846</v>
+        <v>98592</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470789</v>
+        <v>470744</v>
       </c>
       <c r="R49" t="n">
-        <v>6866739</v>
+        <v>6866736</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5373,7 +5373,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128387779</v>
+        <v>128388103</v>
       </c>
       <c r="B50" t="n">
         <v>98592</v>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470744</v>
+        <v>470763</v>
       </c>
       <c r="R50" t="n">
-        <v>6866736</v>
+        <v>6866753</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,32 +5470,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128388103</v>
+        <v>128388207</v>
       </c>
       <c r="B51" t="n">
-        <v>98592</v>
+        <v>78846</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470763</v>
+        <v>470789</v>
       </c>
       <c r="R51" t="n">
-        <v>6866753</v>
+        <v>6866739</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5867,32 +5867,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128387828</v>
+        <v>128387790</v>
       </c>
       <c r="B55" t="n">
-        <v>78847</v>
+        <v>98592</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5902,13 +5902,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470743</v>
+        <v>470732</v>
       </c>
       <c r="R55" t="n">
-        <v>6866698</v>
+        <v>6866727</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5964,32 +5964,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128387790</v>
+        <v>128387828</v>
       </c>
       <c r="B56" t="n">
-        <v>98592</v>
+        <v>78847</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5999,13 +5999,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>470732</v>
+        <v>470743</v>
       </c>
       <c r="R56" t="n">
-        <v>6866727</v>
+        <v>6866698</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128388646</v>
+        <v>128388766</v>
       </c>
       <c r="B72" t="n">
-        <v>79121</v>
+        <v>79168</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470945</v>
+        <v>470981</v>
       </c>
       <c r="R72" t="n">
-        <v>6866709</v>
+        <v>6866714</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128388766</v>
+        <v>128389641</v>
       </c>
       <c r="B73" t="n">
-        <v>79168</v>
+        <v>80194</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7638,21 +7638,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470981</v>
+        <v>471241</v>
       </c>
       <c r="R73" t="n">
-        <v>6866714</v>
+        <v>6866656</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7724,10 +7724,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128389641</v>
+        <v>128388646</v>
       </c>
       <c r="B74" t="n">
-        <v>80194</v>
+        <v>79121</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471241</v>
+        <v>470945</v>
       </c>
       <c r="R74" t="n">
-        <v>6866656</v>
+        <v>6866709</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8412,45 +8412,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128389403</v>
+        <v>128388416</v>
       </c>
       <c r="B81" t="n">
-        <v>78847</v>
+        <v>98592</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471187</v>
+        <v>470816</v>
       </c>
       <c r="R81" t="n">
-        <v>6866586</v>
+        <v>6866722</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8509,54 +8518,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128388416</v>
+        <v>128389403</v>
       </c>
       <c r="B82" t="n">
-        <v>98592</v>
+        <v>78847</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>470816</v>
+        <v>471187</v>
       </c>
       <c r="R82" t="n">
-        <v>6866722</v>
+        <v>6866586</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9012,10 +9012,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128389213</v>
+        <v>128389901</v>
       </c>
       <c r="B87" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9023,21 +9023,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471148</v>
+        <v>471209</v>
       </c>
       <c r="R87" t="n">
-        <v>6866668</v>
+        <v>6866743</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9109,32 +9109,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128389351</v>
+        <v>128388228</v>
       </c>
       <c r="B88" t="n">
-        <v>78061</v>
+        <v>98592</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471215</v>
+        <v>470788</v>
       </c>
       <c r="R88" t="n">
-        <v>6866634</v>
+        <v>6866725</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9206,10 +9206,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128389901</v>
+        <v>128389213</v>
       </c>
       <c r="B89" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9217,21 +9217,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471209</v>
+        <v>471148</v>
       </c>
       <c r="R89" t="n">
-        <v>6866743</v>
+        <v>6866668</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9303,32 +9303,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128388228</v>
+        <v>128389351</v>
       </c>
       <c r="B90" t="n">
-        <v>98592</v>
+        <v>78061</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>470788</v>
+        <v>471215</v>
       </c>
       <c r="R90" t="n">
-        <v>6866725</v>
+        <v>6866634</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9885,10 +9885,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128502263</v>
+        <v>128502381</v>
       </c>
       <c r="B96" t="n">
-        <v>79089</v>
+        <v>79148</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9896,21 +9896,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9920,10 +9920,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471328</v>
+        <v>471311</v>
       </c>
       <c r="R96" t="n">
-        <v>6866612</v>
+        <v>6866616</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9982,10 +9982,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128502381</v>
+        <v>128502263</v>
       </c>
       <c r="B97" t="n">
-        <v>79121</v>
+        <v>79116</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9993,21 +9993,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471311</v>
+        <v>471328</v>
       </c>
       <c r="R97" t="n">
-        <v>6866616</v>
+        <v>6866612</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10082,7 +10082,7 @@
         <v>128501285</v>
       </c>
       <c r="B98" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>128501083</v>
       </c>
       <c r="B99" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>128502704</v>
       </c>
       <c r="B100" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>128501140</v>
       </c>
       <c r="B101" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>128501794</v>
       </c>
       <c r="B102" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>128502548</v>
       </c>
       <c r="B103" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>128501127</v>
       </c>
       <c r="B104" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>128501181</v>
       </c>
       <c r="B105" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>128501480</v>
       </c>
       <c r="B106" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>128501144</v>
       </c>
       <c r="B107" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11049,32 +11049,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128502802</v>
+        <v>128502866</v>
       </c>
       <c r="B108" t="n">
-        <v>79089</v>
+        <v>98536</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471256</v>
+        <v>471139</v>
       </c>
       <c r="R108" t="n">
-        <v>6866728</v>
+        <v>6866727</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11146,10 +11146,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128501209</v>
+        <v>128502100</v>
       </c>
       <c r="B109" t="n">
-        <v>78846</v>
+        <v>79148</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11157,21 +11157,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11181,10 +11181,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471244</v>
+        <v>471347</v>
       </c>
       <c r="R109" t="n">
-        <v>6866687</v>
+        <v>6866584</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11243,10 +11243,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128502100</v>
+        <v>128501209</v>
       </c>
       <c r="B110" t="n">
-        <v>79121</v>
+        <v>78873</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11254,21 +11254,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471347</v>
+        <v>471244</v>
       </c>
       <c r="R110" t="n">
-        <v>6866584</v>
+        <v>6866687</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11340,32 +11340,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128502866</v>
+        <v>128502802</v>
       </c>
       <c r="B111" t="n">
-        <v>98509</v>
+        <v>79116</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11375,10 +11375,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471139</v>
+        <v>471256</v>
       </c>
       <c r="R111" t="n">
-        <v>6866727</v>
+        <v>6866728</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11440,7 +11440,7 @@
         <v>128502259</v>
       </c>
       <c r="B112" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11534,10 +11534,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128502509</v>
+        <v>128501973</v>
       </c>
       <c r="B113" t="n">
-        <v>78846</v>
+        <v>79148</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11545,21 +11545,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471315</v>
+        <v>471363</v>
       </c>
       <c r="R113" t="n">
-        <v>6866670</v>
+        <v>6866544</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11634,7 +11634,7 @@
         <v>128501097</v>
       </c>
       <c r="B114" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>128502607</v>
       </c>
       <c r="B115" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128501973</v>
+        <v>128502509</v>
       </c>
       <c r="B116" t="n">
-        <v>79121</v>
+        <v>78873</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11836,21 +11836,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471363</v>
+        <v>471315</v>
       </c>
       <c r="R116" t="n">
-        <v>6866544</v>
+        <v>6866670</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11925,7 +11925,7 @@
         <v>128501347</v>
       </c>
       <c r="B117" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>128501927</v>
       </c>
       <c r="B118" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>128501224</v>
       </c>
       <c r="B119" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>128502212</v>
       </c>
       <c r="B120" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12310,10 +12310,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128502291</v>
+        <v>128502189</v>
       </c>
       <c r="B121" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471320</v>
+        <v>471327</v>
       </c>
       <c r="R121" t="n">
-        <v>6866609</v>
+        <v>6866591</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12407,10 +12407,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128502189</v>
+        <v>128502291</v>
       </c>
       <c r="B122" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12442,10 +12442,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>471327</v>
+        <v>471320</v>
       </c>
       <c r="R122" t="n">
-        <v>6866591</v>
+        <v>6866609</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12507,7 +12507,7 @@
         <v>128501253</v>
       </c>
       <c r="B123" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>128502309</v>
       </c>
       <c r="B124" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>128502178</v>
       </c>
       <c r="B125" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128375924</v>
+        <v>128373928</v>
       </c>
       <c r="B2" t="n">
-        <v>78847</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471255</v>
+        <v>471086</v>
       </c>
       <c r="R2" t="n">
-        <v>6866786</v>
+        <v>6866862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128374420</v>
+        <v>128375151</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>79148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471132</v>
+        <v>471135</v>
       </c>
       <c r="R3" t="n">
-        <v>6866856</v>
+        <v>6866819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128373928</v>
+        <v>128376373</v>
       </c>
       <c r="B4" t="n">
-        <v>79121</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471086</v>
+        <v>471330</v>
       </c>
       <c r="R4" t="n">
-        <v>6866862</v>
+        <v>6866787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128375151</v>
+        <v>128376618</v>
       </c>
       <c r="B5" t="n">
-        <v>79121</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471135</v>
+        <v>471331</v>
       </c>
       <c r="R5" t="n">
-        <v>6866819</v>
+        <v>6866715</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1066,7 @@
         <v>128374470</v>
       </c>
       <c r="B6" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,45 +1160,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128376373</v>
+        <v>128374420</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471330</v>
+        <v>471132</v>
       </c>
       <c r="R7" t="n">
-        <v>6866787</v>
+        <v>6866856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128376618</v>
+        <v>128375924</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471331</v>
+        <v>471255</v>
       </c>
       <c r="R8" t="n">
-        <v>6866715</v>
+        <v>6866786</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128375190</v>
+        <v>128376258</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471145</v>
+        <v>471292</v>
       </c>
       <c r="R9" t="n">
-        <v>6866802</v>
+        <v>6866805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128376258</v>
+        <v>128375168</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471292</v>
+        <v>471139</v>
       </c>
       <c r="R10" t="n">
-        <v>6866805</v>
+        <v>6866821</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128375168</v>
+        <v>128375190</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471139</v>
+        <v>471145</v>
       </c>
       <c r="R11" t="n">
-        <v>6866821</v>
+        <v>6866802</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,7 +1657,7 @@
         <v>128376197</v>
       </c>
       <c r="B12" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128374859</v>
+        <v>128376676</v>
       </c>
       <c r="B13" t="n">
-        <v>80195</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471125</v>
+        <v>471287</v>
       </c>
       <c r="R13" t="n">
-        <v>6866815</v>
+        <v>6866763</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128376676</v>
+        <v>128374859</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>80222</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471287</v>
+        <v>471125</v>
       </c>
       <c r="R14" t="n">
-        <v>6866763</v>
+        <v>6866815</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
         <v>128375275</v>
       </c>
       <c r="B15" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128374662</v>
+        <v>128375734</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471145</v>
+        <v>471234</v>
       </c>
       <c r="R16" t="n">
-        <v>6866824</v>
+        <v>6866765</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128375734</v>
+        <v>128374662</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471234</v>
+        <v>471145</v>
       </c>
       <c r="R17" t="n">
-        <v>6866765</v>
+        <v>6866824</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>128376712</v>
       </c>
       <c r="B18" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>128375959</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128375989</v>
       </c>
       <c r="B20" t="n">
-        <v>78061</v>
+        <v>78088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128375358</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128375214</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128375758</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>128376206</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128374452</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128375464</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128376736</v>
       </c>
       <c r="B27" t="n">
-        <v>78061</v>
+        <v>78088</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>128375560</v>
       </c>
       <c r="B28" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128374116</v>
+        <v>128376702</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>78519</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,21 +3319,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,13 +3343,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471107</v>
+        <v>471287</v>
       </c>
       <c r="R29" t="n">
-        <v>6866853</v>
+        <v>6866773</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128376702</v>
+        <v>128376574</v>
       </c>
       <c r="B30" t="n">
-        <v>78492</v>
+        <v>78874</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471287</v>
+        <v>471364</v>
       </c>
       <c r="R30" t="n">
-        <v>6866773</v>
+        <v>6866709</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3505,7 +3505,7 @@
         <v>128376636</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128376574</v>
+        <v>128374116</v>
       </c>
       <c r="B32" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471364</v>
+        <v>471107</v>
       </c>
       <c r="R32" t="n">
-        <v>6866709</v>
+        <v>6866853</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>128375289</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>128375249</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>128375794</v>
       </c>
       <c r="B35" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3987,10 +3987,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128376382</v>
+        <v>128374814</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471342</v>
+        <v>471137</v>
       </c>
       <c r="R36" t="n">
-        <v>6866780</v>
+        <v>6866828</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4058,6 +4058,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4084,10 +4089,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128374814</v>
+        <v>128376382</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4119,10 +4124,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471137</v>
+        <v>471342</v>
       </c>
       <c r="R37" t="n">
-        <v>6866828</v>
+        <v>6866780</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4155,11 +4160,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4189,7 +4189,7 @@
         <v>128373989</v>
       </c>
       <c r="B38" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>128374436</v>
       </c>
       <c r="B39" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374500</v>
+        <v>128376649</v>
       </c>
       <c r="B40" t="n">
-        <v>79121</v>
+        <v>79116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4400,21 +4400,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471134</v>
+        <v>471300</v>
       </c>
       <c r="R40" t="n">
-        <v>6866834</v>
+        <v>6866735</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4486,10 +4486,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128376649</v>
+        <v>128374500</v>
       </c>
       <c r="B41" t="n">
-        <v>79089</v>
+        <v>79148</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4497,21 +4497,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471300</v>
+        <v>471134</v>
       </c>
       <c r="R41" t="n">
-        <v>6866735</v>
+        <v>6866834</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4586,7 +4586,7 @@
         <v>128375508</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4680,45 +4680,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128375808</v>
+        <v>128376462</v>
       </c>
       <c r="B43" t="n">
-        <v>79089</v>
+        <v>92068</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471247</v>
+        <v>471351</v>
       </c>
       <c r="R43" t="n">
-        <v>6866787</v>
+        <v>6866748</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4751,6 +4760,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4777,10 +4791,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128375498</v>
+        <v>128375808</v>
       </c>
       <c r="B44" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4812,10 +4826,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471198</v>
+        <v>471247</v>
       </c>
       <c r="R44" t="n">
-        <v>6866776</v>
+        <v>6866787</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4874,54 +4888,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128376462</v>
+        <v>128375498</v>
       </c>
       <c r="B45" t="n">
-        <v>92041</v>
+        <v>79116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471351</v>
+        <v>471198</v>
       </c>
       <c r="R45" t="n">
-        <v>6866748</v>
+        <v>6866776</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4954,11 +4959,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4988,7 +4988,7 @@
         <v>128375307</v>
       </c>
       <c r="B46" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128375399</v>
+        <v>128376295</v>
       </c>
       <c r="B47" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471183</v>
+        <v>471321</v>
       </c>
       <c r="R47" t="n">
-        <v>6866790</v>
+        <v>6866820</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5179,10 +5179,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128376295</v>
+        <v>128375399</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5214,10 +5214,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>471321</v>
+        <v>471183</v>
       </c>
       <c r="R48" t="n">
-        <v>6866820</v>
+        <v>6866790</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5276,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128387779</v>
+        <v>128388207</v>
       </c>
       <c r="B49" t="n">
-        <v>98592</v>
+        <v>78873</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470744</v>
+        <v>470789</v>
       </c>
       <c r="R49" t="n">
-        <v>6866736</v>
+        <v>6866739</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5376,7 +5376,7 @@
         <v>128388103</v>
       </c>
       <c r="B50" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5470,32 +5470,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128388207</v>
+        <v>128387779</v>
       </c>
       <c r="B51" t="n">
-        <v>78846</v>
+        <v>98619</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470789</v>
+        <v>470744</v>
       </c>
       <c r="R51" t="n">
-        <v>6866739</v>
+        <v>6866736</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5570,7 +5570,7 @@
         <v>128387977</v>
       </c>
       <c r="B52" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128389953</v>
+        <v>128389894</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>471200</v>
+        <v>471207</v>
       </c>
       <c r="R53" t="n">
-        <v>6866759</v>
+        <v>6866729</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5770,10 +5770,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128389894</v>
+        <v>128389953</v>
       </c>
       <c r="B54" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5805,13 +5805,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>471207</v>
+        <v>471200</v>
       </c>
       <c r="R54" t="n">
-        <v>6866729</v>
+        <v>6866759</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>128387790</v>
       </c>
       <c r="B55" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>128387828</v>
       </c>
       <c r="B56" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>128388996</v>
       </c>
       <c r="B57" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>128388496</v>
       </c>
       <c r="B58" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>128389324</v>
       </c>
       <c r="B59" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>128387936</v>
       </c>
       <c r="B60" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128388778</v>
+        <v>128389262</v>
       </c>
       <c r="B61" t="n">
-        <v>79168</v>
+        <v>80222</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,10 +6493,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>470995</v>
+        <v>471168</v>
       </c>
       <c r="R61" t="n">
-        <v>6866711</v>
+        <v>6866647</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128389262</v>
+        <v>128388778</v>
       </c>
       <c r="B62" t="n">
-        <v>80195</v>
+        <v>79195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6566,21 +6566,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471168</v>
+        <v>470995</v>
       </c>
       <c r="R62" t="n">
-        <v>6866647</v>
+        <v>6866711</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128389329</v>
+        <v>128389511</v>
       </c>
       <c r="B63" t="n">
-        <v>78846</v>
+        <v>80221</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6663,21 +6663,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471172</v>
+        <v>471237</v>
       </c>
       <c r="R63" t="n">
-        <v>6866632</v>
+        <v>6866588</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128389511</v>
+        <v>128389329</v>
       </c>
       <c r="B64" t="n">
-        <v>80194</v>
+        <v>78873</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471237</v>
+        <v>471172</v>
       </c>
       <c r="R64" t="n">
-        <v>6866588</v>
+        <v>6866632</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6849,7 +6849,7 @@
         <v>128387227</v>
       </c>
       <c r="B65" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128389855</v>
+        <v>128387286</v>
       </c>
       <c r="B66" t="n">
-        <v>57849</v>
+        <v>80221</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,21 +6954,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>471241</v>
+        <v>470551</v>
       </c>
       <c r="R66" t="n">
-        <v>6866622</v>
+        <v>6866872</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7014,11 +7014,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7045,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128387286</v>
+        <v>128389855</v>
       </c>
       <c r="B67" t="n">
-        <v>80194</v>
+        <v>57876</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7056,21 +7051,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7080,13 +7075,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>470551</v>
+        <v>471241</v>
       </c>
       <c r="R67" t="n">
-        <v>6866872</v>
+        <v>6866622</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7116,6 +7111,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7142,10 +7142,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128388804</v>
+        <v>128389069</v>
       </c>
       <c r="B68" t="n">
-        <v>79121</v>
+        <v>80221</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>470987</v>
+        <v>471158</v>
       </c>
       <c r="R68" t="n">
-        <v>6866706</v>
+        <v>6866734</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128389227</v>
+        <v>128389187</v>
       </c>
       <c r="B69" t="n">
-        <v>79121</v>
+        <v>78873</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,10 +7274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471156</v>
+        <v>471196</v>
       </c>
       <c r="R69" t="n">
-        <v>6866665</v>
+        <v>6866706</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7336,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128389187</v>
+        <v>128389227</v>
       </c>
       <c r="B70" t="n">
-        <v>78846</v>
+        <v>79148</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7347,21 +7347,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471196</v>
+        <v>471156</v>
       </c>
       <c r="R70" t="n">
-        <v>6866706</v>
+        <v>6866665</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128389069</v>
+        <v>128388804</v>
       </c>
       <c r="B71" t="n">
-        <v>80194</v>
+        <v>79148</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471158</v>
+        <v>470987</v>
       </c>
       <c r="R71" t="n">
-        <v>6866734</v>
+        <v>6866706</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128388766</v>
+        <v>128388646</v>
       </c>
       <c r="B72" t="n">
-        <v>79168</v>
+        <v>79148</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470981</v>
+        <v>470945</v>
       </c>
       <c r="R72" t="n">
-        <v>6866714</v>
+        <v>6866709</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128389641</v>
+        <v>128388766</v>
       </c>
       <c r="B73" t="n">
-        <v>80194</v>
+        <v>79195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7638,21 +7638,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471241</v>
+        <v>470981</v>
       </c>
       <c r="R73" t="n">
-        <v>6866656</v>
+        <v>6866714</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7724,10 +7724,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128388646</v>
+        <v>128389641</v>
       </c>
       <c r="B74" t="n">
-        <v>79121</v>
+        <v>80221</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>470945</v>
+        <v>471241</v>
       </c>
       <c r="R74" t="n">
-        <v>6866709</v>
+        <v>6866656</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7824,7 +7824,7 @@
         <v>128387695</v>
       </c>
       <c r="B75" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>128388053</v>
       </c>
       <c r="B76" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>128387629</v>
       </c>
       <c r="B77" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8121,10 +8121,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128388815</v>
+        <v>128389403</v>
       </c>
       <c r="B78" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8132,21 +8132,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470992</v>
+        <v>471187</v>
       </c>
       <c r="R78" t="n">
-        <v>6866696</v>
+        <v>6866586</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8218,45 +8218,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128388714</v>
+        <v>128388416</v>
       </c>
       <c r="B79" t="n">
-        <v>79089</v>
+        <v>98619</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>470987</v>
+        <v>470816</v>
       </c>
       <c r="R79" t="n">
-        <v>6866714</v>
+        <v>6866722</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8315,10 +8324,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128389886</v>
+        <v>128388815</v>
       </c>
       <c r="B80" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8350,10 +8359,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471211</v>
+        <v>470992</v>
       </c>
       <c r="R80" t="n">
-        <v>6866717</v>
+        <v>6866696</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8412,54 +8421,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128388416</v>
+        <v>128389886</v>
       </c>
       <c r="B81" t="n">
-        <v>98592</v>
+        <v>79116</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>470816</v>
+        <v>471211</v>
       </c>
       <c r="R81" t="n">
-        <v>6866722</v>
+        <v>6866717</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8518,10 +8518,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128389403</v>
+        <v>128388714</v>
       </c>
       <c r="B82" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8529,21 +8529,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471187</v>
+        <v>470987</v>
       </c>
       <c r="R82" t="n">
-        <v>6866586</v>
+        <v>6866714</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8618,7 +8618,7 @@
         <v>128387736</v>
       </c>
       <c r="B83" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>128389124</v>
       </c>
       <c r="B84" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>128387659</v>
       </c>
       <c r="B85" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>128387292</v>
       </c>
       <c r="B86" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128389901</v>
+        <v>128388228</v>
       </c>
       <c r="B87" t="n">
-        <v>79089</v>
+        <v>98619</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471209</v>
+        <v>470788</v>
       </c>
       <c r="R87" t="n">
-        <v>6866743</v>
+        <v>6866725</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9109,32 +9109,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128388228</v>
+        <v>128389901</v>
       </c>
       <c r="B88" t="n">
-        <v>98592</v>
+        <v>79116</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>470788</v>
+        <v>471209</v>
       </c>
       <c r="R88" t="n">
-        <v>6866725</v>
+        <v>6866743</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9209,7 +9209,7 @@
         <v>128389213</v>
       </c>
       <c r="B89" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>128389351</v>
       </c>
       <c r="B90" t="n">
-        <v>78061</v>
+        <v>78088</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>128388690</v>
       </c>
       <c r="B91" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128388173</v>
+        <v>128389587</v>
       </c>
       <c r="B92" t="n">
-        <v>78755</v>
+        <v>80222</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>470786</v>
+        <v>471274</v>
       </c>
       <c r="R92" t="n">
-        <v>6866737</v>
+        <v>6866626</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128389918</v>
+        <v>128388173</v>
       </c>
       <c r="B93" t="n">
-        <v>79089</v>
+        <v>78782</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471210</v>
+        <v>470786</v>
       </c>
       <c r="R93" t="n">
-        <v>6866755</v>
+        <v>6866737</v>
       </c>
       <c r="S93" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9691,10 +9691,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128389587</v>
+        <v>128389918</v>
       </c>
       <c r="B94" t="n">
-        <v>80195</v>
+        <v>79116</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9702,21 +9702,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9726,13 +9726,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471274</v>
+        <v>471210</v>
       </c>
       <c r="R94" t="n">
-        <v>6866626</v>
+        <v>6866755</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>128389286</v>
       </c>
       <c r="B95" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10273,32 +10273,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128502704</v>
+        <v>128501140</v>
       </c>
       <c r="B100" t="n">
-        <v>91459</v>
+        <v>79116</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471366</v>
+        <v>471253</v>
       </c>
       <c r="R100" t="n">
-        <v>6866720</v>
+        <v>6866704</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10370,32 +10370,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128501140</v>
+        <v>128502704</v>
       </c>
       <c r="B101" t="n">
-        <v>79116</v>
+        <v>91459</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471253</v>
+        <v>471366</v>
       </c>
       <c r="R101" t="n">
-        <v>6866704</v>
+        <v>6866720</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12310,7 +12310,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128502189</v>
+        <v>128502291</v>
       </c>
       <c r="B121" t="n">
         <v>79148</v>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471327</v>
+        <v>471320</v>
       </c>
       <c r="R121" t="n">
-        <v>6866591</v>
+        <v>6866609</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12407,7 +12407,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128502291</v>
+        <v>128502189</v>
       </c>
       <c r="B122" t="n">
         <v>79148</v>
@@ -12442,10 +12442,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>471320</v>
+        <v>471327</v>
       </c>
       <c r="R122" t="n">
-        <v>6866609</v>
+        <v>6866591</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128376618</v>
+        <v>128374470</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>78873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471331</v>
+        <v>471139</v>
       </c>
       <c r="R5" t="n">
-        <v>6866715</v>
+        <v>6866835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128374470</v>
+        <v>128376618</v>
       </c>
       <c r="B6" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471139</v>
+        <v>471331</v>
       </c>
       <c r="R6" t="n">
-        <v>6866835</v>
+        <v>6866715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,54 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128374420</v>
+        <v>128375924</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>78874</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471132</v>
+        <v>471255</v>
       </c>
       <c r="R7" t="n">
-        <v>6866856</v>
+        <v>6866786</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,45 +1257,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128375924</v>
+        <v>128374420</v>
       </c>
       <c r="B8" t="n">
-        <v>78874</v>
+        <v>98619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471255</v>
+        <v>471132</v>
       </c>
       <c r="R8" t="n">
-        <v>6866786</v>
+        <v>6866856</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128376258</v>
+        <v>128376197</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471292</v>
+        <v>471280</v>
       </c>
       <c r="R9" t="n">
-        <v>6866805</v>
+        <v>6866807</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128375168</v>
+        <v>128376258</v>
       </c>
       <c r="B10" t="n">
         <v>79116</v>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471139</v>
+        <v>471292</v>
       </c>
       <c r="R10" t="n">
-        <v>6866821</v>
+        <v>6866805</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128375190</v>
+        <v>128375168</v>
       </c>
       <c r="B11" t="n">
         <v>79116</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471145</v>
+        <v>471139</v>
       </c>
       <c r="R11" t="n">
-        <v>6866802</v>
+        <v>6866821</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128376197</v>
+        <v>128375190</v>
       </c>
       <c r="B12" t="n">
-        <v>78874</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471280</v>
+        <v>471145</v>
       </c>
       <c r="R12" t="n">
-        <v>6866807</v>
+        <v>6866802</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128376676</v>
+        <v>128374859</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>80222</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471287</v>
+        <v>471125</v>
       </c>
       <c r="R13" t="n">
-        <v>6866763</v>
+        <v>6866815</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128374859</v>
+        <v>128376676</v>
       </c>
       <c r="B14" t="n">
-        <v>80222</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471125</v>
+        <v>471287</v>
       </c>
       <c r="R14" t="n">
-        <v>6866815</v>
+        <v>6866763</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128375959</v>
+        <v>128375989</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>78088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471266</v>
+        <v>471276</v>
       </c>
       <c r="R19" t="n">
-        <v>6866792</v>
+        <v>6866805</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128375989</v>
+        <v>128375959</v>
       </c>
       <c r="B20" t="n">
-        <v>78088</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471276</v>
+        <v>471266</v>
       </c>
       <c r="R20" t="n">
-        <v>6866805</v>
+        <v>6866792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128375358</v>
+        <v>128375214</v>
       </c>
       <c r="B21" t="n">
         <v>79116</v>
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471166</v>
+        <v>471144</v>
       </c>
       <c r="R21" t="n">
-        <v>6866785</v>
+        <v>6866814</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2624,7 +2624,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128375214</v>
+        <v>128375358</v>
       </c>
       <c r="B22" t="n">
         <v>79116</v>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471144</v>
+        <v>471166</v>
       </c>
       <c r="R22" t="n">
-        <v>6866814</v>
+        <v>6866785</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128376736</v>
+        <v>128375560</v>
       </c>
       <c r="B27" t="n">
-        <v>78088</v>
+        <v>57876</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471282</v>
+        <v>471219</v>
       </c>
       <c r="R27" t="n">
-        <v>6866783</v>
+        <v>6866779</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3180,6 +3180,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3206,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128375560</v>
+        <v>128376736</v>
       </c>
       <c r="B28" t="n">
-        <v>57876</v>
+        <v>78088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3217,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3241,13 +3246,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471219</v>
+        <v>471282</v>
       </c>
       <c r="R28" t="n">
-        <v>6866779</v>
+        <v>6866783</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3277,11 +3282,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128376702</v>
+        <v>128376574</v>
       </c>
       <c r="B29" t="n">
-        <v>78519</v>
+        <v>78874</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,21 +3319,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471287</v>
+        <v>471364</v>
       </c>
       <c r="R29" t="n">
-        <v>6866773</v>
+        <v>6866709</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128376574</v>
+        <v>128376636</v>
       </c>
       <c r="B30" t="n">
-        <v>78874</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471364</v>
+        <v>471320</v>
       </c>
       <c r="R30" t="n">
-        <v>6866709</v>
+        <v>6866734</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128376636</v>
+        <v>128376702</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>78519</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,13 +3537,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471320</v>
+        <v>471287</v>
       </c>
       <c r="R31" t="n">
-        <v>6866734</v>
+        <v>6866773</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128375289</v>
+        <v>128375794</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471165</v>
+        <v>471241</v>
       </c>
       <c r="R33" t="n">
-        <v>6866794</v>
+        <v>6866786</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128375249</v>
+        <v>128375289</v>
       </c>
       <c r="B34" t="n">
         <v>79116</v>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471158</v>
+        <v>471165</v>
       </c>
       <c r="R34" t="n">
-        <v>6866800</v>
+        <v>6866794</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128375794</v>
+        <v>128375249</v>
       </c>
       <c r="B35" t="n">
-        <v>78874</v>
+        <v>79116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471241</v>
+        <v>471158</v>
       </c>
       <c r="R35" t="n">
-        <v>6866786</v>
+        <v>6866800</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128376649</v>
+        <v>128374500</v>
       </c>
       <c r="B40" t="n">
-        <v>79116</v>
+        <v>79148</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4400,21 +4400,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471300</v>
+        <v>471134</v>
       </c>
       <c r="R40" t="n">
-        <v>6866735</v>
+        <v>6866834</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4486,10 +4486,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128374500</v>
+        <v>128376649</v>
       </c>
       <c r="B41" t="n">
-        <v>79148</v>
+        <v>79116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4497,21 +4497,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471134</v>
+        <v>471300</v>
       </c>
       <c r="R41" t="n">
-        <v>6866834</v>
+        <v>6866735</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5276,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128388207</v>
+        <v>128387779</v>
       </c>
       <c r="B49" t="n">
-        <v>78873</v>
+        <v>98619</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470789</v>
+        <v>470744</v>
       </c>
       <c r="R49" t="n">
-        <v>6866739</v>
+        <v>6866736</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5470,32 +5470,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128387779</v>
+        <v>128388207</v>
       </c>
       <c r="B51" t="n">
-        <v>98619</v>
+        <v>78873</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470744</v>
+        <v>470789</v>
       </c>
       <c r="R51" t="n">
-        <v>6866736</v>
+        <v>6866739</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5867,32 +5867,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128387790</v>
+        <v>128387828</v>
       </c>
       <c r="B55" t="n">
-        <v>98619</v>
+        <v>78874</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5902,13 +5902,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470732</v>
+        <v>470743</v>
       </c>
       <c r="R55" t="n">
-        <v>6866727</v>
+        <v>6866698</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5964,32 +5964,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128387828</v>
+        <v>128387790</v>
       </c>
       <c r="B56" t="n">
-        <v>78874</v>
+        <v>98619</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5999,13 +5999,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>470743</v>
+        <v>470732</v>
       </c>
       <c r="R56" t="n">
-        <v>6866698</v>
+        <v>6866727</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128389262</v>
+        <v>128388778</v>
       </c>
       <c r="B61" t="n">
-        <v>80222</v>
+        <v>79195</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,10 +6493,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471168</v>
+        <v>470995</v>
       </c>
       <c r="R61" t="n">
-        <v>6866647</v>
+        <v>6866711</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128388778</v>
+        <v>128389262</v>
       </c>
       <c r="B62" t="n">
-        <v>79195</v>
+        <v>80222</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6566,21 +6566,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>470995</v>
+        <v>471168</v>
       </c>
       <c r="R62" t="n">
-        <v>6866711</v>
+        <v>6866647</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7142,10 +7142,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128389069</v>
+        <v>128389227</v>
       </c>
       <c r="B68" t="n">
-        <v>80221</v>
+        <v>79148</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471158</v>
+        <v>471156</v>
       </c>
       <c r="R68" t="n">
-        <v>6866734</v>
+        <v>6866665</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128389187</v>
+        <v>128388804</v>
       </c>
       <c r="B69" t="n">
-        <v>78873</v>
+        <v>79148</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471196</v>
+        <v>470987</v>
       </c>
       <c r="R69" t="n">
         <v>6866706</v>
@@ -7336,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128389227</v>
+        <v>128389069</v>
       </c>
       <c r="B70" t="n">
-        <v>79148</v>
+        <v>80221</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7347,21 +7347,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471156</v>
+        <v>471158</v>
       </c>
       <c r="R70" t="n">
-        <v>6866665</v>
+        <v>6866734</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128388804</v>
+        <v>128389187</v>
       </c>
       <c r="B71" t="n">
-        <v>79148</v>
+        <v>78873</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>470987</v>
+        <v>471196</v>
       </c>
       <c r="R71" t="n">
         <v>6866706</v>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128388646</v>
+        <v>128388766</v>
       </c>
       <c r="B72" t="n">
-        <v>79148</v>
+        <v>79195</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470945</v>
+        <v>470981</v>
       </c>
       <c r="R72" t="n">
-        <v>6866709</v>
+        <v>6866714</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128388766</v>
+        <v>128388646</v>
       </c>
       <c r="B73" t="n">
-        <v>79195</v>
+        <v>79148</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7638,21 +7638,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470981</v>
+        <v>470945</v>
       </c>
       <c r="R73" t="n">
-        <v>6866714</v>
+        <v>6866709</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8121,10 +8121,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128389403</v>
+        <v>128388815</v>
       </c>
       <c r="B78" t="n">
-        <v>78874</v>
+        <v>79116</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8132,21 +8132,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471187</v>
+        <v>470992</v>
       </c>
       <c r="R78" t="n">
-        <v>6866586</v>
+        <v>6866696</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8218,54 +8218,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128388416</v>
+        <v>128389886</v>
       </c>
       <c r="B79" t="n">
-        <v>98619</v>
+        <v>79116</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>470816</v>
+        <v>471211</v>
       </c>
       <c r="R79" t="n">
-        <v>6866722</v>
+        <v>6866717</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8324,7 +8315,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128388815</v>
+        <v>128388714</v>
       </c>
       <c r="B80" t="n">
         <v>79116</v>
@@ -8359,10 +8350,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>470992</v>
+        <v>470987</v>
       </c>
       <c r="R80" t="n">
-        <v>6866696</v>
+        <v>6866714</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8421,45 +8412,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128389886</v>
+        <v>128388416</v>
       </c>
       <c r="B81" t="n">
-        <v>79116</v>
+        <v>98619</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471211</v>
+        <v>470816</v>
       </c>
       <c r="R81" t="n">
-        <v>6866717</v>
+        <v>6866722</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8518,10 +8518,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128388714</v>
+        <v>128389403</v>
       </c>
       <c r="B82" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8529,21 +8529,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>470987</v>
+        <v>471187</v>
       </c>
       <c r="R82" t="n">
-        <v>6866714</v>
+        <v>6866586</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128389901</v>
+        <v>128389213</v>
       </c>
       <c r="B88" t="n">
-        <v>79116</v>
+        <v>80221</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471209</v>
+        <v>471148</v>
       </c>
       <c r="R88" t="n">
-        <v>6866743</v>
+        <v>6866668</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9206,10 +9206,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128389213</v>
+        <v>128389901</v>
       </c>
       <c r="B89" t="n">
-        <v>80221</v>
+        <v>79116</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9217,21 +9217,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471148</v>
+        <v>471209</v>
       </c>
       <c r="R89" t="n">
-        <v>6866668</v>
+        <v>6866743</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128389587</v>
+        <v>128388173</v>
       </c>
       <c r="B92" t="n">
-        <v>80222</v>
+        <v>78782</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471274</v>
+        <v>470786</v>
       </c>
       <c r="R92" t="n">
-        <v>6866626</v>
+        <v>6866737</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128388173</v>
+        <v>128389587</v>
       </c>
       <c r="B93" t="n">
-        <v>78782</v>
+        <v>80222</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9629,10 +9629,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>470786</v>
+        <v>471274</v>
       </c>
       <c r="R93" t="n">
-        <v>6866737</v>
+        <v>6866626</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9888,7 +9888,7 @@
         <v>128502381</v>
       </c>
       <c r="B96" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>128502263</v>
       </c>
       <c r="B97" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>128501285</v>
       </c>
       <c r="B98" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>128501083</v>
       </c>
       <c r="B99" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10273,32 +10273,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128501140</v>
+        <v>128502704</v>
       </c>
       <c r="B100" t="n">
-        <v>79116</v>
+        <v>91464</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471253</v>
+        <v>471366</v>
       </c>
       <c r="R100" t="n">
-        <v>6866704</v>
+        <v>6866720</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10370,32 +10370,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128502704</v>
+        <v>128501140</v>
       </c>
       <c r="B101" t="n">
-        <v>91459</v>
+        <v>79120</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471366</v>
+        <v>471253</v>
       </c>
       <c r="R101" t="n">
-        <v>6866720</v>
+        <v>6866704</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10470,7 +10470,7 @@
         <v>128501794</v>
       </c>
       <c r="B102" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>128502548</v>
       </c>
       <c r="B103" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>128501127</v>
       </c>
       <c r="B104" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>128501181</v>
       </c>
       <c r="B105" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>128501480</v>
       </c>
       <c r="B106" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>128501144</v>
       </c>
       <c r="B107" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11049,32 +11049,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128502866</v>
+        <v>128501209</v>
       </c>
       <c r="B108" t="n">
-        <v>98536</v>
+        <v>78877</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471139</v>
+        <v>471244</v>
       </c>
       <c r="R108" t="n">
-        <v>6866727</v>
+        <v>6866687</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11149,7 +11149,7 @@
         <v>128502100</v>
       </c>
       <c r="B109" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11243,10 +11243,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128501209</v>
+        <v>128502802</v>
       </c>
       <c r="B110" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11254,21 +11254,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471244</v>
+        <v>471256</v>
       </c>
       <c r="R110" t="n">
-        <v>6866687</v>
+        <v>6866728</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11340,32 +11340,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128502802</v>
+        <v>128502866</v>
       </c>
       <c r="B111" t="n">
-        <v>79116</v>
+        <v>98542</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11375,10 +11375,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471256</v>
+        <v>471139</v>
       </c>
       <c r="R111" t="n">
-        <v>6866728</v>
+        <v>6866727</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11440,7 +11440,7 @@
         <v>128502259</v>
       </c>
       <c r="B112" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>128501973</v>
       </c>
       <c r="B113" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>128501097</v>
       </c>
       <c r="B114" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11728,10 +11728,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128502607</v>
+        <v>128502509</v>
       </c>
       <c r="B115" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11763,10 +11763,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471349</v>
+        <v>471315</v>
       </c>
       <c r="R115" t="n">
-        <v>6866695</v>
+        <v>6866670</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128502509</v>
+        <v>128502607</v>
       </c>
       <c r="B116" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471315</v>
+        <v>471349</v>
       </c>
       <c r="R116" t="n">
-        <v>6866670</v>
+        <v>6866695</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11925,7 +11925,7 @@
         <v>128501347</v>
       </c>
       <c r="B117" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>128501927</v>
       </c>
       <c r="B118" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>128501224</v>
       </c>
       <c r="B119" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>128502212</v>
       </c>
       <c r="B120" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>128502291</v>
       </c>
       <c r="B121" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>128502189</v>
       </c>
       <c r="B122" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>128501253</v>
       </c>
       <c r="B123" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>128502309</v>
       </c>
       <c r="B124" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>128502178</v>
       </c>
       <c r="B125" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128373928</v>
+        <v>128374420</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471086</v>
+        <v>471132</v>
       </c>
       <c r="R2" t="n">
-        <v>6866862</v>
+        <v>6866856</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128375151</v>
+        <v>128375924</v>
       </c>
       <c r="B3" t="n">
-        <v>79148</v>
+        <v>78878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471135</v>
+        <v>471255</v>
       </c>
       <c r="R3" t="n">
-        <v>6866819</v>
+        <v>6866786</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128376373</v>
+        <v>128373928</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471330</v>
+        <v>471086</v>
       </c>
       <c r="R4" t="n">
-        <v>6866787</v>
+        <v>6866862</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128374470</v>
+        <v>128376373</v>
       </c>
       <c r="B5" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +986,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471139</v>
+        <v>471330</v>
       </c>
       <c r="R5" t="n">
-        <v>6866835</v>
+        <v>6866787</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128376618</v>
+        <v>128374470</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>78877</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471331</v>
+        <v>471139</v>
       </c>
       <c r="R6" t="n">
-        <v>6866715</v>
+        <v>6866835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128375924</v>
+        <v>128376618</v>
       </c>
       <c r="B7" t="n">
-        <v>78874</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471255</v>
+        <v>471331</v>
       </c>
       <c r="R7" t="n">
-        <v>6866786</v>
+        <v>6866715</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,54 +1266,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128374420</v>
+        <v>128375151</v>
       </c>
       <c r="B8" t="n">
-        <v>98619</v>
+        <v>79152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471132</v>
+        <v>471135</v>
       </c>
       <c r="R8" t="n">
-        <v>6866856</v>
+        <v>6866819</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128376197</v>
+        <v>128376258</v>
       </c>
       <c r="B9" t="n">
-        <v>78874</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471280</v>
+        <v>471292</v>
       </c>
       <c r="R9" t="n">
-        <v>6866807</v>
+        <v>6866805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128376258</v>
+        <v>128375168</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471292</v>
+        <v>471139</v>
       </c>
       <c r="R10" t="n">
-        <v>6866805</v>
+        <v>6866821</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128375168</v>
+        <v>128375190</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471139</v>
+        <v>471145</v>
       </c>
       <c r="R11" t="n">
-        <v>6866821</v>
+        <v>6866802</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128375190</v>
+        <v>128376197</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>78878</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471145</v>
+        <v>471280</v>
       </c>
       <c r="R12" t="n">
-        <v>6866802</v>
+        <v>6866807</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128374859</v>
+        <v>128376676</v>
       </c>
       <c r="B13" t="n">
-        <v>80222</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471125</v>
+        <v>471287</v>
       </c>
       <c r="R13" t="n">
-        <v>6866815</v>
+        <v>6866763</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128376676</v>
+        <v>128374859</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>80226</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471287</v>
+        <v>471125</v>
       </c>
       <c r="R14" t="n">
-        <v>6866763</v>
+        <v>6866815</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128375275</v>
+        <v>128376712</v>
       </c>
       <c r="B15" t="n">
-        <v>79148</v>
+        <v>79710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471162</v>
+        <v>471282</v>
       </c>
       <c r="R15" t="n">
-        <v>6866793</v>
+        <v>6866780</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128375734</v>
+        <v>128375275</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79152</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471234</v>
+        <v>471162</v>
       </c>
       <c r="R16" t="n">
-        <v>6866765</v>
+        <v>6866793</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128374662</v>
+        <v>128375734</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471145</v>
+        <v>471234</v>
       </c>
       <c r="R17" t="n">
-        <v>6866824</v>
+        <v>6866765</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128376712</v>
+        <v>128374662</v>
       </c>
       <c r="B18" t="n">
-        <v>79706</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471282</v>
+        <v>471145</v>
       </c>
       <c r="R18" t="n">
-        <v>6866780</v>
+        <v>6866824</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2336,7 +2336,7 @@
         <v>128375989</v>
       </c>
       <c r="B19" t="n">
-        <v>78088</v>
+        <v>78092</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128375959</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128375214</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128375358</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128375758</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>128376206</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128374452</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128375464</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>128376736</v>
       </c>
       <c r="B28" t="n">
-        <v>78088</v>
+        <v>78092</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>128376574</v>
       </c>
       <c r="B29" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>128376636</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>128376702</v>
       </c>
       <c r="B31" t="n">
-        <v>78519</v>
+        <v>78523</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>128374116</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128375794</v>
+        <v>128375289</v>
       </c>
       <c r="B33" t="n">
-        <v>78874</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471241</v>
+        <v>471165</v>
       </c>
       <c r="R33" t="n">
-        <v>6866786</v>
+        <v>6866794</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128375289</v>
+        <v>128375249</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471165</v>
+        <v>471158</v>
       </c>
       <c r="R34" t="n">
-        <v>6866794</v>
+        <v>6866800</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128375249</v>
+        <v>128375794</v>
       </c>
       <c r="B35" t="n">
-        <v>79116</v>
+        <v>78878</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471158</v>
+        <v>471241</v>
       </c>
       <c r="R35" t="n">
-        <v>6866800</v>
+        <v>6866786</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
         <v>128374814</v>
       </c>
       <c r="B36" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>128376382</v>
       </c>
       <c r="B37" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>128373989</v>
       </c>
       <c r="B38" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>128374436</v>
       </c>
       <c r="B39" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374500</v>
+        <v>128376649</v>
       </c>
       <c r="B40" t="n">
-        <v>79148</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4400,21 +4400,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471134</v>
+        <v>471300</v>
       </c>
       <c r="R40" t="n">
-        <v>6866834</v>
+        <v>6866735</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4486,10 +4486,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128376649</v>
+        <v>128375508</v>
       </c>
       <c r="B41" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471300</v>
+        <v>471209</v>
       </c>
       <c r="R41" t="n">
-        <v>6866735</v>
+        <v>6866776</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4583,10 +4583,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128375508</v>
+        <v>128374500</v>
       </c>
       <c r="B42" t="n">
-        <v>79116</v>
+        <v>79152</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4594,21 +4594,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471209</v>
+        <v>471134</v>
       </c>
       <c r="R42" t="n">
-        <v>6866776</v>
+        <v>6866834</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4680,54 +4680,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128376462</v>
+        <v>128375808</v>
       </c>
       <c r="B43" t="n">
-        <v>92068</v>
+        <v>79120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471351</v>
+        <v>471247</v>
       </c>
       <c r="R43" t="n">
-        <v>6866748</v>
+        <v>6866787</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4760,11 +4751,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4791,10 +4777,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128375808</v>
+        <v>128375498</v>
       </c>
       <c r="B44" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4826,10 +4812,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471247</v>
+        <v>471198</v>
       </c>
       <c r="R44" t="n">
-        <v>6866787</v>
+        <v>6866776</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4888,45 +4874,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128375498</v>
+        <v>128376462</v>
       </c>
       <c r="B45" t="n">
-        <v>79116</v>
+        <v>92078</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471198</v>
+        <v>471351</v>
       </c>
       <c r="R45" t="n">
-        <v>6866776</v>
+        <v>6866748</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4959,6 +4954,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4988,7 +4988,7 @@
         <v>128375307</v>
       </c>
       <c r="B46" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>128376295</v>
       </c>
       <c r="B47" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>128375399</v>
       </c>
       <c r="B48" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5276,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128387779</v>
+        <v>128388207</v>
       </c>
       <c r="B49" t="n">
-        <v>98619</v>
+        <v>78877</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470744</v>
+        <v>470789</v>
       </c>
       <c r="R49" t="n">
-        <v>6866736</v>
+        <v>6866739</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128388103</v>
+        <v>128387779</v>
       </c>
       <c r="B50" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470763</v>
+        <v>470744</v>
       </c>
       <c r="R50" t="n">
-        <v>6866753</v>
+        <v>6866736</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,32 +5470,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128388207</v>
+        <v>128388103</v>
       </c>
       <c r="B51" t="n">
-        <v>78873</v>
+        <v>98632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470789</v>
+        <v>470763</v>
       </c>
       <c r="R51" t="n">
-        <v>6866739</v>
+        <v>6866753</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5570,7 +5570,7 @@
         <v>128387977</v>
       </c>
       <c r="B52" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>128389894</v>
       </c>
       <c r="B53" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>128389953</v>
       </c>
       <c r="B54" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5867,32 +5867,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128387828</v>
+        <v>128387790</v>
       </c>
       <c r="B55" t="n">
-        <v>78874</v>
+        <v>98632</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5902,13 +5902,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470743</v>
+        <v>470732</v>
       </c>
       <c r="R55" t="n">
-        <v>6866698</v>
+        <v>6866727</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5964,32 +5964,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128387790</v>
+        <v>128387828</v>
       </c>
       <c r="B56" t="n">
-        <v>98619</v>
+        <v>78878</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5999,13 +5999,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>470732</v>
+        <v>470743</v>
       </c>
       <c r="R56" t="n">
-        <v>6866727</v>
+        <v>6866698</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>128388996</v>
       </c>
       <c r="B57" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>128388496</v>
       </c>
       <c r="B58" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>128389324</v>
       </c>
       <c r="B59" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>128387936</v>
       </c>
       <c r="B60" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128388778</v>
+        <v>128389511</v>
       </c>
       <c r="B61" t="n">
-        <v>79195</v>
+        <v>80225</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,10 +6493,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>470995</v>
+        <v>471237</v>
       </c>
       <c r="R61" t="n">
-        <v>6866711</v>
+        <v>6866588</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128389262</v>
+        <v>128389329</v>
       </c>
       <c r="B62" t="n">
-        <v>80222</v>
+        <v>78877</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6566,21 +6566,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471168</v>
+        <v>471172</v>
       </c>
       <c r="R62" t="n">
-        <v>6866647</v>
+        <v>6866632</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128389511</v>
+        <v>128387227</v>
       </c>
       <c r="B63" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471237</v>
+        <v>470551</v>
       </c>
       <c r="R63" t="n">
-        <v>6866588</v>
+        <v>6866892</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128389329</v>
+        <v>128387286</v>
       </c>
       <c r="B64" t="n">
-        <v>78873</v>
+        <v>80225</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471172</v>
+        <v>470551</v>
       </c>
       <c r="R64" t="n">
-        <v>6866632</v>
+        <v>6866872</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128387227</v>
+        <v>128389262</v>
       </c>
       <c r="B65" t="n">
-        <v>80221</v>
+        <v>80226</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>470551</v>
+        <v>471168</v>
       </c>
       <c r="R65" t="n">
-        <v>6866892</v>
+        <v>6866647</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128387286</v>
+        <v>128388778</v>
       </c>
       <c r="B66" t="n">
-        <v>80221</v>
+        <v>79199</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,21 +6954,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470551</v>
+        <v>470995</v>
       </c>
       <c r="R66" t="n">
-        <v>6866872</v>
+        <v>6866711</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7142,10 +7142,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128389227</v>
+        <v>128389069</v>
       </c>
       <c r="B68" t="n">
-        <v>79148</v>
+        <v>80225</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471156</v>
+        <v>471158</v>
       </c>
       <c r="R68" t="n">
-        <v>6866665</v>
+        <v>6866734</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128388804</v>
+        <v>128389187</v>
       </c>
       <c r="B69" t="n">
-        <v>79148</v>
+        <v>78877</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>470987</v>
+        <v>471196</v>
       </c>
       <c r="R69" t="n">
         <v>6866706</v>
@@ -7336,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128389069</v>
+        <v>128389227</v>
       </c>
       <c r="B70" t="n">
-        <v>80221</v>
+        <v>79152</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7347,21 +7347,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471158</v>
+        <v>471156</v>
       </c>
       <c r="R70" t="n">
-        <v>6866734</v>
+        <v>6866665</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128389187</v>
+        <v>128388804</v>
       </c>
       <c r="B71" t="n">
-        <v>78873</v>
+        <v>79152</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471196</v>
+        <v>470987</v>
       </c>
       <c r="R71" t="n">
         <v>6866706</v>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128388766</v>
+        <v>128389641</v>
       </c>
       <c r="B72" t="n">
-        <v>79195</v>
+        <v>80225</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470981</v>
+        <v>471241</v>
       </c>
       <c r="R72" t="n">
-        <v>6866714</v>
+        <v>6866656</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128388646</v>
+        <v>128388766</v>
       </c>
       <c r="B73" t="n">
-        <v>79148</v>
+        <v>79199</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7638,21 +7638,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470945</v>
+        <v>470981</v>
       </c>
       <c r="R73" t="n">
-        <v>6866709</v>
+        <v>6866714</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7724,10 +7724,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128389641</v>
+        <v>128388646</v>
       </c>
       <c r="B74" t="n">
-        <v>80221</v>
+        <v>79152</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471241</v>
+        <v>470945</v>
       </c>
       <c r="R74" t="n">
-        <v>6866656</v>
+        <v>6866709</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7824,7 +7824,7 @@
         <v>128387695</v>
       </c>
       <c r="B75" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>128388053</v>
       </c>
       <c r="B76" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>128387629</v>
       </c>
       <c r="B77" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8121,45 +8121,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128388815</v>
+        <v>128388416</v>
       </c>
       <c r="B78" t="n">
-        <v>79116</v>
+        <v>98632</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470992</v>
+        <v>470816</v>
       </c>
       <c r="R78" t="n">
-        <v>6866696</v>
+        <v>6866722</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8218,10 +8227,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128389886</v>
+        <v>128388815</v>
       </c>
       <c r="B79" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8253,10 +8262,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471211</v>
+        <v>470992</v>
       </c>
       <c r="R79" t="n">
-        <v>6866717</v>
+        <v>6866696</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8315,10 +8324,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128388714</v>
+        <v>128389886</v>
       </c>
       <c r="B80" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8350,10 +8359,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>470987</v>
+        <v>471211</v>
       </c>
       <c r="R80" t="n">
-        <v>6866714</v>
+        <v>6866717</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8412,54 +8421,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128388416</v>
+        <v>128388714</v>
       </c>
       <c r="B81" t="n">
-        <v>98619</v>
+        <v>79120</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>470816</v>
+        <v>470987</v>
       </c>
       <c r="R81" t="n">
-        <v>6866722</v>
+        <v>6866714</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8521,7 +8521,7 @@
         <v>128389403</v>
       </c>
       <c r="B82" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>128387736</v>
       </c>
       <c r="B83" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>128389124</v>
       </c>
       <c r="B84" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>128387659</v>
       </c>
       <c r="B85" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>128387292</v>
       </c>
       <c r="B86" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>128388228</v>
       </c>
       <c r="B87" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>128389213</v>
       </c>
       <c r="B88" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>128389901</v>
       </c>
       <c r="B89" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>128389351</v>
       </c>
       <c r="B90" t="n">
-        <v>78088</v>
+        <v>78092</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>128388690</v>
       </c>
       <c r="B91" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128388173</v>
+        <v>128389587</v>
       </c>
       <c r="B92" t="n">
-        <v>78782</v>
+        <v>80226</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>470786</v>
+        <v>471274</v>
       </c>
       <c r="R92" t="n">
-        <v>6866737</v>
+        <v>6866626</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128389587</v>
+        <v>128388173</v>
       </c>
       <c r="B93" t="n">
-        <v>80222</v>
+        <v>78786</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9629,10 +9629,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471274</v>
+        <v>470786</v>
       </c>
       <c r="R93" t="n">
-        <v>6866626</v>
+        <v>6866737</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9694,7 +9694,7 @@
         <v>128389918</v>
       </c>
       <c r="B94" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>128389286</v>
       </c>
       <c r="B95" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10273,32 +10273,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128502704</v>
+        <v>128501140</v>
       </c>
       <c r="B100" t="n">
-        <v>91464</v>
+        <v>79120</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471366</v>
+        <v>471253</v>
       </c>
       <c r="R100" t="n">
-        <v>6866720</v>
+        <v>6866704</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10370,32 +10370,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128501140</v>
+        <v>128502704</v>
       </c>
       <c r="B101" t="n">
-        <v>79120</v>
+        <v>91469</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471253</v>
+        <v>471366</v>
       </c>
       <c r="R101" t="n">
-        <v>6866704</v>
+        <v>6866720</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11049,10 +11049,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128501209</v>
+        <v>128502100</v>
       </c>
       <c r="B108" t="n">
-        <v>78877</v>
+        <v>79152</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11060,21 +11060,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471244</v>
+        <v>471347</v>
       </c>
       <c r="R108" t="n">
-        <v>6866687</v>
+        <v>6866584</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11146,10 +11146,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128502100</v>
+        <v>128502802</v>
       </c>
       <c r="B109" t="n">
-        <v>79152</v>
+        <v>79120</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11157,21 +11157,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11181,10 +11181,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471347</v>
+        <v>471256</v>
       </c>
       <c r="R109" t="n">
-        <v>6866584</v>
+        <v>6866728</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11243,10 +11243,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128502802</v>
+        <v>128501209</v>
       </c>
       <c r="B110" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11254,21 +11254,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471256</v>
+        <v>471244</v>
       </c>
       <c r="R110" t="n">
-        <v>6866728</v>
+        <v>6866687</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11343,7 +11343,7 @@
         <v>128502866</v>
       </c>
       <c r="B111" t="n">
-        <v>98542</v>
+        <v>98549</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11631,10 +11631,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128501097</v>
+        <v>128501347</v>
       </c>
       <c r="B114" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11642,21 +11642,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471224</v>
+        <v>471275</v>
       </c>
       <c r="R114" t="n">
-        <v>6866707</v>
+        <v>6866627</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128502607</v>
+        <v>128501097</v>
       </c>
       <c r="B116" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11836,21 +11836,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471349</v>
+        <v>471224</v>
       </c>
       <c r="R116" t="n">
-        <v>6866695</v>
+        <v>6866707</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11922,10 +11922,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128501347</v>
+        <v>128502607</v>
       </c>
       <c r="B117" t="n">
-        <v>80225</v>
+        <v>78877</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11933,21 +11933,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11957,10 +11957,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471275</v>
+        <v>471349</v>
       </c>
       <c r="R117" t="n">
-        <v>6866627</v>
+        <v>6866695</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128374420</v>
+        <v>128376373</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471132</v>
+        <v>471330</v>
       </c>
       <c r="R2" t="n">
-        <v>6866856</v>
+        <v>6866787</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128375924</v>
+        <v>128374470</v>
       </c>
       <c r="B3" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471255</v>
+        <v>471139</v>
       </c>
       <c r="R3" t="n">
-        <v>6866786</v>
+        <v>6866835</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128373928</v>
+        <v>128376618</v>
       </c>
       <c r="B4" t="n">
-        <v>79152</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471086</v>
+        <v>471331</v>
       </c>
       <c r="R4" t="n">
-        <v>6866862</v>
+        <v>6866715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128376373</v>
+        <v>128373928</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471330</v>
+        <v>471086</v>
       </c>
       <c r="R5" t="n">
-        <v>6866787</v>
+        <v>6866862</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128374470</v>
+        <v>128375151</v>
       </c>
       <c r="B6" t="n">
-        <v>78877</v>
+        <v>79152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471139</v>
+        <v>471135</v>
       </c>
       <c r="R6" t="n">
-        <v>6866835</v>
+        <v>6866819</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,45 +1160,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128376618</v>
+        <v>128374420</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471331</v>
+        <v>471132</v>
       </c>
       <c r="R7" t="n">
-        <v>6866715</v>
+        <v>6866856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128375151</v>
+        <v>128375924</v>
       </c>
       <c r="B8" t="n">
-        <v>79152</v>
+        <v>78878</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471135</v>
+        <v>471255</v>
       </c>
       <c r="R8" t="n">
-        <v>6866819</v>
+        <v>6866786</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128376676</v>
+        <v>128374859</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>80226</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471287</v>
+        <v>471125</v>
       </c>
       <c r="R13" t="n">
-        <v>6866763</v>
+        <v>6866815</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128374859</v>
+        <v>128376676</v>
       </c>
       <c r="B14" t="n">
-        <v>80226</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471125</v>
+        <v>471287</v>
       </c>
       <c r="R14" t="n">
-        <v>6866815</v>
+        <v>6866763</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128376712</v>
+        <v>128375275</v>
       </c>
       <c r="B15" t="n">
-        <v>79710</v>
+        <v>79152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471282</v>
+        <v>471162</v>
       </c>
       <c r="R15" t="n">
-        <v>6866780</v>
+        <v>6866793</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128375275</v>
+        <v>128375734</v>
       </c>
       <c r="B16" t="n">
-        <v>79152</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471162</v>
+        <v>471234</v>
       </c>
       <c r="R16" t="n">
-        <v>6866793</v>
+        <v>6866765</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128375734</v>
+        <v>128376712</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79710</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471234</v>
+        <v>471282</v>
       </c>
       <c r="R17" t="n">
-        <v>6866765</v>
+        <v>6866780</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128375560</v>
+        <v>128376736</v>
       </c>
       <c r="B27" t="n">
-        <v>57876</v>
+        <v>78092</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471219</v>
+        <v>471282</v>
       </c>
       <c r="R27" t="n">
-        <v>6866779</v>
+        <v>6866783</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3180,11 +3180,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3211,10 +3206,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128376736</v>
+        <v>128375560</v>
       </c>
       <c r="B28" t="n">
-        <v>78092</v>
+        <v>57876</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3217,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,13 +3241,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471282</v>
+        <v>471219</v>
       </c>
       <c r="R28" t="n">
-        <v>6866783</v>
+        <v>6866779</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3282,6 +3277,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128376574</v>
+        <v>128376636</v>
       </c>
       <c r="B29" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,21 +3319,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,13 +3343,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471364</v>
+        <v>471320</v>
       </c>
       <c r="R29" t="n">
-        <v>6866709</v>
+        <v>6866734</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128376636</v>
+        <v>128376702</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>78523</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471320</v>
+        <v>471287</v>
       </c>
       <c r="R30" t="n">
-        <v>6866734</v>
+        <v>6866773</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128376702</v>
+        <v>128374116</v>
       </c>
       <c r="B31" t="n">
-        <v>78523</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,13 +3537,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471287</v>
+        <v>471107</v>
       </c>
       <c r="R31" t="n">
-        <v>6866773</v>
+        <v>6866853</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128374116</v>
+        <v>128376574</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471107</v>
+        <v>471364</v>
       </c>
       <c r="R32" t="n">
-        <v>6866853</v>
+        <v>6866709</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128376649</v>
+        <v>128374500</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>79152</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4400,21 +4400,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471300</v>
+        <v>471134</v>
       </c>
       <c r="R40" t="n">
-        <v>6866735</v>
+        <v>6866834</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4486,7 +4486,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128375508</v>
+        <v>128376649</v>
       </c>
       <c r="B41" t="n">
         <v>79120</v>
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471209</v>
+        <v>471300</v>
       </c>
       <c r="R41" t="n">
-        <v>6866776</v>
+        <v>6866735</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4583,10 +4583,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128374500</v>
+        <v>128375508</v>
       </c>
       <c r="B42" t="n">
-        <v>79152</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4594,21 +4594,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471134</v>
+        <v>471209</v>
       </c>
       <c r="R42" t="n">
-        <v>6866834</v>
+        <v>6866776</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6061,7 +6061,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128388996</v>
+        <v>128388496</v>
       </c>
       <c r="B57" t="n">
         <v>79120</v>
@@ -6096,10 +6096,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>471118</v>
+        <v>470869</v>
       </c>
       <c r="R57" t="n">
-        <v>6866746</v>
+        <v>6866723</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6158,7 +6158,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128388496</v>
+        <v>128388996</v>
       </c>
       <c r="B58" t="n">
         <v>79120</v>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>470869</v>
+        <v>471118</v>
       </c>
       <c r="R58" t="n">
-        <v>6866723</v>
+        <v>6866746</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128389511</v>
+        <v>128388778</v>
       </c>
       <c r="B61" t="n">
-        <v>80225</v>
+        <v>79199</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,10 +6493,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471237</v>
+        <v>470995</v>
       </c>
       <c r="R61" t="n">
-        <v>6866588</v>
+        <v>6866711</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128389329</v>
+        <v>128389262</v>
       </c>
       <c r="B62" t="n">
-        <v>78877</v>
+        <v>80226</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6566,21 +6566,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471172</v>
+        <v>471168</v>
       </c>
       <c r="R62" t="n">
-        <v>6866632</v>
+        <v>6866647</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128387227</v>
+        <v>128389855</v>
       </c>
       <c r="B63" t="n">
-        <v>80225</v>
+        <v>57876</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6663,21 +6663,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>470551</v>
+        <v>471241</v>
       </c>
       <c r="R63" t="n">
-        <v>6866892</v>
+        <v>6866622</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6723,6 +6723,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6749,7 +6754,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128387286</v>
+        <v>128389511</v>
       </c>
       <c r="B64" t="n">
         <v>80225</v>
@@ -6784,10 +6789,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>470551</v>
+        <v>471237</v>
       </c>
       <c r="R64" t="n">
-        <v>6866872</v>
+        <v>6866588</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,10 +6851,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128389262</v>
+        <v>128389329</v>
       </c>
       <c r="B65" t="n">
-        <v>80226</v>
+        <v>78877</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6857,21 +6862,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6886,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471168</v>
+        <v>471172</v>
       </c>
       <c r="R65" t="n">
-        <v>6866647</v>
+        <v>6866632</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,10 +6948,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128388778</v>
+        <v>128387227</v>
       </c>
       <c r="B66" t="n">
-        <v>79199</v>
+        <v>80225</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,21 +6959,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6983,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470995</v>
+        <v>470551</v>
       </c>
       <c r="R66" t="n">
-        <v>6866711</v>
+        <v>6866892</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7040,10 +7045,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128389855</v>
+        <v>128387286</v>
       </c>
       <c r="B67" t="n">
-        <v>57876</v>
+        <v>80225</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,21 +7056,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,13 +7080,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471241</v>
+        <v>470551</v>
       </c>
       <c r="R67" t="n">
-        <v>6866622</v>
+        <v>6866872</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7111,11 +7116,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7142,10 +7142,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128389069</v>
+        <v>128389227</v>
       </c>
       <c r="B68" t="n">
-        <v>80225</v>
+        <v>79152</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471158</v>
+        <v>471156</v>
       </c>
       <c r="R68" t="n">
-        <v>6866734</v>
+        <v>6866665</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128389187</v>
+        <v>128388804</v>
       </c>
       <c r="B69" t="n">
-        <v>78877</v>
+        <v>79152</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471196</v>
+        <v>470987</v>
       </c>
       <c r="R69" t="n">
         <v>6866706</v>
@@ -7336,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128389227</v>
+        <v>128389069</v>
       </c>
       <c r="B70" t="n">
-        <v>79152</v>
+        <v>80225</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7347,21 +7347,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471156</v>
+        <v>471158</v>
       </c>
       <c r="R70" t="n">
-        <v>6866665</v>
+        <v>6866734</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128388804</v>
+        <v>128389187</v>
       </c>
       <c r="B71" t="n">
-        <v>79152</v>
+        <v>78877</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>470987</v>
+        <v>471196</v>
       </c>
       <c r="R71" t="n">
         <v>6866706</v>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128389641</v>
+        <v>128388766</v>
       </c>
       <c r="B72" t="n">
-        <v>80225</v>
+        <v>79199</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471241</v>
+        <v>470981</v>
       </c>
       <c r="R72" t="n">
-        <v>6866656</v>
+        <v>6866714</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128388766</v>
+        <v>128388646</v>
       </c>
       <c r="B73" t="n">
-        <v>79199</v>
+        <v>79152</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7638,21 +7638,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470981</v>
+        <v>470945</v>
       </c>
       <c r="R73" t="n">
-        <v>6866714</v>
+        <v>6866709</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7724,10 +7724,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128388646</v>
+        <v>128389641</v>
       </c>
       <c r="B74" t="n">
-        <v>79152</v>
+        <v>80225</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>470945</v>
+        <v>471241</v>
       </c>
       <c r="R74" t="n">
-        <v>6866709</v>
+        <v>6866656</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7821,32 +7821,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128387695</v>
+        <v>128388053</v>
       </c>
       <c r="B75" t="n">
-        <v>98632</v>
+        <v>78878</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7856,13 +7856,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>470733</v>
+        <v>470770</v>
       </c>
       <c r="R75" t="n">
-        <v>6866772</v>
+        <v>6866780</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7918,32 +7918,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128388053</v>
+        <v>128387695</v>
       </c>
       <c r="B76" t="n">
-        <v>78878</v>
+        <v>98632</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7953,13 +7953,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>470770</v>
+        <v>470733</v>
       </c>
       <c r="R76" t="n">
-        <v>6866780</v>
+        <v>6866772</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8121,54 +8121,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128388416</v>
+        <v>128388815</v>
       </c>
       <c r="B78" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470816</v>
+        <v>470992</v>
       </c>
       <c r="R78" t="n">
-        <v>6866722</v>
+        <v>6866696</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8227,7 +8218,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128388815</v>
+        <v>128389886</v>
       </c>
       <c r="B79" t="n">
         <v>79120</v>
@@ -8262,10 +8253,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>470992</v>
+        <v>471211</v>
       </c>
       <c r="R79" t="n">
-        <v>6866696</v>
+        <v>6866717</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8324,7 +8315,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128389886</v>
+        <v>128388714</v>
       </c>
       <c r="B80" t="n">
         <v>79120</v>
@@ -8359,10 +8350,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471211</v>
+        <v>470987</v>
       </c>
       <c r="R80" t="n">
-        <v>6866717</v>
+        <v>6866714</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8421,45 +8412,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128388714</v>
+        <v>128388416</v>
       </c>
       <c r="B81" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>470987</v>
+        <v>470816</v>
       </c>
       <c r="R81" t="n">
-        <v>6866714</v>
+        <v>6866722</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128388228</v>
+        <v>128389213</v>
       </c>
       <c r="B87" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>470788</v>
+        <v>471148</v>
       </c>
       <c r="R87" t="n">
-        <v>6866725</v>
+        <v>6866668</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128389213</v>
+        <v>128389901</v>
       </c>
       <c r="B88" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471148</v>
+        <v>471209</v>
       </c>
       <c r="R88" t="n">
-        <v>6866668</v>
+        <v>6866743</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9206,10 +9206,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128389901</v>
+        <v>128389351</v>
       </c>
       <c r="B89" t="n">
-        <v>79120</v>
+        <v>78092</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9217,21 +9217,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471209</v>
+        <v>471215</v>
       </c>
       <c r="R89" t="n">
-        <v>6866743</v>
+        <v>6866634</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9303,32 +9303,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128389351</v>
+        <v>128388228</v>
       </c>
       <c r="B90" t="n">
-        <v>78092</v>
+        <v>98632</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471215</v>
+        <v>470788</v>
       </c>
       <c r="R90" t="n">
-        <v>6866634</v>
+        <v>6866725</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128389587</v>
+        <v>128389918</v>
       </c>
       <c r="B92" t="n">
-        <v>80226</v>
+        <v>79120</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9532,13 +9532,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471274</v>
+        <v>471210</v>
       </c>
       <c r="R92" t="n">
-        <v>6866626</v>
+        <v>6866755</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9691,10 +9691,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128389918</v>
+        <v>128389587</v>
       </c>
       <c r="B94" t="n">
-        <v>79120</v>
+        <v>80226</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9702,21 +9702,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9726,13 +9726,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471210</v>
+        <v>471274</v>
       </c>
       <c r="R94" t="n">
-        <v>6866755</v>
+        <v>6866626</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10273,32 +10273,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128501140</v>
+        <v>128502704</v>
       </c>
       <c r="B100" t="n">
-        <v>79120</v>
+        <v>91469</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471253</v>
+        <v>471366</v>
       </c>
       <c r="R100" t="n">
-        <v>6866704</v>
+        <v>6866720</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10370,32 +10370,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128502704</v>
+        <v>128501140</v>
       </c>
       <c r="B101" t="n">
-        <v>91469</v>
+        <v>79120</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471366</v>
+        <v>471253</v>
       </c>
       <c r="R101" t="n">
-        <v>6866720</v>
+        <v>6866704</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11049,10 +11049,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128502100</v>
+        <v>128502802</v>
       </c>
       <c r="B108" t="n">
-        <v>79152</v>
+        <v>79120</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11060,21 +11060,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471347</v>
+        <v>471256</v>
       </c>
       <c r="R108" t="n">
-        <v>6866584</v>
+        <v>6866728</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11146,10 +11146,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128502802</v>
+        <v>128501209</v>
       </c>
       <c r="B109" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11157,21 +11157,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11181,10 +11181,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471256</v>
+        <v>471244</v>
       </c>
       <c r="R109" t="n">
-        <v>6866728</v>
+        <v>6866687</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11243,32 +11243,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128501209</v>
+        <v>128502866</v>
       </c>
       <c r="B110" t="n">
-        <v>78877</v>
+        <v>98549</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471244</v>
+        <v>471139</v>
       </c>
       <c r="R110" t="n">
-        <v>6866687</v>
+        <v>6866727</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11340,32 +11340,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128502866</v>
+        <v>128502100</v>
       </c>
       <c r="B111" t="n">
-        <v>98549</v>
+        <v>79152</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11375,10 +11375,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471139</v>
+        <v>471347</v>
       </c>
       <c r="R111" t="n">
-        <v>6866727</v>
+        <v>6866584</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11631,10 +11631,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128501347</v>
+        <v>128502509</v>
       </c>
       <c r="B114" t="n">
-        <v>80225</v>
+        <v>78877</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11642,21 +11642,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471275</v>
+        <v>471315</v>
       </c>
       <c r="R114" t="n">
-        <v>6866627</v>
+        <v>6866670</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11728,10 +11728,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128502509</v>
+        <v>128501097</v>
       </c>
       <c r="B115" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11739,21 +11739,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11763,10 +11763,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471315</v>
+        <v>471224</v>
       </c>
       <c r="R115" t="n">
-        <v>6866670</v>
+        <v>6866707</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128501097</v>
+        <v>128502607</v>
       </c>
       <c r="B116" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11836,21 +11836,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471224</v>
+        <v>471349</v>
       </c>
       <c r="R116" t="n">
-        <v>6866707</v>
+        <v>6866695</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11922,10 +11922,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128502607</v>
+        <v>128501347</v>
       </c>
       <c r="B117" t="n">
-        <v>78877</v>
+        <v>80225</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11933,21 +11933,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11957,10 +11957,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471349</v>
+        <v>471275</v>
       </c>
       <c r="R117" t="n">
-        <v>6866695</v>
+        <v>6866627</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128376373</v>
+        <v>128373928</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471330</v>
+        <v>471086</v>
       </c>
       <c r="R2" t="n">
-        <v>6866787</v>
+        <v>6866862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128374470</v>
+        <v>128375151</v>
       </c>
       <c r="B3" t="n">
-        <v>78877</v>
+        <v>79152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471139</v>
+        <v>471135</v>
       </c>
       <c r="R3" t="n">
-        <v>6866835</v>
+        <v>6866819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128376618</v>
+        <v>128376373</v>
       </c>
       <c r="B4" t="n">
         <v>79120</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471331</v>
+        <v>471330</v>
       </c>
       <c r="R4" t="n">
-        <v>6866715</v>
+        <v>6866787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373928</v>
+        <v>128374470</v>
       </c>
       <c r="B5" t="n">
-        <v>79152</v>
+        <v>78877</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471086</v>
+        <v>471139</v>
       </c>
       <c r="R5" t="n">
-        <v>6866862</v>
+        <v>6866835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128375151</v>
+        <v>128376618</v>
       </c>
       <c r="B6" t="n">
-        <v>79152</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471135</v>
+        <v>471331</v>
       </c>
       <c r="R6" t="n">
-        <v>6866819</v>
+        <v>6866715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128375289</v>
+        <v>128375794</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471165</v>
+        <v>471241</v>
       </c>
       <c r="R33" t="n">
-        <v>6866794</v>
+        <v>6866786</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128375249</v>
+        <v>128375289</v>
       </c>
       <c r="B34" t="n">
         <v>79120</v>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471158</v>
+        <v>471165</v>
       </c>
       <c r="R34" t="n">
-        <v>6866800</v>
+        <v>6866794</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128375794</v>
+        <v>128375249</v>
       </c>
       <c r="B35" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471241</v>
+        <v>471158</v>
       </c>
       <c r="R35" t="n">
-        <v>6866786</v>
+        <v>6866800</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4680,45 +4680,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128375808</v>
+        <v>128376462</v>
       </c>
       <c r="B43" t="n">
-        <v>79120</v>
+        <v>92078</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471247</v>
+        <v>471351</v>
       </c>
       <c r="R43" t="n">
-        <v>6866787</v>
+        <v>6866748</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4751,6 +4760,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4777,7 +4791,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128375498</v>
+        <v>128375808</v>
       </c>
       <c r="B44" t="n">
         <v>79120</v>
@@ -4812,10 +4826,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471198</v>
+        <v>471247</v>
       </c>
       <c r="R44" t="n">
-        <v>6866776</v>
+        <v>6866787</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4874,54 +4888,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128376462</v>
+        <v>128375498</v>
       </c>
       <c r="B45" t="n">
-        <v>92078</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471351</v>
+        <v>471198</v>
       </c>
       <c r="R45" t="n">
-        <v>6866748</v>
+        <v>6866776</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4954,11 +4959,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5673,32 +5673,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128389894</v>
+        <v>128387790</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5708,10 +5708,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>471207</v>
+        <v>470732</v>
       </c>
       <c r="R53" t="n">
-        <v>6866729</v>
+        <v>6866727</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5770,7 +5770,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128389953</v>
+        <v>128389894</v>
       </c>
       <c r="B54" t="n">
         <v>79120</v>
@@ -5805,13 +5805,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>471200</v>
+        <v>471207</v>
       </c>
       <c r="R54" t="n">
-        <v>6866759</v>
+        <v>6866729</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5867,32 +5867,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128387790</v>
+        <v>128389953</v>
       </c>
       <c r="B55" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5902,13 +5902,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470732</v>
+        <v>471200</v>
       </c>
       <c r="R55" t="n">
-        <v>6866727</v>
+        <v>6866759</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128389855</v>
+        <v>128389511</v>
       </c>
       <c r="B63" t="n">
-        <v>57876</v>
+        <v>80225</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6663,21 +6663,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471241</v>
+        <v>471237</v>
       </c>
       <c r="R63" t="n">
-        <v>6866622</v>
+        <v>6866588</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6723,11 +6723,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6754,10 +6749,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128389511</v>
+        <v>128389329</v>
       </c>
       <c r="B64" t="n">
-        <v>80225</v>
+        <v>78877</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6765,21 +6760,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6789,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471237</v>
+        <v>471172</v>
       </c>
       <c r="R64" t="n">
-        <v>6866588</v>
+        <v>6866632</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6851,10 +6846,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128389329</v>
+        <v>128387227</v>
       </c>
       <c r="B65" t="n">
-        <v>78877</v>
+        <v>80225</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6862,21 +6857,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6886,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471172</v>
+        <v>470551</v>
       </c>
       <c r="R65" t="n">
-        <v>6866632</v>
+        <v>6866892</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6948,7 +6943,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128387227</v>
+        <v>128387286</v>
       </c>
       <c r="B66" t="n">
         <v>80225</v>
@@ -6986,7 +6981,7 @@
         <v>470551</v>
       </c>
       <c r="R66" t="n">
-        <v>6866892</v>
+        <v>6866872</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7045,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128387286</v>
+        <v>128389855</v>
       </c>
       <c r="B67" t="n">
-        <v>80225</v>
+        <v>57876</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7056,21 +7051,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7080,13 +7075,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>470551</v>
+        <v>471241</v>
       </c>
       <c r="R67" t="n">
-        <v>6866872</v>
+        <v>6866622</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7116,6 +7111,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7142,10 +7142,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128389227</v>
+        <v>128389069</v>
       </c>
       <c r="B68" t="n">
-        <v>79152</v>
+        <v>80225</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471156</v>
+        <v>471158</v>
       </c>
       <c r="R68" t="n">
-        <v>6866665</v>
+        <v>6866734</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128388804</v>
+        <v>128389187</v>
       </c>
       <c r="B69" t="n">
-        <v>79152</v>
+        <v>78877</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>470987</v>
+        <v>471196</v>
       </c>
       <c r="R69" t="n">
         <v>6866706</v>
@@ -7336,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128389069</v>
+        <v>128389227</v>
       </c>
       <c r="B70" t="n">
-        <v>80225</v>
+        <v>79152</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7347,21 +7347,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471158</v>
+        <v>471156</v>
       </c>
       <c r="R70" t="n">
-        <v>6866734</v>
+        <v>6866665</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128389187</v>
+        <v>128388804</v>
       </c>
       <c r="B71" t="n">
-        <v>78877</v>
+        <v>79152</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471196</v>
+        <v>470987</v>
       </c>
       <c r="R71" t="n">
         <v>6866706</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128389213</v>
+        <v>128388228</v>
       </c>
       <c r="B87" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471148</v>
+        <v>470788</v>
       </c>
       <c r="R87" t="n">
-        <v>6866668</v>
+        <v>6866725</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128389901</v>
+        <v>128389213</v>
       </c>
       <c r="B88" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471209</v>
+        <v>471148</v>
       </c>
       <c r="R88" t="n">
-        <v>6866743</v>
+        <v>6866668</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9206,10 +9206,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128389351</v>
+        <v>128389901</v>
       </c>
       <c r="B89" t="n">
-        <v>78092</v>
+        <v>79120</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9217,21 +9217,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471215</v>
+        <v>471209</v>
       </c>
       <c r="R89" t="n">
-        <v>6866634</v>
+        <v>6866743</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9303,32 +9303,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128388228</v>
+        <v>128389351</v>
       </c>
       <c r="B90" t="n">
-        <v>98632</v>
+        <v>78092</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>470788</v>
+        <v>471215</v>
       </c>
       <c r="R90" t="n">
-        <v>6866725</v>
+        <v>6866634</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10273,32 +10273,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128502704</v>
+        <v>128501140</v>
       </c>
       <c r="B100" t="n">
-        <v>91469</v>
+        <v>79120</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471366</v>
+        <v>471253</v>
       </c>
       <c r="R100" t="n">
-        <v>6866720</v>
+        <v>6866704</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10370,32 +10370,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128501140</v>
+        <v>128502704</v>
       </c>
       <c r="B101" t="n">
-        <v>79120</v>
+        <v>91469</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471253</v>
+        <v>471366</v>
       </c>
       <c r="R101" t="n">
-        <v>6866704</v>
+        <v>6866720</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11049,32 +11049,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128502802</v>
+        <v>128502866</v>
       </c>
       <c r="B108" t="n">
-        <v>79120</v>
+        <v>98549</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471256</v>
+        <v>471139</v>
       </c>
       <c r="R108" t="n">
-        <v>6866728</v>
+        <v>6866727</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11146,10 +11146,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128501209</v>
+        <v>128502100</v>
       </c>
       <c r="B109" t="n">
-        <v>78877</v>
+        <v>79152</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11157,21 +11157,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11181,10 +11181,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471244</v>
+        <v>471347</v>
       </c>
       <c r="R109" t="n">
-        <v>6866687</v>
+        <v>6866584</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11243,32 +11243,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128502866</v>
+        <v>128502802</v>
       </c>
       <c r="B110" t="n">
-        <v>98549</v>
+        <v>79120</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471139</v>
+        <v>471256</v>
       </c>
       <c r="R110" t="n">
-        <v>6866727</v>
+        <v>6866728</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11340,10 +11340,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128502100</v>
+        <v>128501209</v>
       </c>
       <c r="B111" t="n">
-        <v>79152</v>
+        <v>78877</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11351,21 +11351,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11375,10 +11375,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471347</v>
+        <v>471244</v>
       </c>
       <c r="R111" t="n">
-        <v>6866584</v>
+        <v>6866687</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128373928</v>
+        <v>128375924</v>
       </c>
       <c r="B2" t="n">
-        <v>79152</v>
+        <v>78878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471086</v>
+        <v>471255</v>
       </c>
       <c r="R2" t="n">
-        <v>6866862</v>
+        <v>6866786</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128375151</v>
+        <v>128373928</v>
       </c>
       <c r="B3" t="n">
         <v>79152</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471135</v>
+        <v>471086</v>
       </c>
       <c r="R3" t="n">
-        <v>6866819</v>
+        <v>6866862</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128376373</v>
+        <v>128375151</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471330</v>
+        <v>471135</v>
       </c>
       <c r="R4" t="n">
-        <v>6866787</v>
+        <v>6866819</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128374470</v>
+        <v>128376373</v>
       </c>
       <c r="B5" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471139</v>
+        <v>471330</v>
       </c>
       <c r="R5" t="n">
-        <v>6866835</v>
+        <v>6866787</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,54 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128374420</v>
+        <v>128374470</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>78877</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471132</v>
+        <v>471139</v>
       </c>
       <c r="R7" t="n">
-        <v>6866856</v>
+        <v>6866835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,45 +1257,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128375924</v>
+        <v>128374420</v>
       </c>
       <c r="B8" t="n">
-        <v>78878</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471255</v>
+        <v>471132</v>
       </c>
       <c r="R8" t="n">
-        <v>6866786</v>
+        <v>6866856</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128375734</v>
+        <v>128374662</v>
       </c>
       <c r="B16" t="n">
         <v>79120</v>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471234</v>
+        <v>471145</v>
       </c>
       <c r="R16" t="n">
-        <v>6866765</v>
+        <v>6866824</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128376712</v>
+        <v>128375734</v>
       </c>
       <c r="B17" t="n">
-        <v>79710</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471282</v>
+        <v>471234</v>
       </c>
       <c r="R17" t="n">
-        <v>6866780</v>
+        <v>6866765</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128374662</v>
+        <v>128376712</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471145</v>
+        <v>471282</v>
       </c>
       <c r="R18" t="n">
-        <v>6866824</v>
+        <v>6866780</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128375989</v>
+        <v>128375959</v>
       </c>
       <c r="B19" t="n">
-        <v>78092</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471276</v>
+        <v>471266</v>
       </c>
       <c r="R19" t="n">
-        <v>6866805</v>
+        <v>6866792</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128375959</v>
+        <v>128375989</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>78092</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471266</v>
+        <v>471276</v>
       </c>
       <c r="R20" t="n">
-        <v>6866792</v>
+        <v>6866805</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128375214</v>
+        <v>128375358</v>
       </c>
       <c r="B21" t="n">
         <v>79120</v>
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471144</v>
+        <v>471166</v>
       </c>
       <c r="R21" t="n">
-        <v>6866814</v>
+        <v>6866785</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2624,7 +2624,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128375358</v>
+        <v>128375214</v>
       </c>
       <c r="B22" t="n">
         <v>79120</v>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471166</v>
+        <v>471144</v>
       </c>
       <c r="R22" t="n">
-        <v>6866785</v>
+        <v>6866814</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128376736</v>
+        <v>128375560</v>
       </c>
       <c r="B27" t="n">
-        <v>78092</v>
+        <v>57876</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471282</v>
+        <v>471219</v>
       </c>
       <c r="R27" t="n">
-        <v>6866783</v>
+        <v>6866779</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3180,6 +3180,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3206,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128375560</v>
+        <v>128376736</v>
       </c>
       <c r="B28" t="n">
-        <v>57876</v>
+        <v>78092</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3217,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3241,13 +3246,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471219</v>
+        <v>471282</v>
       </c>
       <c r="R28" t="n">
-        <v>6866779</v>
+        <v>6866783</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3277,11 +3282,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128376636</v>
+        <v>128376574</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,21 +3319,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,13 +3343,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471320</v>
+        <v>471364</v>
       </c>
       <c r="R29" t="n">
-        <v>6866734</v>
+        <v>6866709</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128376702</v>
+        <v>128374116</v>
       </c>
       <c r="B30" t="n">
-        <v>78523</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471287</v>
+        <v>471107</v>
       </c>
       <c r="R30" t="n">
-        <v>6866773</v>
+        <v>6866853</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374116</v>
+        <v>128376636</v>
       </c>
       <c r="B31" t="n">
         <v>79120</v>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471107</v>
+        <v>471320</v>
       </c>
       <c r="R31" t="n">
-        <v>6866853</v>
+        <v>6866734</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128376574</v>
+        <v>128376702</v>
       </c>
       <c r="B32" t="n">
-        <v>78878</v>
+        <v>78523</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471364</v>
+        <v>471287</v>
       </c>
       <c r="R32" t="n">
-        <v>6866709</v>
+        <v>6866773</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3987,7 +3987,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128374814</v>
+        <v>128376382</v>
       </c>
       <c r="B36" t="n">
         <v>79120</v>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471137</v>
+        <v>471342</v>
       </c>
       <c r="R36" t="n">
-        <v>6866828</v>
+        <v>6866780</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4058,11 +4058,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4089,7 +4084,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128376382</v>
+        <v>128374814</v>
       </c>
       <c r="B37" t="n">
         <v>79120</v>
@@ -4124,10 +4119,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471342</v>
+        <v>471137</v>
       </c>
       <c r="R37" t="n">
-        <v>6866780</v>
+        <v>6866828</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4160,6 +4155,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4791,7 +4791,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128375808</v>
+        <v>128375498</v>
       </c>
       <c r="B44" t="n">
         <v>79120</v>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471247</v>
+        <v>471198</v>
       </c>
       <c r="R44" t="n">
-        <v>6866787</v>
+        <v>6866776</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4888,7 +4888,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128375498</v>
+        <v>128375808</v>
       </c>
       <c r="B45" t="n">
         <v>79120</v>
@@ -4923,10 +4923,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471198</v>
+        <v>471247</v>
       </c>
       <c r="R45" t="n">
-        <v>6866776</v>
+        <v>6866787</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5082,7 +5082,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128376295</v>
+        <v>128375399</v>
       </c>
       <c r="B47" t="n">
         <v>79120</v>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471321</v>
+        <v>471183</v>
       </c>
       <c r="R47" t="n">
-        <v>6866820</v>
+        <v>6866790</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5179,7 +5179,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128375399</v>
+        <v>128376295</v>
       </c>
       <c r="B48" t="n">
         <v>79120</v>
@@ -5214,10 +5214,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>471183</v>
+        <v>471321</v>
       </c>
       <c r="R48" t="n">
-        <v>6866790</v>
+        <v>6866820</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5276,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128388207</v>
+        <v>128387779</v>
       </c>
       <c r="B49" t="n">
-        <v>78877</v>
+        <v>98632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470789</v>
+        <v>470744</v>
       </c>
       <c r="R49" t="n">
-        <v>6866739</v>
+        <v>6866736</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5373,7 +5373,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128387779</v>
+        <v>128388103</v>
       </c>
       <c r="B50" t="n">
         <v>98632</v>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470744</v>
+        <v>470763</v>
       </c>
       <c r="R50" t="n">
-        <v>6866736</v>
+        <v>6866753</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,32 +5470,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128388103</v>
+        <v>128388207</v>
       </c>
       <c r="B51" t="n">
-        <v>98632</v>
+        <v>78877</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470763</v>
+        <v>470789</v>
       </c>
       <c r="R51" t="n">
-        <v>6866753</v>
+        <v>6866739</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5673,32 +5673,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128387790</v>
+        <v>128389953</v>
       </c>
       <c r="B53" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>470732</v>
+        <v>471200</v>
       </c>
       <c r="R53" t="n">
-        <v>6866727</v>
+        <v>6866759</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5867,32 +5867,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128389953</v>
+        <v>128387790</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5902,13 +5902,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>471200</v>
+        <v>470732</v>
       </c>
       <c r="R55" t="n">
-        <v>6866759</v>
+        <v>6866727</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128388778</v>
+        <v>128389855</v>
       </c>
       <c r="B61" t="n">
-        <v>79199</v>
+        <v>57876</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>864</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>470995</v>
+        <v>471241</v>
       </c>
       <c r="R61" t="n">
-        <v>6866711</v>
+        <v>6866622</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6529,6 +6529,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6555,10 +6560,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128389262</v>
+        <v>128389329</v>
       </c>
       <c r="B62" t="n">
-        <v>80226</v>
+        <v>78877</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6566,21 +6571,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6595,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471168</v>
+        <v>471172</v>
       </c>
       <c r="R62" t="n">
-        <v>6866647</v>
+        <v>6866632</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6749,10 +6754,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128389329</v>
+        <v>128387227</v>
       </c>
       <c r="B64" t="n">
-        <v>78877</v>
+        <v>80225</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6760,21 +6765,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6789,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471172</v>
+        <v>470551</v>
       </c>
       <c r="R64" t="n">
-        <v>6866632</v>
+        <v>6866892</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,7 +6851,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128387227</v>
+        <v>128387286</v>
       </c>
       <c r="B65" t="n">
         <v>80225</v>
@@ -6884,7 +6889,7 @@
         <v>470551</v>
       </c>
       <c r="R65" t="n">
-        <v>6866892</v>
+        <v>6866872</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,10 +6948,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128387286</v>
+        <v>128388778</v>
       </c>
       <c r="B66" t="n">
-        <v>80225</v>
+        <v>79199</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,21 +6959,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6983,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470551</v>
+        <v>470995</v>
       </c>
       <c r="R66" t="n">
-        <v>6866872</v>
+        <v>6866711</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7040,10 +7045,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128389855</v>
+        <v>128389262</v>
       </c>
       <c r="B67" t="n">
-        <v>57876</v>
+        <v>80226</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,21 +7056,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,13 +7080,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471241</v>
+        <v>471168</v>
       </c>
       <c r="R67" t="n">
-        <v>6866622</v>
+        <v>6866647</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7111,11 +7116,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7142,10 +7142,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128389069</v>
+        <v>128389227</v>
       </c>
       <c r="B68" t="n">
-        <v>80225</v>
+        <v>79152</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471158</v>
+        <v>471156</v>
       </c>
       <c r="R68" t="n">
-        <v>6866734</v>
+        <v>6866665</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128389187</v>
+        <v>128388804</v>
       </c>
       <c r="B69" t="n">
-        <v>78877</v>
+        <v>79152</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471196</v>
+        <v>470987</v>
       </c>
       <c r="R69" t="n">
         <v>6866706</v>
@@ -7336,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128389227</v>
+        <v>128389187</v>
       </c>
       <c r="B70" t="n">
-        <v>79152</v>
+        <v>78877</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7347,21 +7347,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471156</v>
+        <v>471196</v>
       </c>
       <c r="R70" t="n">
-        <v>6866665</v>
+        <v>6866706</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128388804</v>
+        <v>128389069</v>
       </c>
       <c r="B71" t="n">
-        <v>79152</v>
+        <v>80225</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>470987</v>
+        <v>471158</v>
       </c>
       <c r="R71" t="n">
-        <v>6866706</v>
+        <v>6866734</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128388766</v>
+        <v>128389641</v>
       </c>
       <c r="B72" t="n">
-        <v>79199</v>
+        <v>80225</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470981</v>
+        <v>471241</v>
       </c>
       <c r="R72" t="n">
-        <v>6866714</v>
+        <v>6866656</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7724,10 +7724,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128389641</v>
+        <v>128388766</v>
       </c>
       <c r="B74" t="n">
-        <v>80225</v>
+        <v>79199</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471241</v>
+        <v>470981</v>
       </c>
       <c r="R74" t="n">
-        <v>6866656</v>
+        <v>6866714</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8121,45 +8121,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128388815</v>
+        <v>128388416</v>
       </c>
       <c r="B78" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470992</v>
+        <v>470816</v>
       </c>
       <c r="R78" t="n">
-        <v>6866696</v>
+        <v>6866722</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8218,10 +8227,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128389886</v>
+        <v>128389403</v>
       </c>
       <c r="B79" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8229,21 +8238,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8253,10 +8262,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471211</v>
+        <v>471187</v>
       </c>
       <c r="R79" t="n">
-        <v>6866717</v>
+        <v>6866586</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8315,7 +8324,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128388714</v>
+        <v>128388815</v>
       </c>
       <c r="B80" t="n">
         <v>79120</v>
@@ -8350,10 +8359,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>470987</v>
+        <v>470992</v>
       </c>
       <c r="R80" t="n">
-        <v>6866714</v>
+        <v>6866696</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8412,54 +8421,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128388416</v>
+        <v>128388714</v>
       </c>
       <c r="B81" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>470816</v>
+        <v>470987</v>
       </c>
       <c r="R81" t="n">
-        <v>6866722</v>
+        <v>6866714</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8518,10 +8518,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128389403</v>
+        <v>128389886</v>
       </c>
       <c r="B82" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8529,21 +8529,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471187</v>
+        <v>471211</v>
       </c>
       <c r="R82" t="n">
-        <v>6866586</v>
+        <v>6866717</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128388228</v>
+        <v>128389901</v>
       </c>
       <c r="B87" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>470788</v>
+        <v>471209</v>
       </c>
       <c r="R87" t="n">
-        <v>6866725</v>
+        <v>6866743</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9206,10 +9206,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128389901</v>
+        <v>128389351</v>
       </c>
       <c r="B89" t="n">
-        <v>79120</v>
+        <v>78092</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9217,21 +9217,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471209</v>
+        <v>471215</v>
       </c>
       <c r="R89" t="n">
-        <v>6866743</v>
+        <v>6866634</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9303,32 +9303,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128389351</v>
+        <v>128388228</v>
       </c>
       <c r="B90" t="n">
-        <v>78092</v>
+        <v>98632</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471215</v>
+        <v>470788</v>
       </c>
       <c r="R90" t="n">
-        <v>6866634</v>
+        <v>6866725</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128389918</v>
+        <v>128388173</v>
       </c>
       <c r="B92" t="n">
-        <v>79120</v>
+        <v>78786</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9532,13 +9532,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471210</v>
+        <v>470786</v>
       </c>
       <c r="R92" t="n">
-        <v>6866755</v>
+        <v>6866737</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128388173</v>
+        <v>128389587</v>
       </c>
       <c r="B93" t="n">
-        <v>78786</v>
+        <v>80226</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9629,10 +9629,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>470786</v>
+        <v>471274</v>
       </c>
       <c r="R93" t="n">
-        <v>6866737</v>
+        <v>6866626</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9691,10 +9691,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128389587</v>
+        <v>128389918</v>
       </c>
       <c r="B94" t="n">
-        <v>80226</v>
+        <v>79120</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9702,21 +9702,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9726,13 +9726,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471274</v>
+        <v>471210</v>
       </c>
       <c r="R94" t="n">
-        <v>6866626</v>
+        <v>6866755</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9885,10 +9885,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128502381</v>
+        <v>128502263</v>
       </c>
       <c r="B96" t="n">
-        <v>79152</v>
+        <v>79124</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9896,21 +9896,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9920,10 +9920,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471311</v>
+        <v>471328</v>
       </c>
       <c r="R96" t="n">
-        <v>6866616</v>
+        <v>6866612</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9982,10 +9982,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128502263</v>
+        <v>128502381</v>
       </c>
       <c r="B97" t="n">
-        <v>79120</v>
+        <v>79156</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9993,21 +9993,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471328</v>
+        <v>471311</v>
       </c>
       <c r="R97" t="n">
-        <v>6866612</v>
+        <v>6866616</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10082,7 +10082,7 @@
         <v>128501285</v>
       </c>
       <c r="B98" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>128501083</v>
       </c>
       <c r="B99" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10273,32 +10273,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128501140</v>
+        <v>128502704</v>
       </c>
       <c r="B100" t="n">
-        <v>79120</v>
+        <v>91473</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471253</v>
+        <v>471366</v>
       </c>
       <c r="R100" t="n">
-        <v>6866704</v>
+        <v>6866720</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10370,32 +10370,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128502704</v>
+        <v>128501140</v>
       </c>
       <c r="B101" t="n">
-        <v>91469</v>
+        <v>79124</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471366</v>
+        <v>471253</v>
       </c>
       <c r="R101" t="n">
-        <v>6866720</v>
+        <v>6866704</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10470,7 +10470,7 @@
         <v>128501794</v>
       </c>
       <c r="B102" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>128502548</v>
       </c>
       <c r="B103" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>128501127</v>
       </c>
       <c r="B104" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>128501181</v>
       </c>
       <c r="B105" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>128501480</v>
       </c>
       <c r="B106" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>128501144</v>
       </c>
       <c r="B107" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11049,32 +11049,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128502866</v>
+        <v>128501209</v>
       </c>
       <c r="B108" t="n">
-        <v>98549</v>
+        <v>78881</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471139</v>
+        <v>471244</v>
       </c>
       <c r="R108" t="n">
-        <v>6866727</v>
+        <v>6866687</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11149,7 +11149,7 @@
         <v>128502100</v>
       </c>
       <c r="B109" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>128502802</v>
       </c>
       <c r="B110" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11340,32 +11340,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128501209</v>
+        <v>128502866</v>
       </c>
       <c r="B111" t="n">
-        <v>78877</v>
+        <v>98553</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11375,10 +11375,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471244</v>
+        <v>471139</v>
       </c>
       <c r="R111" t="n">
-        <v>6866687</v>
+        <v>6866727</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11440,7 +11440,7 @@
         <v>128502259</v>
       </c>
       <c r="B112" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>128501973</v>
       </c>
       <c r="B113" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11631,10 +11631,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128502509</v>
+        <v>128501097</v>
       </c>
       <c r="B114" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11642,21 +11642,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471315</v>
+        <v>471224</v>
       </c>
       <c r="R114" t="n">
-        <v>6866670</v>
+        <v>6866707</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11728,10 +11728,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128501097</v>
+        <v>128502607</v>
       </c>
       <c r="B115" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11739,21 +11739,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11763,10 +11763,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471224</v>
+        <v>471349</v>
       </c>
       <c r="R115" t="n">
-        <v>6866707</v>
+        <v>6866695</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128502607</v>
+        <v>128502509</v>
       </c>
       <c r="B116" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471349</v>
+        <v>471315</v>
       </c>
       <c r="R116" t="n">
-        <v>6866695</v>
+        <v>6866670</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11925,7 +11925,7 @@
         <v>128501347</v>
       </c>
       <c r="B117" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>128501927</v>
       </c>
       <c r="B118" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>128501224</v>
       </c>
       <c r="B119" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>128502212</v>
       </c>
       <c r="B120" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>128502291</v>
       </c>
       <c r="B121" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>128502189</v>
       </c>
       <c r="B122" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12504,10 +12504,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128501253</v>
+        <v>128502309</v>
       </c>
       <c r="B123" t="n">
-        <v>79152</v>
+        <v>78882</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12515,21 +12515,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12539,10 +12539,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471267</v>
+        <v>471311</v>
       </c>
       <c r="R123" t="n">
-        <v>6866658</v>
+        <v>6866598</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12601,10 +12601,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128502309</v>
+        <v>128501253</v>
       </c>
       <c r="B124" t="n">
-        <v>78878</v>
+        <v>79156</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12612,21 +12612,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>471311</v>
+        <v>471267</v>
       </c>
       <c r="R124" t="n">
-        <v>6866598</v>
+        <v>6866658</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12701,7 +12701,7 @@
         <v>128502178</v>
       </c>
       <c r="B125" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128375924</v>
+        <v>128373928</v>
       </c>
       <c r="B2" t="n">
-        <v>78878</v>
+        <v>79156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471255</v>
+        <v>471086</v>
       </c>
       <c r="R2" t="n">
-        <v>6866786</v>
+        <v>6866862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128373928</v>
+        <v>128375151</v>
       </c>
       <c r="B3" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471086</v>
+        <v>471135</v>
       </c>
       <c r="R3" t="n">
-        <v>6866862</v>
+        <v>6866819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128375151</v>
+        <v>128375924</v>
       </c>
       <c r="B4" t="n">
-        <v>79152</v>
+        <v>78882</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471135</v>
+        <v>471255</v>
       </c>
       <c r="R4" t="n">
-        <v>6866819</v>
+        <v>6866786</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,45 +966,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128376373</v>
+        <v>128374420</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471330</v>
+        <v>471132</v>
       </c>
       <c r="R5" t="n">
-        <v>6866787</v>
+        <v>6866856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128376618</v>
+        <v>128376373</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471331</v>
+        <v>471330</v>
       </c>
       <c r="R6" t="n">
-        <v>6866715</v>
+        <v>6866787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128374470</v>
+        <v>128376618</v>
       </c>
       <c r="B7" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471139</v>
+        <v>471331</v>
       </c>
       <c r="R7" t="n">
-        <v>6866835</v>
+        <v>6866715</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,54 +1266,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128374420</v>
+        <v>128374470</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>78881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471132</v>
+        <v>471139</v>
       </c>
       <c r="R8" t="n">
-        <v>6866856</v>
+        <v>6866835</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128376258</v>
+        <v>128375190</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471292</v>
+        <v>471145</v>
       </c>
       <c r="R9" t="n">
-        <v>6866805</v>
+        <v>6866802</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128375168</v>
+        <v>128376258</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471139</v>
+        <v>471292</v>
       </c>
       <c r="R10" t="n">
-        <v>6866821</v>
+        <v>6866805</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128375190</v>
+        <v>128375168</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471145</v>
+        <v>471139</v>
       </c>
       <c r="R11" t="n">
-        <v>6866802</v>
+        <v>6866821</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,7 +1657,7 @@
         <v>128376197</v>
       </c>
       <c r="B12" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128374859</v>
       </c>
       <c r="B13" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>128376676</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>128375275</v>
       </c>
       <c r="B15" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>128374662</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>128375734</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>128376712</v>
       </c>
       <c r="B18" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128375959</v>
+        <v>128375989</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>78096</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471266</v>
+        <v>471276</v>
       </c>
       <c r="R19" t="n">
-        <v>6866792</v>
+        <v>6866805</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128375989</v>
+        <v>128375959</v>
       </c>
       <c r="B20" t="n">
-        <v>78092</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471276</v>
+        <v>471266</v>
       </c>
       <c r="R20" t="n">
-        <v>6866805</v>
+        <v>6866792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>128375358</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128375214</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128375758</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>128376206</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128374452</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128375464</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128375560</v>
+        <v>128376736</v>
       </c>
       <c r="B27" t="n">
-        <v>57876</v>
+        <v>78096</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471219</v>
+        <v>471282</v>
       </c>
       <c r="R27" t="n">
-        <v>6866779</v>
+        <v>6866783</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3180,11 +3180,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3211,10 +3206,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128376736</v>
+        <v>128375560</v>
       </c>
       <c r="B28" t="n">
-        <v>78092</v>
+        <v>57880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3217,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,13 +3241,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471282</v>
+        <v>471219</v>
       </c>
       <c r="R28" t="n">
-        <v>6866783</v>
+        <v>6866779</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3282,6 +3277,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128376574</v>
+        <v>128374116</v>
       </c>
       <c r="B29" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,21 +3319,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,13 +3343,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471364</v>
+        <v>471107</v>
       </c>
       <c r="R29" t="n">
-        <v>6866709</v>
+        <v>6866853</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128374116</v>
+        <v>128376702</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>78527</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471107</v>
+        <v>471287</v>
       </c>
       <c r="R30" t="n">
-        <v>6866853</v>
+        <v>6866773</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>128376636</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128376702</v>
+        <v>128376574</v>
       </c>
       <c r="B32" t="n">
-        <v>78523</v>
+        <v>78882</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471287</v>
+        <v>471364</v>
       </c>
       <c r="R32" t="n">
-        <v>6866773</v>
+        <v>6866709</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128375794</v>
+        <v>128375249</v>
       </c>
       <c r="B33" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471241</v>
+        <v>471158</v>
       </c>
       <c r="R33" t="n">
-        <v>6866786</v>
+        <v>6866800</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,7 +3796,7 @@
         <v>128375289</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128375249</v>
+        <v>128375794</v>
       </c>
       <c r="B35" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471158</v>
+        <v>471241</v>
       </c>
       <c r="R35" t="n">
-        <v>6866800</v>
+        <v>6866786</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
         <v>128376382</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>128374814</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>128373989</v>
       </c>
       <c r="B38" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>128374436</v>
       </c>
       <c r="B39" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374500</v>
+        <v>128376649</v>
       </c>
       <c r="B40" t="n">
-        <v>79152</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4400,21 +4400,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471134</v>
+        <v>471300</v>
       </c>
       <c r="R40" t="n">
-        <v>6866834</v>
+        <v>6866735</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4486,10 +4486,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128376649</v>
+        <v>128375508</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471300</v>
+        <v>471209</v>
       </c>
       <c r="R41" t="n">
-        <v>6866735</v>
+        <v>6866776</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4583,10 +4583,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128375508</v>
+        <v>128374500</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>79156</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4594,21 +4594,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471209</v>
+        <v>471134</v>
       </c>
       <c r="R42" t="n">
-        <v>6866776</v>
+        <v>6866834</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4683,7 +4683,7 @@
         <v>128376462</v>
       </c>
       <c r="B43" t="n">
-        <v>92078</v>
+        <v>92082</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4791,10 +4791,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128375498</v>
+        <v>128375808</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471198</v>
+        <v>471247</v>
       </c>
       <c r="R44" t="n">
-        <v>6866776</v>
+        <v>6866787</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4888,10 +4888,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128375808</v>
+        <v>128375498</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4923,10 +4923,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471247</v>
+        <v>471198</v>
       </c>
       <c r="R45" t="n">
-        <v>6866787</v>
+        <v>6866776</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4988,7 +4988,7 @@
         <v>128375307</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>128375399</v>
       </c>
       <c r="B47" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>128376295</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5276,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128387779</v>
+        <v>128388207</v>
       </c>
       <c r="B49" t="n">
-        <v>98632</v>
+        <v>78881</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470744</v>
+        <v>470789</v>
       </c>
       <c r="R49" t="n">
-        <v>6866736</v>
+        <v>6866739</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128388103</v>
+        <v>128387779</v>
       </c>
       <c r="B50" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470763</v>
+        <v>470744</v>
       </c>
       <c r="R50" t="n">
-        <v>6866753</v>
+        <v>6866736</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,32 +5470,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128388207</v>
+        <v>128388103</v>
       </c>
       <c r="B51" t="n">
-        <v>78877</v>
+        <v>98636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470789</v>
+        <v>470763</v>
       </c>
       <c r="R51" t="n">
-        <v>6866739</v>
+        <v>6866753</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5570,7 +5570,7 @@
         <v>128387977</v>
       </c>
       <c r="B52" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>128389953</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>128389894</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5867,32 +5867,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128387790</v>
+        <v>128387828</v>
       </c>
       <c r="B55" t="n">
-        <v>98632</v>
+        <v>78882</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5902,13 +5902,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470732</v>
+        <v>470743</v>
       </c>
       <c r="R55" t="n">
-        <v>6866727</v>
+        <v>6866698</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5964,32 +5964,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128387828</v>
+        <v>128387790</v>
       </c>
       <c r="B56" t="n">
-        <v>78878</v>
+        <v>98636</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5999,13 +5999,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>470743</v>
+        <v>470732</v>
       </c>
       <c r="R56" t="n">
-        <v>6866698</v>
+        <v>6866727</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6061,10 +6061,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128388496</v>
+        <v>128388996</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>470869</v>
+        <v>471118</v>
       </c>
       <c r="R57" t="n">
-        <v>6866723</v>
+        <v>6866746</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6158,10 +6158,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128388996</v>
+        <v>128388496</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>471118</v>
+        <v>470869</v>
       </c>
       <c r="R58" t="n">
-        <v>6866746</v>
+        <v>6866723</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6258,7 +6258,7 @@
         <v>128389324</v>
       </c>
       <c r="B59" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>128387936</v>
       </c>
       <c r="B60" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128389855</v>
+        <v>128388778</v>
       </c>
       <c r="B61" t="n">
-        <v>57876</v>
+        <v>79203</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471241</v>
+        <v>470995</v>
       </c>
       <c r="R61" t="n">
-        <v>6866622</v>
+        <v>6866711</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6529,11 +6529,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6560,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128389329</v>
+        <v>128389262</v>
       </c>
       <c r="B62" t="n">
-        <v>78877</v>
+        <v>80230</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6571,21 +6566,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6595,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471172</v>
+        <v>471168</v>
       </c>
       <c r="R62" t="n">
-        <v>6866632</v>
+        <v>6866647</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6660,7 +6655,7 @@
         <v>128389511</v>
       </c>
       <c r="B63" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6757,7 +6752,7 @@
         <v>128387227</v>
       </c>
       <c r="B64" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6854,7 +6849,7 @@
         <v>128387286</v>
       </c>
       <c r="B65" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6948,10 +6943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128388778</v>
+        <v>128389855</v>
       </c>
       <c r="B66" t="n">
-        <v>79199</v>
+        <v>57880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6959,21 +6954,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>864</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6983,13 +6978,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470995</v>
+        <v>471241</v>
       </c>
       <c r="R66" t="n">
-        <v>6866711</v>
+        <v>6866622</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7019,6 +7014,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7045,10 +7045,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128389262</v>
+        <v>128389329</v>
       </c>
       <c r="B67" t="n">
-        <v>80226</v>
+        <v>78881</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7056,21 +7056,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7080,10 +7080,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471168</v>
+        <v>471172</v>
       </c>
       <c r="R67" t="n">
-        <v>6866647</v>
+        <v>6866632</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7145,7 +7145,7 @@
         <v>128389227</v>
       </c>
       <c r="B68" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>128388804</v>
       </c>
       <c r="B69" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7336,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128389187</v>
+        <v>128389069</v>
       </c>
       <c r="B70" t="n">
-        <v>78877</v>
+        <v>80229</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7347,21 +7347,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471196</v>
+        <v>471158</v>
       </c>
       <c r="R70" t="n">
-        <v>6866706</v>
+        <v>6866734</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128389069</v>
+        <v>128389187</v>
       </c>
       <c r="B71" t="n">
-        <v>80225</v>
+        <v>78881</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471158</v>
+        <v>471196</v>
       </c>
       <c r="R71" t="n">
-        <v>6866734</v>
+        <v>6866706</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128389641</v>
+        <v>128388766</v>
       </c>
       <c r="B72" t="n">
-        <v>80225</v>
+        <v>79203</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7541,21 +7541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471241</v>
+        <v>470981</v>
       </c>
       <c r="R72" t="n">
-        <v>6866656</v>
+        <v>6866714</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7630,7 +7630,7 @@
         <v>128388646</v>
       </c>
       <c r="B73" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7724,10 +7724,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128388766</v>
+        <v>128389641</v>
       </c>
       <c r="B74" t="n">
-        <v>79199</v>
+        <v>80229</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>470981</v>
+        <v>471241</v>
       </c>
       <c r="R74" t="n">
-        <v>6866714</v>
+        <v>6866656</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7824,7 +7824,7 @@
         <v>128388053</v>
       </c>
       <c r="B75" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>128387695</v>
       </c>
       <c r="B76" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>128387629</v>
       </c>
       <c r="B77" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8121,54 +8121,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128388416</v>
+        <v>128388815</v>
       </c>
       <c r="B78" t="n">
-        <v>98632</v>
+        <v>79124</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470816</v>
+        <v>470992</v>
       </c>
       <c r="R78" t="n">
-        <v>6866722</v>
+        <v>6866696</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8227,10 +8218,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128389403</v>
+        <v>128388714</v>
       </c>
       <c r="B79" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8238,21 +8229,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8262,10 +8253,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471187</v>
+        <v>470987</v>
       </c>
       <c r="R79" t="n">
-        <v>6866586</v>
+        <v>6866714</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8324,10 +8315,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128388815</v>
+        <v>128389886</v>
       </c>
       <c r="B80" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8359,10 +8350,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>470992</v>
+        <v>471211</v>
       </c>
       <c r="R80" t="n">
-        <v>6866696</v>
+        <v>6866717</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8421,10 +8412,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128388714</v>
+        <v>128389403</v>
       </c>
       <c r="B81" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8432,21 +8423,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8456,10 +8447,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>470987</v>
+        <v>471187</v>
       </c>
       <c r="R81" t="n">
-        <v>6866714</v>
+        <v>6866586</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8518,45 +8509,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128389886</v>
+        <v>128388416</v>
       </c>
       <c r="B82" t="n">
-        <v>79120</v>
+        <v>98636</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471211</v>
+        <v>470816</v>
       </c>
       <c r="R82" t="n">
-        <v>6866717</v>
+        <v>6866722</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8618,7 +8618,7 @@
         <v>128387736</v>
       </c>
       <c r="B83" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>128389124</v>
       </c>
       <c r="B84" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>128387659</v>
       </c>
       <c r="B85" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>128387292</v>
       </c>
       <c r="B86" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>128389901</v>
       </c>
       <c r="B87" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>128389213</v>
       </c>
       <c r="B88" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>128389351</v>
       </c>
       <c r="B89" t="n">
-        <v>78092</v>
+        <v>78096</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>128388228</v>
       </c>
       <c r="B90" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>128388690</v>
       </c>
       <c r="B91" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>128388173</v>
       </c>
       <c r="B92" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>128389587</v>
       </c>
       <c r="B93" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>128389918</v>
       </c>
       <c r="B94" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>128389286</v>
       </c>
       <c r="B95" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9885,10 +9885,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128502263</v>
+        <v>128502381</v>
       </c>
       <c r="B96" t="n">
-        <v>79124</v>
+        <v>79156</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9896,21 +9896,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9920,10 +9920,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471328</v>
+        <v>471311</v>
       </c>
       <c r="R96" t="n">
-        <v>6866612</v>
+        <v>6866616</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9982,10 +9982,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128502381</v>
+        <v>128502263</v>
       </c>
       <c r="B97" t="n">
-        <v>79156</v>
+        <v>79124</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9993,21 +9993,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471311</v>
+        <v>471328</v>
       </c>
       <c r="R97" t="n">
-        <v>6866616</v>
+        <v>6866612</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10273,32 +10273,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128502704</v>
+        <v>128501140</v>
       </c>
       <c r="B100" t="n">
-        <v>91473</v>
+        <v>79124</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471366</v>
+        <v>471253</v>
       </c>
       <c r="R100" t="n">
-        <v>6866720</v>
+        <v>6866704</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10370,32 +10370,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128501140</v>
+        <v>128502704</v>
       </c>
       <c r="B101" t="n">
-        <v>79124</v>
+        <v>91473</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471253</v>
+        <v>471366</v>
       </c>
       <c r="R101" t="n">
-        <v>6866704</v>
+        <v>6866720</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11049,10 +11049,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128501209</v>
+        <v>128502100</v>
       </c>
       <c r="B108" t="n">
-        <v>78881</v>
+        <v>79156</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11060,21 +11060,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471244</v>
+        <v>471347</v>
       </c>
       <c r="R108" t="n">
-        <v>6866687</v>
+        <v>6866584</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11146,10 +11146,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128502100</v>
+        <v>128502802</v>
       </c>
       <c r="B109" t="n">
-        <v>79156</v>
+        <v>79124</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11157,21 +11157,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11181,10 +11181,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471347</v>
+        <v>471256</v>
       </c>
       <c r="R109" t="n">
-        <v>6866584</v>
+        <v>6866728</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11243,10 +11243,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128502802</v>
+        <v>128501209</v>
       </c>
       <c r="B110" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11254,21 +11254,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471256</v>
+        <v>471244</v>
       </c>
       <c r="R110" t="n">
-        <v>6866728</v>
+        <v>6866687</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11534,10 +11534,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128501973</v>
+        <v>128501347</v>
       </c>
       <c r="B113" t="n">
-        <v>79156</v>
+        <v>80229</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11545,21 +11545,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471363</v>
+        <v>471275</v>
       </c>
       <c r="R113" t="n">
-        <v>6866544</v>
+        <v>6866627</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11631,10 +11631,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128501097</v>
+        <v>128501973</v>
       </c>
       <c r="B114" t="n">
-        <v>79124</v>
+        <v>79156</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11642,21 +11642,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471224</v>
+        <v>471363</v>
       </c>
       <c r="R114" t="n">
-        <v>6866707</v>
+        <v>6866544</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11728,7 +11728,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128502607</v>
+        <v>128502509</v>
       </c>
       <c r="B115" t="n">
         <v>78881</v>
@@ -11763,10 +11763,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471349</v>
+        <v>471315</v>
       </c>
       <c r="R115" t="n">
-        <v>6866695</v>
+        <v>6866670</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128502509</v>
+        <v>128501097</v>
       </c>
       <c r="B116" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11836,21 +11836,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471315</v>
+        <v>471224</v>
       </c>
       <c r="R116" t="n">
-        <v>6866670</v>
+        <v>6866707</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11922,10 +11922,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128501347</v>
+        <v>128502607</v>
       </c>
       <c r="B117" t="n">
-        <v>80229</v>
+        <v>78881</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11933,21 +11933,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11957,10 +11957,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471275</v>
+        <v>471349</v>
       </c>
       <c r="R117" t="n">
-        <v>6866627</v>
+        <v>6866695</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128373928</v>
+        <v>128376373</v>
       </c>
       <c r="B2" t="n">
-        <v>79156</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471086</v>
+        <v>471330</v>
       </c>
       <c r="R2" t="n">
-        <v>6866862</v>
+        <v>6866787</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128375151</v>
+        <v>128376618</v>
       </c>
       <c r="B3" t="n">
-        <v>79156</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471135</v>
+        <v>471331</v>
       </c>
       <c r="R3" t="n">
-        <v>6866819</v>
+        <v>6866715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128375924</v>
+        <v>128374470</v>
       </c>
       <c r="B4" t="n">
-        <v>78882</v>
+        <v>78881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471255</v>
+        <v>471139</v>
       </c>
       <c r="R4" t="n">
-        <v>6866786</v>
+        <v>6866835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128376373</v>
+        <v>128373928</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471330</v>
+        <v>471086</v>
       </c>
       <c r="R6" t="n">
-        <v>6866787</v>
+        <v>6866862</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128376618</v>
+        <v>128375151</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471331</v>
+        <v>471135</v>
       </c>
       <c r="R7" t="n">
-        <v>6866715</v>
+        <v>6866819</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128374470</v>
+        <v>128375924</v>
       </c>
       <c r="B8" t="n">
-        <v>78881</v>
+        <v>78882</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471139</v>
+        <v>471255</v>
       </c>
       <c r="R8" t="n">
-        <v>6866835</v>
+        <v>6866786</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128375275</v>
+        <v>128376712</v>
       </c>
       <c r="B15" t="n">
-        <v>79156</v>
+        <v>79714</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471162</v>
+        <v>471282</v>
       </c>
       <c r="R15" t="n">
-        <v>6866793</v>
+        <v>6866780</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128374662</v>
+        <v>128375275</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79156</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471145</v>
+        <v>471162</v>
       </c>
       <c r="R16" t="n">
-        <v>6866824</v>
+        <v>6866793</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,7 +2139,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128375734</v>
+        <v>128374662</v>
       </c>
       <c r="B17" t="n">
         <v>79124</v>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471234</v>
+        <v>471145</v>
       </c>
       <c r="R17" t="n">
-        <v>6866765</v>
+        <v>6866824</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128376712</v>
+        <v>128375734</v>
       </c>
       <c r="B18" t="n">
-        <v>79714</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,13 +2271,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471282</v>
+        <v>471234</v>
       </c>
       <c r="R18" t="n">
-        <v>6866780</v>
+        <v>6866765</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128375989</v>
+        <v>128375959</v>
       </c>
       <c r="B19" t="n">
-        <v>78096</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471276</v>
+        <v>471266</v>
       </c>
       <c r="R19" t="n">
-        <v>6866805</v>
+        <v>6866792</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128375959</v>
+        <v>128375989</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>78096</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471266</v>
+        <v>471276</v>
       </c>
       <c r="R20" t="n">
-        <v>6866792</v>
+        <v>6866805</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -4389,10 +4389,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128376649</v>
+        <v>128374500</v>
       </c>
       <c r="B40" t="n">
-        <v>79124</v>
+        <v>79156</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4400,21 +4400,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471300</v>
+        <v>471134</v>
       </c>
       <c r="R40" t="n">
-        <v>6866735</v>
+        <v>6866834</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4486,7 +4486,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128375508</v>
+        <v>128376649</v>
       </c>
       <c r="B41" t="n">
         <v>79124</v>
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471209</v>
+        <v>471300</v>
       </c>
       <c r="R41" t="n">
-        <v>6866776</v>
+        <v>6866735</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4583,10 +4583,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128374500</v>
+        <v>128375508</v>
       </c>
       <c r="B42" t="n">
-        <v>79156</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4594,21 +4594,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471134</v>
+        <v>471209</v>
       </c>
       <c r="R42" t="n">
-        <v>6866834</v>
+        <v>6866776</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4680,54 +4680,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128376462</v>
+        <v>128375808</v>
       </c>
       <c r="B43" t="n">
-        <v>92082</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471351</v>
+        <v>471247</v>
       </c>
       <c r="R43" t="n">
-        <v>6866748</v>
+        <v>6866787</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4760,11 +4751,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4791,7 +4777,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128375808</v>
+        <v>128375498</v>
       </c>
       <c r="B44" t="n">
         <v>79124</v>
@@ -4826,10 +4812,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471247</v>
+        <v>471198</v>
       </c>
       <c r="R44" t="n">
-        <v>6866787</v>
+        <v>6866776</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4888,45 +4874,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128375498</v>
+        <v>128376462</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>92082</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471198</v>
+        <v>471351</v>
       </c>
       <c r="R45" t="n">
-        <v>6866776</v>
+        <v>6866748</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4959,6 +4954,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128388207</v>
+        <v>128387779</v>
       </c>
       <c r="B49" t="n">
-        <v>78881</v>
+        <v>98636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470789</v>
+        <v>470744</v>
       </c>
       <c r="R49" t="n">
-        <v>6866739</v>
+        <v>6866736</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5373,7 +5373,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128387779</v>
+        <v>128388103</v>
       </c>
       <c r="B50" t="n">
         <v>98636</v>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470744</v>
+        <v>470763</v>
       </c>
       <c r="R50" t="n">
-        <v>6866736</v>
+        <v>6866753</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,32 +5470,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128388103</v>
+        <v>128388207</v>
       </c>
       <c r="B51" t="n">
-        <v>98636</v>
+        <v>78881</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470763</v>
+        <v>470789</v>
       </c>
       <c r="R51" t="n">
-        <v>6866753</v>
+        <v>6866739</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7821,32 +7821,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128388053</v>
+        <v>128387695</v>
       </c>
       <c r="B75" t="n">
-        <v>78882</v>
+        <v>98636</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7856,13 +7856,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>470770</v>
+        <v>470733</v>
       </c>
       <c r="R75" t="n">
-        <v>6866780</v>
+        <v>6866772</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7918,32 +7918,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128387695</v>
+        <v>128388053</v>
       </c>
       <c r="B76" t="n">
-        <v>98636</v>
+        <v>78882</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7953,13 +7953,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>470733</v>
+        <v>470770</v>
       </c>
       <c r="R76" t="n">
-        <v>6866772</v>
+        <v>6866780</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9012,10 +9012,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128389901</v>
+        <v>128389213</v>
       </c>
       <c r="B87" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9023,21 +9023,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471209</v>
+        <v>471148</v>
       </c>
       <c r="R87" t="n">
-        <v>6866743</v>
+        <v>6866668</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128389213</v>
+        <v>128389351</v>
       </c>
       <c r="B88" t="n">
-        <v>80229</v>
+        <v>78096</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471148</v>
+        <v>471215</v>
       </c>
       <c r="R88" t="n">
-        <v>6866668</v>
+        <v>6866634</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9206,32 +9206,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128389351</v>
+        <v>128388228</v>
       </c>
       <c r="B89" t="n">
-        <v>78096</v>
+        <v>98636</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471215</v>
+        <v>470788</v>
       </c>
       <c r="R89" t="n">
-        <v>6866634</v>
+        <v>6866725</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9303,32 +9303,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128388228</v>
+        <v>128389901</v>
       </c>
       <c r="B90" t="n">
-        <v>98636</v>
+        <v>79124</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>470788</v>
+        <v>471209</v>
       </c>
       <c r="R90" t="n">
-        <v>6866725</v>
+        <v>6866743</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128389587</v>
+        <v>128389918</v>
       </c>
       <c r="B93" t="n">
-        <v>80230</v>
+        <v>79124</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471274</v>
+        <v>471210</v>
       </c>
       <c r="R93" t="n">
-        <v>6866626</v>
+        <v>6866755</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9691,10 +9691,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128389918</v>
+        <v>128389587</v>
       </c>
       <c r="B94" t="n">
-        <v>79124</v>
+        <v>80230</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9702,21 +9702,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9726,13 +9726,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471210</v>
+        <v>471274</v>
       </c>
       <c r="R94" t="n">
-        <v>6866755</v>
+        <v>6866626</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9885,10 +9885,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128502381</v>
+        <v>128502263</v>
       </c>
       <c r="B96" t="n">
-        <v>79156</v>
+        <v>79124</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9896,21 +9896,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9920,10 +9920,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471311</v>
+        <v>471328</v>
       </c>
       <c r="R96" t="n">
-        <v>6866616</v>
+        <v>6866612</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9982,10 +9982,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128502263</v>
+        <v>128502381</v>
       </c>
       <c r="B97" t="n">
-        <v>79124</v>
+        <v>79156</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9993,21 +9993,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471328</v>
+        <v>471311</v>
       </c>
       <c r="R97" t="n">
-        <v>6866612</v>
+        <v>6866616</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11534,10 +11534,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128501347</v>
+        <v>128501973</v>
       </c>
       <c r="B113" t="n">
-        <v>80229</v>
+        <v>79156</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11545,21 +11545,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471275</v>
+        <v>471363</v>
       </c>
       <c r="R113" t="n">
-        <v>6866627</v>
+        <v>6866544</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11631,10 +11631,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128501973</v>
+        <v>128502607</v>
       </c>
       <c r="B114" t="n">
-        <v>79156</v>
+        <v>78881</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11642,21 +11642,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471363</v>
+        <v>471349</v>
       </c>
       <c r="R114" t="n">
-        <v>6866544</v>
+        <v>6866695</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128501097</v>
+        <v>128501347</v>
       </c>
       <c r="B116" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11836,21 +11836,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471224</v>
+        <v>471275</v>
       </c>
       <c r="R116" t="n">
-        <v>6866707</v>
+        <v>6866627</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11922,10 +11922,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128502607</v>
+        <v>128501097</v>
       </c>
       <c r="B117" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11933,21 +11933,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11957,10 +11957,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471349</v>
+        <v>471224</v>
       </c>
       <c r="R117" t="n">
-        <v>6866695</v>
+        <v>6866707</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12504,10 +12504,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128502309</v>
+        <v>128501253</v>
       </c>
       <c r="B123" t="n">
-        <v>78882</v>
+        <v>79156</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12515,21 +12515,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12539,10 +12539,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471311</v>
+        <v>471267</v>
       </c>
       <c r="R123" t="n">
-        <v>6866598</v>
+        <v>6866658</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12601,10 +12601,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128501253</v>
+        <v>128502309</v>
       </c>
       <c r="B124" t="n">
-        <v>79156</v>
+        <v>78882</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12612,21 +12612,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>471267</v>
+        <v>471311</v>
       </c>
       <c r="R124" t="n">
-        <v>6866658</v>
+        <v>6866598</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY125"/>
+  <dimension ref="A1:AY132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128376373</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128376618</v>
+        <v>128374470</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471331</v>
+        <v>471139</v>
       </c>
       <c r="R3" t="n">
-        <v>6866715</v>
+        <v>6866835</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128374470</v>
+        <v>128373928</v>
       </c>
       <c r="B4" t="n">
-        <v>78881</v>
+        <v>79061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471139</v>
+        <v>471086</v>
       </c>
       <c r="R4" t="n">
-        <v>6866835</v>
+        <v>6866862</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,54 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128374420</v>
+        <v>128375151</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>79061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471132</v>
+        <v>471135</v>
       </c>
       <c r="R5" t="n">
-        <v>6866856</v>
+        <v>6866819</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373928</v>
+        <v>128376618</v>
       </c>
       <c r="B6" t="n">
-        <v>79156</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471086</v>
+        <v>471331</v>
       </c>
       <c r="R6" t="n">
-        <v>6866862</v>
+        <v>6866715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,45 +1160,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128375151</v>
+        <v>128374420</v>
       </c>
       <c r="B7" t="n">
-        <v>79156</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471135</v>
+        <v>471132</v>
       </c>
       <c r="R7" t="n">
-        <v>6866819</v>
+        <v>6866856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,7 +1269,7 @@
         <v>128375924</v>
       </c>
       <c r="B8" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128375190</v>
+        <v>128376258</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471145</v>
+        <v>471292</v>
       </c>
       <c r="R9" t="n">
-        <v>6866802</v>
+        <v>6866805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128376258</v>
+        <v>128375168</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471292</v>
+        <v>471139</v>
       </c>
       <c r="R10" t="n">
-        <v>6866805</v>
+        <v>6866821</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128375168</v>
+        <v>128375190</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471139</v>
+        <v>471145</v>
       </c>
       <c r="R11" t="n">
-        <v>6866821</v>
+        <v>6866802</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,7 +1657,7 @@
         <v>128376197</v>
       </c>
       <c r="B12" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128374859</v>
       </c>
       <c r="B13" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>128376676</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128376712</v>
+        <v>128375275</v>
       </c>
       <c r="B15" t="n">
-        <v>79714</v>
+        <v>79061</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471282</v>
+        <v>471162</v>
       </c>
       <c r="R15" t="n">
-        <v>6866780</v>
+        <v>6866793</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128375275</v>
+        <v>128375734</v>
       </c>
       <c r="B16" t="n">
-        <v>79156</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471162</v>
+        <v>471234</v>
       </c>
       <c r="R16" t="n">
-        <v>6866793</v>
+        <v>6866765</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>128374662</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128375734</v>
+        <v>128376712</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,13 +2271,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471234</v>
+        <v>471282</v>
       </c>
       <c r="R18" t="n">
-        <v>6866765</v>
+        <v>6866780</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128375959</v>
+        <v>128375989</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>78037</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471266</v>
+        <v>471276</v>
       </c>
       <c r="R19" t="n">
-        <v>6866792</v>
+        <v>6866805</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128375989</v>
+        <v>128375959</v>
       </c>
       <c r="B20" t="n">
-        <v>78096</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471276</v>
+        <v>471266</v>
       </c>
       <c r="R20" t="n">
-        <v>6866805</v>
+        <v>6866792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2527,10 +2527,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128375358</v>
+        <v>128375214</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471166</v>
+        <v>471144</v>
       </c>
       <c r="R21" t="n">
-        <v>6866785</v>
+        <v>6866814</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2624,10 +2624,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128375214</v>
+        <v>128375358</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471144</v>
+        <v>471166</v>
       </c>
       <c r="R22" t="n">
-        <v>6866814</v>
+        <v>6866785</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2724,7 +2724,7 @@
         <v>128375758</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>128376206</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128374452</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128375464</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128376736</v>
+        <v>128375560</v>
       </c>
       <c r="B27" t="n">
-        <v>78096</v>
+        <v>57883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471282</v>
+        <v>471219</v>
       </c>
       <c r="R27" t="n">
-        <v>6866783</v>
+        <v>6866779</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3180,6 +3180,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3206,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128375560</v>
+        <v>128376736</v>
       </c>
       <c r="B28" t="n">
-        <v>57880</v>
+        <v>78037</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3217,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3241,13 +3246,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471219</v>
+        <v>471282</v>
       </c>
       <c r="R28" t="n">
-        <v>6866779</v>
+        <v>6866783</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3277,11 +3282,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128374116</v>
+        <v>128376636</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471107</v>
+        <v>471320</v>
       </c>
       <c r="R29" t="n">
-        <v>6866853</v>
+        <v>6866734</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
         <v>128376702</v>
       </c>
       <c r="B30" t="n">
-        <v>78527</v>
+        <v>78432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128376636</v>
+        <v>128374116</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471320</v>
+        <v>471107</v>
       </c>
       <c r="R31" t="n">
-        <v>6866734</v>
+        <v>6866853</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
         <v>128376574</v>
       </c>
       <c r="B32" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128375249</v>
+        <v>128375289</v>
       </c>
       <c r="B33" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471158</v>
+        <v>471165</v>
       </c>
       <c r="R33" t="n">
-        <v>6866800</v>
+        <v>6866794</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128375289</v>
+        <v>128375249</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471165</v>
+        <v>471158</v>
       </c>
       <c r="R34" t="n">
-        <v>6866794</v>
+        <v>6866800</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,7 +3893,7 @@
         <v>128375794</v>
       </c>
       <c r="B35" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3987,10 +3987,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128376382</v>
+        <v>128374814</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471342</v>
+        <v>471137</v>
       </c>
       <c r="R36" t="n">
-        <v>6866780</v>
+        <v>6866828</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4058,6 +4058,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4084,10 +4089,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128374814</v>
+        <v>128376382</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4119,10 +4124,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471137</v>
+        <v>471342</v>
       </c>
       <c r="R37" t="n">
-        <v>6866828</v>
+        <v>6866780</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4155,11 +4160,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4189,7 +4189,7 @@
         <v>128373989</v>
       </c>
       <c r="B38" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>128374436</v>
       </c>
       <c r="B39" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>128374500</v>
       </c>
       <c r="B40" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>128376649</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>128375508</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4680,45 +4680,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128375808</v>
+        <v>128376462</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>92087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471247</v>
+        <v>471351</v>
       </c>
       <c r="R43" t="n">
-        <v>6866787</v>
+        <v>6866748</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4751,6 +4760,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4777,10 +4791,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128375498</v>
+        <v>128375808</v>
       </c>
       <c r="B44" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4812,10 +4826,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471198</v>
+        <v>471247</v>
       </c>
       <c r="R44" t="n">
-        <v>6866776</v>
+        <v>6866787</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4874,54 +4888,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128376462</v>
+        <v>128375498</v>
       </c>
       <c r="B45" t="n">
-        <v>92082</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471351</v>
+        <v>471198</v>
       </c>
       <c r="R45" t="n">
-        <v>6866748</v>
+        <v>6866776</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4954,11 +4959,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4988,7 +4988,7 @@
         <v>128375307</v>
       </c>
       <c r="B46" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128375399</v>
+        <v>128376295</v>
       </c>
       <c r="B47" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471183</v>
+        <v>471321</v>
       </c>
       <c r="R47" t="n">
-        <v>6866790</v>
+        <v>6866820</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5179,10 +5179,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128376295</v>
+        <v>128375399</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5214,10 +5214,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>471321</v>
+        <v>471183</v>
       </c>
       <c r="R48" t="n">
-        <v>6866820</v>
+        <v>6866790</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5276,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128387779</v>
+        <v>128388207</v>
       </c>
       <c r="B49" t="n">
-        <v>98636</v>
+        <v>78786</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470744</v>
+        <v>470789</v>
       </c>
       <c r="R49" t="n">
-        <v>6866736</v>
+        <v>6866739</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128388103</v>
+        <v>128387779</v>
       </c>
       <c r="B50" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470763</v>
+        <v>470744</v>
       </c>
       <c r="R50" t="n">
-        <v>6866753</v>
+        <v>6866736</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,32 +5470,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128388207</v>
+        <v>128388103</v>
       </c>
       <c r="B51" t="n">
-        <v>78881</v>
+        <v>98643</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470789</v>
+        <v>470763</v>
       </c>
       <c r="R51" t="n">
-        <v>6866739</v>
+        <v>6866753</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5570,7 +5570,7 @@
         <v>128387977</v>
       </c>
       <c r="B52" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128389953</v>
+        <v>128389894</v>
       </c>
       <c r="B53" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>471200</v>
+        <v>471207</v>
       </c>
       <c r="R53" t="n">
-        <v>6866759</v>
+        <v>6866729</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5770,10 +5770,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128389894</v>
+        <v>128389953</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5805,13 +5805,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>471207</v>
+        <v>471200</v>
       </c>
       <c r="R54" t="n">
-        <v>6866729</v>
+        <v>6866759</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>128387828</v>
       </c>
       <c r="B55" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>128387790</v>
       </c>
       <c r="B56" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>128388996</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>128388496</v>
       </c>
       <c r="B58" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>128389324</v>
       </c>
       <c r="B59" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>128387936</v>
       </c>
       <c r="B60" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>128388778</v>
       </c>
       <c r="B61" t="n">
-        <v>79203</v>
+        <v>79108</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>128389262</v>
       </c>
       <c r="B62" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>128389511</v>
       </c>
       <c r="B63" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128387227</v>
+        <v>128389329</v>
       </c>
       <c r="B64" t="n">
-        <v>80229</v>
+        <v>78786</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>470551</v>
+        <v>471172</v>
       </c>
       <c r="R64" t="n">
-        <v>6866892</v>
+        <v>6866632</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128387286</v>
+        <v>128387227</v>
       </c>
       <c r="B65" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>470551</v>
       </c>
       <c r="R65" t="n">
-        <v>6866872</v>
+        <v>6866892</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128389855</v>
+        <v>128387286</v>
       </c>
       <c r="B66" t="n">
-        <v>57880</v>
+        <v>80134</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,21 +6954,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>471241</v>
+        <v>470551</v>
       </c>
       <c r="R66" t="n">
-        <v>6866622</v>
+        <v>6866872</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7014,11 +7014,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7045,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128389329</v>
+        <v>128389855</v>
       </c>
       <c r="B67" t="n">
-        <v>78881</v>
+        <v>57883</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7056,21 +7051,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7080,13 +7075,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471172</v>
+        <v>471241</v>
       </c>
       <c r="R67" t="n">
-        <v>6866632</v>
+        <v>6866622</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7116,6 +7111,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7142,10 +7142,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128389227</v>
+        <v>128389069</v>
       </c>
       <c r="B68" t="n">
-        <v>79156</v>
+        <v>80134</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471156</v>
+        <v>471158</v>
       </c>
       <c r="R68" t="n">
-        <v>6866665</v>
+        <v>6866734</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128388804</v>
+        <v>128389187</v>
       </c>
       <c r="B69" t="n">
-        <v>79156</v>
+        <v>78786</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>470987</v>
+        <v>471196</v>
       </c>
       <c r="R69" t="n">
         <v>6866706</v>
@@ -7336,10 +7336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128389069</v>
+        <v>128389227</v>
       </c>
       <c r="B70" t="n">
-        <v>80229</v>
+        <v>79061</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7347,21 +7347,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471158</v>
+        <v>471156</v>
       </c>
       <c r="R70" t="n">
-        <v>6866734</v>
+        <v>6866665</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128389187</v>
+        <v>128388804</v>
       </c>
       <c r="B71" t="n">
-        <v>78881</v>
+        <v>79061</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7444,21 +7444,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471196</v>
+        <v>470987</v>
       </c>
       <c r="R71" t="n">
         <v>6866706</v>
@@ -7533,7 +7533,7 @@
         <v>128388766</v>
       </c>
       <c r="B72" t="n">
-        <v>79203</v>
+        <v>79108</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>128388646</v>
       </c>
       <c r="B73" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>128389641</v>
       </c>
       <c r="B74" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7821,32 +7821,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128387695</v>
+        <v>128388053</v>
       </c>
       <c r="B75" t="n">
-        <v>98636</v>
+        <v>78787</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7856,13 +7856,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>470733</v>
+        <v>470770</v>
       </c>
       <c r="R75" t="n">
-        <v>6866772</v>
+        <v>6866780</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7918,32 +7918,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128388053</v>
+        <v>128387695</v>
       </c>
       <c r="B76" t="n">
-        <v>78882</v>
+        <v>98643</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7953,13 +7953,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>470770</v>
+        <v>470733</v>
       </c>
       <c r="R76" t="n">
-        <v>6866780</v>
+        <v>6866772</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>128387629</v>
       </c>
       <c r="B77" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>128388815</v>
       </c>
       <c r="B78" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128388714</v>
+        <v>128389886</v>
       </c>
       <c r="B79" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>470987</v>
+        <v>471211</v>
       </c>
       <c r="R79" t="n">
-        <v>6866714</v>
+        <v>6866717</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8315,10 +8315,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128389886</v>
+        <v>128388714</v>
       </c>
       <c r="B80" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8350,10 +8350,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471211</v>
+        <v>470987</v>
       </c>
       <c r="R80" t="n">
-        <v>6866717</v>
+        <v>6866714</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8412,45 +8412,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128389403</v>
+        <v>128388416</v>
       </c>
       <c r="B81" t="n">
-        <v>78882</v>
+        <v>98643</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471187</v>
+        <v>470816</v>
       </c>
       <c r="R81" t="n">
-        <v>6866586</v>
+        <v>6866722</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8509,54 +8518,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128388416</v>
+        <v>128389403</v>
       </c>
       <c r="B82" t="n">
-        <v>98636</v>
+        <v>78787</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>470816</v>
+        <v>471187</v>
       </c>
       <c r="R82" t="n">
-        <v>6866722</v>
+        <v>6866586</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8618,7 +8618,7 @@
         <v>128387736</v>
       </c>
       <c r="B83" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>128389124</v>
       </c>
       <c r="B84" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>128387659</v>
       </c>
       <c r="B85" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>128387292</v>
       </c>
       <c r="B86" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>128389213</v>
       </c>
       <c r="B87" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128389351</v>
+        <v>128389901</v>
       </c>
       <c r="B88" t="n">
-        <v>78096</v>
+        <v>79029</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471215</v>
+        <v>471209</v>
       </c>
       <c r="R88" t="n">
-        <v>6866634</v>
+        <v>6866743</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9206,32 +9206,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128388228</v>
+        <v>128389351</v>
       </c>
       <c r="B89" t="n">
-        <v>98636</v>
+        <v>78037</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>470788</v>
+        <v>471215</v>
       </c>
       <c r="R89" t="n">
-        <v>6866725</v>
+        <v>6866634</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9303,32 +9303,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128389901</v>
+        <v>128388228</v>
       </c>
       <c r="B90" t="n">
-        <v>79124</v>
+        <v>98643</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471209</v>
+        <v>470788</v>
       </c>
       <c r="R90" t="n">
-        <v>6866743</v>
+        <v>6866725</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9403,7 +9403,7 @@
         <v>128388690</v>
       </c>
       <c r="B91" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128388173</v>
+        <v>128389918</v>
       </c>
       <c r="B92" t="n">
-        <v>78790</v>
+        <v>79029</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9532,13 +9532,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>470786</v>
+        <v>471210</v>
       </c>
       <c r="R92" t="n">
-        <v>6866737</v>
+        <v>6866755</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128389918</v>
+        <v>128388173</v>
       </c>
       <c r="B93" t="n">
-        <v>79124</v>
+        <v>78695</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471210</v>
+        <v>470786</v>
       </c>
       <c r="R93" t="n">
-        <v>6866755</v>
+        <v>6866737</v>
       </c>
       <c r="S93" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>128389587</v>
       </c>
       <c r="B94" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>128389286</v>
       </c>
       <c r="B95" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9885,10 +9885,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128502263</v>
+        <v>128502381</v>
       </c>
       <c r="B96" t="n">
-        <v>79124</v>
+        <v>79061</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9896,21 +9896,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9920,10 +9920,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471328</v>
+        <v>471311</v>
       </c>
       <c r="R96" t="n">
-        <v>6866612</v>
+        <v>6866616</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9982,10 +9982,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128502381</v>
+        <v>128502263</v>
       </c>
       <c r="B97" t="n">
-        <v>79156</v>
+        <v>79029</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9993,21 +9993,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471311</v>
+        <v>471328</v>
       </c>
       <c r="R97" t="n">
-        <v>6866616</v>
+        <v>6866612</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10082,7 +10082,7 @@
         <v>128501285</v>
       </c>
       <c r="B98" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>128501083</v>
       </c>
       <c r="B99" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10273,32 +10273,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128501140</v>
+        <v>128502704</v>
       </c>
       <c r="B100" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471253</v>
+        <v>471366</v>
       </c>
       <c r="R100" t="n">
-        <v>6866704</v>
+        <v>6866720</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10370,32 +10370,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128502704</v>
+        <v>128501140</v>
       </c>
       <c r="B101" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471366</v>
+        <v>471253</v>
       </c>
       <c r="R101" t="n">
-        <v>6866720</v>
+        <v>6866704</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10470,7 +10470,7 @@
         <v>128501794</v>
       </c>
       <c r="B102" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>128502548</v>
       </c>
       <c r="B103" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>128501127</v>
       </c>
       <c r="B104" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>128501181</v>
       </c>
       <c r="B105" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10855,10 +10855,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128501480</v>
+        <v>128501144</v>
       </c>
       <c r="B106" t="n">
-        <v>79156</v>
+        <v>78787</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10866,21 +10866,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10890,13 +10890,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471273</v>
+        <v>471257</v>
       </c>
       <c r="R106" t="n">
-        <v>6866589</v>
+        <v>6866697</v>
       </c>
       <c r="S106" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10952,10 +10952,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128501144</v>
+        <v>128501480</v>
       </c>
       <c r="B107" t="n">
-        <v>78882</v>
+        <v>79061</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10963,21 +10963,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471257</v>
+        <v>471273</v>
       </c>
       <c r="R107" t="n">
-        <v>6866697</v>
+        <v>6866589</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>128502100</v>
       </c>
       <c r="B108" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>128502802</v>
       </c>
       <c r="B109" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>128501209</v>
       </c>
       <c r="B110" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>128502866</v>
       </c>
       <c r="B111" t="n">
-        <v>98553</v>
+        <v>98560</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>128502259</v>
       </c>
       <c r="B112" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>128501973</v>
       </c>
       <c r="B113" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11631,10 +11631,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128502607</v>
+        <v>128501347</v>
       </c>
       <c r="B114" t="n">
-        <v>78881</v>
+        <v>80134</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11642,21 +11642,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471349</v>
+        <v>471275</v>
       </c>
       <c r="R114" t="n">
-        <v>6866695</v>
+        <v>6866627</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11731,7 +11731,7 @@
         <v>128502509</v>
       </c>
       <c r="B115" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128501347</v>
+        <v>128501097</v>
       </c>
       <c r="B116" t="n">
-        <v>80229</v>
+        <v>79029</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11836,21 +11836,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471275</v>
+        <v>471224</v>
       </c>
       <c r="R116" t="n">
-        <v>6866627</v>
+        <v>6866707</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11922,10 +11922,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128501097</v>
+        <v>128502607</v>
       </c>
       <c r="B117" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11933,21 +11933,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11957,10 +11957,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471224</v>
+        <v>471349</v>
       </c>
       <c r="R117" t="n">
-        <v>6866707</v>
+        <v>6866695</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12022,7 +12022,7 @@
         <v>128501927</v>
       </c>
       <c r="B118" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>128501224</v>
       </c>
       <c r="B119" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>128502212</v>
       </c>
       <c r="B120" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>128502291</v>
       </c>
       <c r="B121" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>128502189</v>
       </c>
       <c r="B122" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>128501253</v>
       </c>
       <c r="B123" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>128502309</v>
       </c>
       <c r="B124" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>128502178</v>
       </c>
       <c r="B125" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12792,6 +12792,740 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>129011154</v>
+      </c>
+      <c r="B126" t="n">
+        <v>92803</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>471298</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6866571</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>129011146</v>
+      </c>
+      <c r="B127" t="n">
+        <v>92815</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>471277</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6866584</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>129011121</v>
+      </c>
+      <c r="B128" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>471276</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6866578</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>129012527</v>
+      </c>
+      <c r="B129" t="n">
+        <v>78695</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>353</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>470886</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6866737</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129010927</v>
+      </c>
+      <c r="B130" t="n">
+        <v>98643</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>471189</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6866691</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129012279</v>
+      </c>
+      <c r="B131" t="n">
+        <v>98643</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>470794</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6866768</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>129011818</v>
+      </c>
+      <c r="B132" t="n">
+        <v>92803</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>471292</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6866776</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -9888,7 +9888,7 @@
         <v>128502381</v>
       </c>
       <c r="B96" t="n">
-        <v>79061</v>
+        <v>79066</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>128502263</v>
       </c>
       <c r="B97" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>128501285</v>
       </c>
       <c r="B98" t="n">
-        <v>79061</v>
+        <v>79066</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>128501083</v>
       </c>
       <c r="B99" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10273,32 +10273,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128501140</v>
+        <v>128502704</v>
       </c>
       <c r="B100" t="n">
-        <v>79029</v>
+        <v>91485</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471253</v>
+        <v>471366</v>
       </c>
       <c r="R100" t="n">
-        <v>6866704</v>
+        <v>6866720</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10370,32 +10370,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128502704</v>
+        <v>128501140</v>
       </c>
       <c r="B101" t="n">
-        <v>91480</v>
+        <v>79034</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471366</v>
+        <v>471253</v>
       </c>
       <c r="R101" t="n">
-        <v>6866720</v>
+        <v>6866704</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10470,7 +10470,7 @@
         <v>128501794</v>
       </c>
       <c r="B102" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>128502548</v>
       </c>
       <c r="B103" t="n">
-        <v>79061</v>
+        <v>79066</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>128501127</v>
       </c>
       <c r="B104" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>128501181</v>
       </c>
       <c r="B105" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>128501480</v>
       </c>
       <c r="B106" t="n">
-        <v>79061</v>
+        <v>79066</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>128501144</v>
       </c>
       <c r="B107" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>128502100</v>
       </c>
       <c r="B108" t="n">
-        <v>79061</v>
+        <v>79066</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>128502802</v>
       </c>
       <c r="B109" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>128501209</v>
       </c>
       <c r="B110" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>128502866</v>
       </c>
       <c r="B111" t="n">
-        <v>98563</v>
+        <v>98568</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>128502259</v>
       </c>
       <c r="B112" t="n">
-        <v>79061</v>
+        <v>79066</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11534,10 +11534,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128502509</v>
+        <v>128501973</v>
       </c>
       <c r="B113" t="n">
-        <v>78786</v>
+        <v>79066</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11545,21 +11545,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471315</v>
+        <v>471363</v>
       </c>
       <c r="R113" t="n">
-        <v>6866670</v>
+        <v>6866544</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11631,10 +11631,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128501097</v>
+        <v>128501347</v>
       </c>
       <c r="B114" t="n">
-        <v>79029</v>
+        <v>80139</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11642,21 +11642,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471224</v>
+        <v>471275</v>
       </c>
       <c r="R114" t="n">
-        <v>6866707</v>
+        <v>6866627</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11728,10 +11728,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128501973</v>
+        <v>128502509</v>
       </c>
       <c r="B115" t="n">
-        <v>79061</v>
+        <v>78791</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11739,21 +11739,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11763,10 +11763,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471363</v>
+        <v>471315</v>
       </c>
       <c r="R115" t="n">
-        <v>6866544</v>
+        <v>6866670</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128502607</v>
+        <v>128501097</v>
       </c>
       <c r="B116" t="n">
-        <v>78786</v>
+        <v>79034</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11836,21 +11836,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471349</v>
+        <v>471224</v>
       </c>
       <c r="R116" t="n">
-        <v>6866695</v>
+        <v>6866707</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11922,10 +11922,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128501347</v>
+        <v>128502607</v>
       </c>
       <c r="B117" t="n">
-        <v>80134</v>
+        <v>78791</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11933,21 +11933,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11957,10 +11957,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471275</v>
+        <v>471349</v>
       </c>
       <c r="R117" t="n">
-        <v>6866627</v>
+        <v>6866695</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12022,7 +12022,7 @@
         <v>128501927</v>
       </c>
       <c r="B118" t="n">
-        <v>79061</v>
+        <v>79066</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>128501224</v>
       </c>
       <c r="B119" t="n">
-        <v>79061</v>
+        <v>79066</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>128502212</v>
       </c>
       <c r="B120" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>128502291</v>
       </c>
       <c r="B121" t="n">
-        <v>79061</v>
+        <v>79066</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>128502189</v>
       </c>
       <c r="B122" t="n">
-        <v>79061</v>
+        <v>79066</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>128501253</v>
       </c>
       <c r="B123" t="n">
-        <v>79061</v>
+        <v>79066</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>128502309</v>
       </c>
       <c r="B124" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>128502178</v>
       </c>
       <c r="B125" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -12798,7 +12798,7 @@
         <v>129011154</v>
       </c>
       <c r="B126" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>129011146</v>
       </c>
       <c r="B127" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13003,10 +13003,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129011121</v>
+        <v>129012527</v>
       </c>
       <c r="B128" t="n">
-        <v>92849</v>
+        <v>78700</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13014,48 +13014,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>471276</v>
+        <v>470886</v>
       </c>
       <c r="R128" t="n">
-        <v>6866578</v>
+        <v>6866737</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13114,10 +13100,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129012527</v>
+        <v>129011121</v>
       </c>
       <c r="B129" t="n">
-        <v>78700</v>
+        <v>92854</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13125,34 +13111,48 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470886</v>
+        <v>471276</v>
       </c>
       <c r="R129" t="n">
-        <v>6866737</v>
+        <v>6866578</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13214,7 +13214,7 @@
         <v>129010927</v>
       </c>
       <c r="B130" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>129012279</v>
       </c>
       <c r="B131" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>129011818</v>
       </c>
       <c r="B132" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -12798,7 +12798,7 @@
         <v>129011154</v>
       </c>
       <c r="B126" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>129011146</v>
       </c>
       <c r="B127" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>129012527</v>
       </c>
       <c r="B128" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>129011121</v>
       </c>
       <c r="B129" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>129010927</v>
       </c>
       <c r="B130" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>129012279</v>
       </c>
       <c r="B131" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>129011818</v>
       </c>
       <c r="B132" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -13003,10 +13003,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129012527</v>
+        <v>129011121</v>
       </c>
       <c r="B128" t="n">
-        <v>78701</v>
+        <v>92857</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13014,34 +13014,48 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470886</v>
+        <v>471276</v>
       </c>
       <c r="R128" t="n">
-        <v>6866737</v>
+        <v>6866578</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13100,10 +13114,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129011121</v>
+        <v>129012527</v>
       </c>
       <c r="B129" t="n">
-        <v>92857</v>
+        <v>78701</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13111,48 +13125,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>471276</v>
+        <v>470886</v>
       </c>
       <c r="R129" t="n">
-        <v>6866578</v>
+        <v>6866737</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -13003,10 +13003,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129011121</v>
+        <v>129012527</v>
       </c>
       <c r="B128" t="n">
-        <v>92857</v>
+        <v>78701</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13014,48 +13014,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>471276</v>
+        <v>470886</v>
       </c>
       <c r="R128" t="n">
-        <v>6866578</v>
+        <v>6866737</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13114,10 +13100,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129012527</v>
+        <v>129011121</v>
       </c>
       <c r="B129" t="n">
-        <v>78701</v>
+        <v>92857</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13125,34 +13111,48 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470886</v>
+        <v>471276</v>
       </c>
       <c r="R129" t="n">
-        <v>6866737</v>
+        <v>6866578</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -12798,7 +12798,7 @@
         <v>129011154</v>
       </c>
       <c r="B126" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>129011146</v>
       </c>
       <c r="B127" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>129012527</v>
       </c>
       <c r="B128" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>129011121</v>
       </c>
       <c r="B129" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>129010927</v>
       </c>
       <c r="B130" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>129012279</v>
       </c>
       <c r="B131" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>129011818</v>
       </c>
       <c r="B132" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -12798,7 +12798,7 @@
         <v>129011154</v>
       </c>
       <c r="B126" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>129011146</v>
       </c>
       <c r="B127" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13003,10 +13003,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129012527</v>
+        <v>129011121</v>
       </c>
       <c r="B128" t="n">
-        <v>78705</v>
+        <v>92871</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13014,34 +13014,48 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470886</v>
+        <v>471276</v>
       </c>
       <c r="R128" t="n">
-        <v>6866737</v>
+        <v>6866578</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13100,10 +13114,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129011121</v>
+        <v>129012527</v>
       </c>
       <c r="B129" t="n">
-        <v>92864</v>
+        <v>78705</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13111,48 +13125,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>471276</v>
+        <v>470886</v>
       </c>
       <c r="R129" t="n">
-        <v>6866578</v>
+        <v>6866737</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13214,7 +13214,7 @@
         <v>129010927</v>
       </c>
       <c r="B130" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>129012279</v>
       </c>
       <c r="B131" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>129011818</v>
       </c>
       <c r="B132" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -12798,7 +12798,7 @@
         <v>129011154</v>
       </c>
       <c r="B126" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>129011146</v>
       </c>
       <c r="B127" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13003,10 +13003,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129011121</v>
+        <v>129012527</v>
       </c>
       <c r="B128" t="n">
-        <v>92871</v>
+        <v>78707</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13014,48 +13014,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>471276</v>
+        <v>470886</v>
       </c>
       <c r="R128" t="n">
-        <v>6866578</v>
+        <v>6866737</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13114,10 +13100,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129012527</v>
+        <v>129011121</v>
       </c>
       <c r="B129" t="n">
-        <v>78705</v>
+        <v>92873</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13125,34 +13111,48 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470886</v>
+        <v>471276</v>
       </c>
       <c r="R129" t="n">
-        <v>6866737</v>
+        <v>6866578</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13214,7 +13214,7 @@
         <v>129010927</v>
       </c>
       <c r="B130" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>129012279</v>
       </c>
       <c r="B131" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>129011818</v>
       </c>
       <c r="B132" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -12798,7 +12798,7 @@
         <v>129011154</v>
       </c>
       <c r="B126" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>129011146</v>
       </c>
       <c r="B127" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>129011121</v>
       </c>
       <c r="B129" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>129010927</v>
       </c>
       <c r="B130" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>129012279</v>
       </c>
       <c r="B131" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>129011818</v>
       </c>
       <c r="B132" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -12798,7 +12798,7 @@
         <v>129011154</v>
       </c>
       <c r="B126" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>129011146</v>
       </c>
       <c r="B127" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13003,10 +13003,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129012527</v>
+        <v>129011121</v>
       </c>
       <c r="B128" t="n">
-        <v>78707</v>
+        <v>92860</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13014,34 +13014,48 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470886</v>
+        <v>471276</v>
       </c>
       <c r="R128" t="n">
-        <v>6866737</v>
+        <v>6866578</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13100,10 +13114,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129011121</v>
+        <v>129012527</v>
       </c>
       <c r="B129" t="n">
-        <v>92859</v>
+        <v>78707</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13111,48 +13125,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>471276</v>
+        <v>470886</v>
       </c>
       <c r="R129" t="n">
-        <v>6866578</v>
+        <v>6866737</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13214,7 +13214,7 @@
         <v>129010927</v>
       </c>
       <c r="B130" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>129012279</v>
       </c>
       <c r="B131" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>129011818</v>
       </c>
       <c r="B132" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -13003,10 +13003,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129011121</v>
+        <v>129012527</v>
       </c>
       <c r="B128" t="n">
-        <v>92860</v>
+        <v>78707</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13014,48 +13014,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>471276</v>
+        <v>470886</v>
       </c>
       <c r="R128" t="n">
-        <v>6866578</v>
+        <v>6866737</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13114,10 +13100,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129012527</v>
+        <v>129011121</v>
       </c>
       <c r="B129" t="n">
-        <v>78707</v>
+        <v>92860</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13125,34 +13111,48 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470886</v>
+        <v>471276</v>
       </c>
       <c r="R129" t="n">
-        <v>6866737</v>
+        <v>6866578</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13214,7 +13214,7 @@
         <v>129010927</v>
       </c>
       <c r="B130" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>129012279</v>
       </c>
       <c r="B131" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -12798,7 +12798,7 @@
         <v>129011154</v>
       </c>
       <c r="B126" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>129011146</v>
       </c>
       <c r="B127" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13003,10 +13003,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129012527</v>
+        <v>129011121</v>
       </c>
       <c r="B128" t="n">
-        <v>78707</v>
+        <v>92863</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13014,34 +13014,48 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470886</v>
+        <v>471276</v>
       </c>
       <c r="R128" t="n">
-        <v>6866737</v>
+        <v>6866578</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13100,10 +13114,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129011121</v>
+        <v>129012527</v>
       </c>
       <c r="B129" t="n">
-        <v>92860</v>
+        <v>78709</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13111,48 +13125,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>471276</v>
+        <v>470886</v>
       </c>
       <c r="R129" t="n">
-        <v>6866578</v>
+        <v>6866737</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13214,7 +13214,7 @@
         <v>129010927</v>
       </c>
       <c r="B130" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>129012279</v>
       </c>
       <c r="B131" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>129011818</v>
       </c>
       <c r="B132" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -12798,7 +12798,7 @@
         <v>129011154</v>
       </c>
       <c r="B126" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>129011146</v>
       </c>
       <c r="B127" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>129011121</v>
       </c>
       <c r="B128" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>129012527</v>
       </c>
       <c r="B129" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>129010927</v>
       </c>
       <c r="B130" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>129012279</v>
       </c>
       <c r="B131" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>129011818</v>
       </c>
       <c r="B132" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -12798,7 +12798,7 @@
         <v>129011154</v>
       </c>
       <c r="B126" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>129011146</v>
       </c>
       <c r="B127" t="n">
-        <v>92839</v>
+        <v>92843</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>129011121</v>
       </c>
       <c r="B128" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>129010927</v>
       </c>
       <c r="B130" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>129012279</v>
       </c>
       <c r="B131" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>129011818</v>
       </c>
       <c r="B132" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -12798,7 +12798,7 @@
         <v>129011154</v>
       </c>
       <c r="B126" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>129011146</v>
       </c>
       <c r="B127" t="n">
-        <v>92843</v>
+        <v>92844</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>129011121</v>
       </c>
       <c r="B128" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>129010927</v>
       </c>
       <c r="B130" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>129012279</v>
       </c>
       <c r="B131" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>129011818</v>
       </c>
       <c r="B132" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -12798,7 +12798,7 @@
         <v>129011154</v>
       </c>
       <c r="B126" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>129011146</v>
       </c>
       <c r="B127" t="n">
-        <v>92844</v>
+        <v>92847</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13003,10 +13003,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129011121</v>
+        <v>129012527</v>
       </c>
       <c r="B128" t="n">
-        <v>92870</v>
+        <v>78710</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13014,48 +13014,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>471276</v>
+        <v>470886</v>
       </c>
       <c r="R128" t="n">
-        <v>6866578</v>
+        <v>6866737</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13114,10 +13100,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129012527</v>
+        <v>129011121</v>
       </c>
       <c r="B129" t="n">
-        <v>78710</v>
+        <v>92873</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13125,34 +13111,48 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470886</v>
+        <v>471276</v>
       </c>
       <c r="R129" t="n">
-        <v>6866737</v>
+        <v>6866578</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13214,7 +13214,7 @@
         <v>129010927</v>
       </c>
       <c r="B130" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>129012279</v>
       </c>
       <c r="B131" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>129011818</v>
       </c>
       <c r="B132" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -13003,10 +13003,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129012527</v>
+        <v>129011121</v>
       </c>
       <c r="B128" t="n">
-        <v>78710</v>
+        <v>92873</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13014,34 +13014,48 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470886</v>
+        <v>471276</v>
       </c>
       <c r="R128" t="n">
-        <v>6866737</v>
+        <v>6866578</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13100,10 +13114,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129011121</v>
+        <v>129012527</v>
       </c>
       <c r="B129" t="n">
-        <v>92873</v>
+        <v>78710</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13111,48 +13125,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>471276</v>
+        <v>470886</v>
       </c>
       <c r="R129" t="n">
-        <v>6866578</v>
+        <v>6866737</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY132"/>
+  <dimension ref="A1:AY144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128376373</v>
+        <v>128373928</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471330</v>
+        <v>471086</v>
       </c>
       <c r="R2" t="n">
-        <v>6866787</v>
+        <v>6866862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128374470</v>
+        <v>128374500</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471139</v>
+        <v>471134</v>
       </c>
       <c r="R3" t="n">
-        <v>6866835</v>
+        <v>6866834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128373928</v>
+        <v>128375151</v>
       </c>
       <c r="B4" t="n">
-        <v>79061</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471086</v>
+        <v>471135</v>
       </c>
       <c r="R4" t="n">
-        <v>6866862</v>
+        <v>6866819</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128375151</v>
+        <v>128375275</v>
       </c>
       <c r="B5" t="n">
-        <v>79061</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471135</v>
+        <v>471162</v>
       </c>
       <c r="R5" t="n">
-        <v>6866819</v>
+        <v>6866793</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128376618</v>
+        <v>128388646</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471331</v>
+        <v>470945</v>
       </c>
       <c r="R6" t="n">
-        <v>6866715</v>
+        <v>6866709</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,54 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128374420</v>
+        <v>128388804</v>
       </c>
       <c r="B7" t="n">
-        <v>98643</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471132</v>
+        <v>470987</v>
       </c>
       <c r="R7" t="n">
-        <v>6866856</v>
+        <v>6866706</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1234,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1266,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128375924</v>
+        <v>128389227</v>
       </c>
       <c r="B8" t="n">
-        <v>78787</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471255</v>
+        <v>471156</v>
       </c>
       <c r="R8" t="n">
-        <v>6866786</v>
+        <v>6866665</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1331,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1363,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128376258</v>
+        <v>128389459</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471292</v>
+        <v>471177</v>
       </c>
       <c r="R9" t="n">
-        <v>6866805</v>
+        <v>6866567</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1428,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1460,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128375168</v>
+        <v>128501224</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471139</v>
+        <v>471253</v>
       </c>
       <c r="R10" t="n">
-        <v>6866821</v>
+        <v>6866666</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1525,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1557,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128375190</v>
+        <v>128501253</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1568,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471145</v>
+        <v>471267</v>
       </c>
       <c r="R11" t="n">
-        <v>6866802</v>
+        <v>6866658</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1622,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1654,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128376197</v>
+        <v>128501285</v>
       </c>
       <c r="B12" t="n">
-        <v>78787</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471280</v>
+        <v>471269</v>
       </c>
       <c r="R12" t="n">
-        <v>6866807</v>
+        <v>6866648</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1719,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1751,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128374859</v>
+        <v>128501480</v>
       </c>
       <c r="B13" t="n">
-        <v>80135</v>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,13 +1777,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471125</v>
+        <v>471273</v>
       </c>
       <c r="R13" t="n">
-        <v>6866815</v>
+        <v>6866589</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1816,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1848,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128376676</v>
+        <v>128501927</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471287</v>
+        <v>471340</v>
       </c>
       <c r="R14" t="n">
-        <v>6866763</v>
+        <v>6866563</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1913,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1945,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128375275</v>
+        <v>128501973</v>
       </c>
       <c r="B15" t="n">
-        <v>79061</v>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1980,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471162</v>
+        <v>471363</v>
       </c>
       <c r="R15" t="n">
-        <v>6866793</v>
+        <v>6866544</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2010,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2042,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128375734</v>
+        <v>128502100</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471234</v>
+        <v>471347</v>
       </c>
       <c r="R16" t="n">
-        <v>6866765</v>
+        <v>6866584</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2107,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2139,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128374662</v>
+        <v>128502189</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471145</v>
+        <v>471327</v>
       </c>
       <c r="R17" t="n">
-        <v>6866824</v>
+        <v>6866591</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2204,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2236,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128376712</v>
+        <v>128502259</v>
       </c>
       <c r="B18" t="n">
-        <v>79619</v>
+        <v>79359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471282</v>
+        <v>471327</v>
       </c>
       <c r="R18" t="n">
-        <v>6866780</v>
+        <v>6866603</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2301,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2333,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128375989</v>
+        <v>128502291</v>
       </c>
       <c r="B19" t="n">
-        <v>78037</v>
+        <v>79359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471276</v>
+        <v>471320</v>
       </c>
       <c r="R19" t="n">
-        <v>6866805</v>
+        <v>6866609</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2398,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2430,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128375959</v>
+        <v>128502381</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471266</v>
+        <v>471311</v>
       </c>
       <c r="R20" t="n">
-        <v>6866792</v>
+        <v>6866616</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2495,12 +2486,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2527,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128375214</v>
+        <v>128502548</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2538,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2562,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471144</v>
+        <v>471325</v>
       </c>
       <c r="R21" t="n">
-        <v>6866814</v>
+        <v>6866680</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2592,12 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2624,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128375358</v>
+        <v>128388173</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>78993</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2635,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471166</v>
+        <v>470786</v>
       </c>
       <c r="R22" t="n">
-        <v>6866785</v>
+        <v>6866737</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2689,12 +2680,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2721,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128375758</v>
+        <v>128502518</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>78993</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2732,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471232</v>
+        <v>471323</v>
       </c>
       <c r="R23" t="n">
-        <v>6866781</v>
+        <v>6866655</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2786,12 +2777,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2818,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128376206</v>
+        <v>129012527</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>78993</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2829,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2853,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>471275</v>
+        <v>470886</v>
       </c>
       <c r="R24" t="n">
-        <v>6866797</v>
+        <v>6866737</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2883,12 +2874,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2915,45 +2906,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128374452</v>
+        <v>128376462</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>92509</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>471138</v>
+        <v>471351</v>
       </c>
       <c r="R25" t="n">
-        <v>6866841</v>
+        <v>6866748</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2986,6 +2986,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3012,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128375464</v>
+        <v>128388766</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79406</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3023,21 +3028,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3047,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471186</v>
+        <v>470981</v>
       </c>
       <c r="R26" t="n">
-        <v>6866787</v>
+        <v>6866714</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3077,12 +3082,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3109,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128375560</v>
+        <v>128388778</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>79406</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,13 +3149,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471219</v>
+        <v>470995</v>
       </c>
       <c r="R27" t="n">
-        <v>6866779</v>
+        <v>6866711</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3174,17 +3179,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Läte från talltitor.</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128376736</v>
+        <v>128374859</v>
       </c>
       <c r="B28" t="n">
-        <v>78037</v>
+        <v>80433</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471282</v>
+        <v>471125</v>
       </c>
       <c r="R28" t="n">
-        <v>6866783</v>
+        <v>6866815</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128376636</v>
+        <v>128388953</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>80433</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,21 +3319,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,13 +3343,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471320</v>
+        <v>471080</v>
       </c>
       <c r="R29" t="n">
-        <v>6866734</v>
+        <v>6866746</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3373,12 +3373,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128376702</v>
+        <v>128389262</v>
       </c>
       <c r="B30" t="n">
-        <v>78432</v>
+        <v>80433</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471287</v>
+        <v>471168</v>
       </c>
       <c r="R30" t="n">
-        <v>6866773</v>
+        <v>6866647</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128374116</v>
+        <v>128389587</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>80433</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471107</v>
+        <v>471274</v>
       </c>
       <c r="R31" t="n">
-        <v>6866853</v>
+        <v>6866626</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128376574</v>
+        <v>129010706</v>
       </c>
       <c r="B32" t="n">
-        <v>78787</v>
+        <v>80433</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,37 +3610,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sålnberget, Sålnberget, Hjd</t>
+          <t>Lillhamra, Lillhamra, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471364</v>
+        <v>471062</v>
       </c>
       <c r="R32" t="n">
-        <v>6866709</v>
+        <v>6866859</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3664,12 +3664,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128375289</v>
+        <v>129011154</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,34 +3707,48 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471165</v>
+        <v>471298</v>
       </c>
       <c r="R33" t="n">
-        <v>6866794</v>
+        <v>6866571</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3761,12 +3775,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3793,10 +3807,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128375249</v>
+        <v>129011818</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3804,34 +3818,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471158</v>
+        <v>471292</v>
       </c>
       <c r="R34" t="n">
-        <v>6866800</v>
+        <v>6866776</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3858,12 +3881,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3890,10 +3913,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128375794</v>
+        <v>129011146</v>
       </c>
       <c r="B35" t="n">
-        <v>78787</v>
+        <v>93209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3901,21 +3924,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3925,10 +3948,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471241</v>
+        <v>471277</v>
       </c>
       <c r="R35" t="n">
-        <v>6866786</v>
+        <v>6866584</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3955,12 +3978,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3987,32 +4010,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128374814</v>
+        <v>128502704</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>91872</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4022,10 +4045,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471137</v>
+        <v>471366</v>
       </c>
       <c r="R36" t="n">
-        <v>6866828</v>
+        <v>6866720</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4052,17 +4075,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4089,10 +4107,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128376382</v>
+        <v>129011121</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>93235</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4100,34 +4118,48 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471342</v>
+        <v>471276</v>
       </c>
       <c r="R37" t="n">
-        <v>6866780</v>
+        <v>6866578</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4154,12 +4186,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4186,32 +4218,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373989</v>
+        <v>128373888</v>
       </c>
       <c r="B38" t="n">
-        <v>80134</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4221,10 +4253,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>471102</v>
+        <v>471081</v>
       </c>
       <c r="R38" t="n">
-        <v>6866857</v>
+        <v>6866883</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4283,10 +4315,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128374436</v>
+        <v>128374116</v>
       </c>
       <c r="B39" t="n">
-        <v>98643</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4294,43 +4326,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>471133</v>
+        <v>471107</v>
       </c>
       <c r="R39" t="n">
-        <v>6866841</v>
+        <v>6866853</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4389,32 +4412,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374500</v>
+        <v>128374452</v>
       </c>
       <c r="B40" t="n">
-        <v>79061</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4424,10 +4447,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471134</v>
+        <v>471138</v>
       </c>
       <c r="R40" t="n">
-        <v>6866834</v>
+        <v>6866841</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4486,14 +4509,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128376649</v>
+        <v>128374662</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4521,10 +4544,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471300</v>
+        <v>471145</v>
       </c>
       <c r="R41" t="n">
-        <v>6866735</v>
+        <v>6866824</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4583,14 +4606,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128375508</v>
+        <v>128374814</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4618,10 +4641,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471209</v>
+        <v>471137</v>
       </c>
       <c r="R42" t="n">
-        <v>6866776</v>
+        <v>6866828</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4654,6 +4677,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4680,10 +4708,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128376462</v>
+        <v>128375168</v>
       </c>
       <c r="B43" t="n">
-        <v>92087</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4691,43 +4719,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471351</v>
+        <v>471139</v>
       </c>
       <c r="R43" t="n">
-        <v>6866748</v>
+        <v>6866821</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4760,11 +4779,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4791,14 +4805,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128375808</v>
+        <v>128375190</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4826,10 +4840,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471247</v>
+        <v>471145</v>
       </c>
       <c r="R44" t="n">
-        <v>6866787</v>
+        <v>6866802</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4888,14 +4902,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128375498</v>
+        <v>128375214</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -4923,10 +4937,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471198</v>
+        <v>471144</v>
       </c>
       <c r="R45" t="n">
-        <v>6866776</v>
+        <v>6866814</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4985,14 +4999,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128375307</v>
+        <v>128375249</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5020,10 +5034,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471169</v>
+        <v>471158</v>
       </c>
       <c r="R46" t="n">
-        <v>6866788</v>
+        <v>6866800</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5082,14 +5096,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128376295</v>
+        <v>128375289</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5117,10 +5131,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471321</v>
+        <v>471165</v>
       </c>
       <c r="R47" t="n">
-        <v>6866820</v>
+        <v>6866794</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5179,14 +5193,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128375399</v>
+        <v>128375307</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5214,10 +5228,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>471183</v>
+        <v>471169</v>
       </c>
       <c r="R48" t="n">
-        <v>6866790</v>
+        <v>6866788</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5276,32 +5290,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128388207</v>
+        <v>128375358</v>
       </c>
       <c r="B49" t="n">
-        <v>78786</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5325,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470789</v>
+        <v>471166</v>
       </c>
       <c r="R49" t="n">
-        <v>6866739</v>
+        <v>6866785</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5341,12 +5355,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5373,10 +5387,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128387779</v>
+        <v>128375399</v>
       </c>
       <c r="B50" t="n">
-        <v>98643</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5384,21 +5398,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5408,10 +5422,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470744</v>
+        <v>471183</v>
       </c>
       <c r="R50" t="n">
-        <v>6866736</v>
+        <v>6866790</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5438,12 +5452,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5470,10 +5484,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128388103</v>
+        <v>128375464</v>
       </c>
       <c r="B51" t="n">
-        <v>98643</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5481,21 +5495,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5519,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470763</v>
+        <v>471186</v>
       </c>
       <c r="R51" t="n">
-        <v>6866753</v>
+        <v>6866787</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5535,12 +5549,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5567,10 +5581,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128387977</v>
+        <v>128375498</v>
       </c>
       <c r="B52" t="n">
-        <v>98643</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5578,43 +5592,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>470754</v>
+        <v>471198</v>
       </c>
       <c r="R52" t="n">
-        <v>6866755</v>
+        <v>6866776</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5641,12 +5646,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5673,14 +5678,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128389894</v>
+        <v>128375508</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -5708,10 +5713,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>471207</v>
+        <v>471209</v>
       </c>
       <c r="R53" t="n">
-        <v>6866729</v>
+        <v>6866776</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5738,12 +5743,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5770,14 +5775,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128389953</v>
+        <v>128375734</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -5805,10 +5810,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>471200</v>
+        <v>471234</v>
       </c>
       <c r="R54" t="n">
-        <v>6866759</v>
+        <v>6866765</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -5835,12 +5840,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5867,32 +5872,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128387828</v>
+        <v>128375758</v>
       </c>
       <c r="B55" t="n">
-        <v>78787</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5902,13 +5907,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470743</v>
+        <v>471232</v>
       </c>
       <c r="R55" t="n">
-        <v>6866698</v>
+        <v>6866781</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5932,12 +5937,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5964,10 +5969,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128387790</v>
+        <v>128375808</v>
       </c>
       <c r="B56" t="n">
-        <v>98643</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5975,21 +5980,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5999,10 +6004,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>470732</v>
+        <v>471247</v>
       </c>
       <c r="R56" t="n">
-        <v>6866727</v>
+        <v>6866787</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6029,12 +6034,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6061,14 +6066,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128388996</v>
+        <v>128375959</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6096,10 +6101,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>471118</v>
+        <v>471266</v>
       </c>
       <c r="R57" t="n">
-        <v>6866746</v>
+        <v>6866792</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6126,12 +6131,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6158,14 +6163,14 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128388496</v>
+        <v>128376206</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -6193,10 +6198,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>470869</v>
+        <v>471275</v>
       </c>
       <c r="R58" t="n">
-        <v>6866723</v>
+        <v>6866797</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6223,12 +6228,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6255,32 +6260,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128389324</v>
+        <v>128376258</v>
       </c>
       <c r="B59" t="n">
-        <v>79619</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6290,10 +6295,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>471177</v>
+        <v>471292</v>
       </c>
       <c r="R59" t="n">
-        <v>6866639</v>
+        <v>6866805</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6320,12 +6325,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6352,10 +6357,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128387936</v>
+        <v>128376295</v>
       </c>
       <c r="B60" t="n">
-        <v>98643</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6363,43 +6368,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>470750</v>
+        <v>471321</v>
       </c>
       <c r="R60" t="n">
-        <v>6866754</v>
+        <v>6866820</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6426,12 +6422,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6458,32 +6454,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128388778</v>
+        <v>128376373</v>
       </c>
       <c r="B61" t="n">
-        <v>79108</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,10 +6489,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>470995</v>
+        <v>471330</v>
       </c>
       <c r="R61" t="n">
-        <v>6866711</v>
+        <v>6866787</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6523,12 +6519,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6555,32 +6551,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128389262</v>
+        <v>128376382</v>
       </c>
       <c r="B62" t="n">
-        <v>80135</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6586,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471168</v>
+        <v>471342</v>
       </c>
       <c r="R62" t="n">
-        <v>6866647</v>
+        <v>6866780</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6620,12 +6616,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6652,32 +6648,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128389511</v>
+        <v>128376618</v>
       </c>
       <c r="B63" t="n">
-        <v>80134</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6683,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471237</v>
+        <v>471331</v>
       </c>
       <c r="R63" t="n">
-        <v>6866588</v>
+        <v>6866715</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6717,12 +6713,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6749,32 +6745,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128389329</v>
+        <v>128376636</v>
       </c>
       <c r="B64" t="n">
-        <v>78786</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6780,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471172</v>
+        <v>471320</v>
       </c>
       <c r="R64" t="n">
-        <v>6866632</v>
+        <v>6866734</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6814,12 +6810,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6846,32 +6842,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128387227</v>
+        <v>128376649</v>
       </c>
       <c r="B65" t="n">
-        <v>80134</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6877,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>470551</v>
+        <v>471300</v>
       </c>
       <c r="R65" t="n">
-        <v>6866892</v>
+        <v>6866735</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6911,12 +6907,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6943,32 +6939,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128387286</v>
+        <v>128376676</v>
       </c>
       <c r="B66" t="n">
-        <v>80134</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6974,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470551</v>
+        <v>471287</v>
       </c>
       <c r="R66" t="n">
-        <v>6866872</v>
+        <v>6866763</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7008,12 +7004,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7040,32 +7036,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128389855</v>
+        <v>128388496</v>
       </c>
       <c r="B67" t="n">
-        <v>57883</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,13 +7071,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471241</v>
+        <v>470869</v>
       </c>
       <c r="R67" t="n">
-        <v>6866622</v>
+        <v>6866723</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7111,11 +7107,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7142,32 +7133,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128389069</v>
+        <v>128388690</v>
       </c>
       <c r="B68" t="n">
-        <v>80134</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7168,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471158</v>
+        <v>470982</v>
       </c>
       <c r="R68" t="n">
-        <v>6866734</v>
+        <v>6866703</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7239,32 +7230,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128389187</v>
+        <v>128388714</v>
       </c>
       <c r="B69" t="n">
-        <v>78786</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,10 +7265,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471196</v>
+        <v>470987</v>
       </c>
       <c r="R69" t="n">
-        <v>6866706</v>
+        <v>6866714</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7336,32 +7327,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128389227</v>
+        <v>128388815</v>
       </c>
       <c r="B70" t="n">
-        <v>79061</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7371,10 +7362,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471156</v>
+        <v>470992</v>
       </c>
       <c r="R70" t="n">
-        <v>6866665</v>
+        <v>6866696</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7433,32 +7424,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128388804</v>
+        <v>128388996</v>
       </c>
       <c r="B71" t="n">
-        <v>79061</v>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7468,10 +7459,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>470987</v>
+        <v>471118</v>
       </c>
       <c r="R71" t="n">
-        <v>6866706</v>
+        <v>6866746</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7530,32 +7521,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128388766</v>
+        <v>128389124</v>
       </c>
       <c r="B72" t="n">
-        <v>79108</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7565,13 +7556,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470981</v>
+        <v>471167</v>
       </c>
       <c r="R72" t="n">
-        <v>6866714</v>
+        <v>6866694</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7627,32 +7618,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128388646</v>
+        <v>128389886</v>
       </c>
       <c r="B73" t="n">
-        <v>79061</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7662,10 +7653,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470945</v>
+        <v>471211</v>
       </c>
       <c r="R73" t="n">
-        <v>6866709</v>
+        <v>6866717</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7724,32 +7715,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128389641</v>
+        <v>128389894</v>
       </c>
       <c r="B74" t="n">
-        <v>80134</v>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7759,10 +7750,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471241</v>
+        <v>471207</v>
       </c>
       <c r="R74" t="n">
-        <v>6866656</v>
+        <v>6866729</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7821,32 +7812,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128388053</v>
+        <v>128389901</v>
       </c>
       <c r="B75" t="n">
-        <v>78787</v>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7856,13 +7847,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>470770</v>
+        <v>471209</v>
       </c>
       <c r="R75" t="n">
-        <v>6866780</v>
+        <v>6866743</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7918,10 +7909,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128387695</v>
+        <v>128389918</v>
       </c>
       <c r="B76" t="n">
-        <v>98643</v>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7929,21 +7920,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7953,13 +7944,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>470733</v>
+        <v>471210</v>
       </c>
       <c r="R76" t="n">
-        <v>6866772</v>
+        <v>6866755</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8015,10 +8006,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128387629</v>
+        <v>128389953</v>
       </c>
       <c r="B77" t="n">
-        <v>98643</v>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8026,46 +8017,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>470725</v>
+        <v>471200</v>
       </c>
       <c r="R77" t="n">
-        <v>6866764</v>
+        <v>6866759</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8121,14 +8103,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128388815</v>
+        <v>128501097</v>
       </c>
       <c r="B78" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -8156,10 +8138,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470992</v>
+        <v>471224</v>
       </c>
       <c r="R78" t="n">
-        <v>6866696</v>
+        <v>6866707</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8186,12 +8168,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8218,14 +8200,14 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128389886</v>
+        <v>128501127</v>
       </c>
       <c r="B79" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -8253,10 +8235,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471211</v>
+        <v>471245</v>
       </c>
       <c r="R79" t="n">
-        <v>6866717</v>
+        <v>6866708</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8283,12 +8265,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8315,14 +8297,14 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128388714</v>
+        <v>128501140</v>
       </c>
       <c r="B80" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -8350,10 +8332,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>470987</v>
+        <v>471253</v>
       </c>
       <c r="R80" t="n">
-        <v>6866714</v>
+        <v>6866704</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8380,12 +8362,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8412,32 +8394,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128389403</v>
+        <v>128501181</v>
       </c>
       <c r="B81" t="n">
-        <v>78787</v>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8447,10 +8429,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471187</v>
+        <v>471251</v>
       </c>
       <c r="R81" t="n">
-        <v>6866586</v>
+        <v>6866689</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8477,12 +8459,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8509,10 +8491,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128388416</v>
+        <v>128501794</v>
       </c>
       <c r="B82" t="n">
-        <v>98643</v>
+        <v>79327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8520,46 +8502,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>470816</v>
+        <v>471329</v>
       </c>
       <c r="R82" t="n">
-        <v>6866722</v>
+        <v>6866557</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8583,12 +8556,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8615,32 +8588,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128387736</v>
+        <v>128502178</v>
       </c>
       <c r="B83" t="n">
-        <v>80134</v>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8650,10 +8623,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>470738</v>
+        <v>471326</v>
       </c>
       <c r="R83" t="n">
-        <v>6866733</v>
+        <v>6866583</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8680,12 +8653,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8712,14 +8685,14 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128389124</v>
+        <v>128502212</v>
       </c>
       <c r="B84" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -8747,13 +8720,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471167</v>
+        <v>471325</v>
       </c>
       <c r="R84" t="n">
-        <v>6866694</v>
+        <v>6866592</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8777,12 +8750,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8809,10 +8782,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128387659</v>
+        <v>128502263</v>
       </c>
       <c r="B85" t="n">
-        <v>98643</v>
+        <v>79327</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8820,43 +8793,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>470734</v>
+        <v>471328</v>
       </c>
       <c r="R85" t="n">
-        <v>6866771</v>
+        <v>6866612</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8883,12 +8847,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8915,32 +8879,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128387292</v>
+        <v>128502802</v>
       </c>
       <c r="B86" t="n">
-        <v>80134</v>
+        <v>79327</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8950,10 +8914,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>470551</v>
+        <v>471256</v>
       </c>
       <c r="R86" t="n">
-        <v>6866868</v>
+        <v>6866728</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8980,12 +8944,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9012,10 +8976,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128389213</v>
+        <v>128376702</v>
       </c>
       <c r="B87" t="n">
-        <v>80134</v>
+        <v>78730</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9023,21 +8987,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9047,13 +9011,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471148</v>
+        <v>471287</v>
       </c>
       <c r="R87" t="n">
-        <v>6866668</v>
+        <v>6866773</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9077,12 +9041,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9109,10 +9073,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128389901</v>
+        <v>128374470</v>
       </c>
       <c r="B88" t="n">
-        <v>79029</v>
+        <v>79084</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9120,21 +9084,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9144,10 +9108,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471209</v>
+        <v>471139</v>
       </c>
       <c r="R88" t="n">
-        <v>6866743</v>
+        <v>6866835</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9174,12 +9138,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9206,10 +9170,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128389351</v>
+        <v>128388207</v>
       </c>
       <c r="B89" t="n">
-        <v>78037</v>
+        <v>79084</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9217,21 +9181,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9241,10 +9205,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471215</v>
+        <v>470789</v>
       </c>
       <c r="R89" t="n">
-        <v>6866634</v>
+        <v>6866739</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9303,32 +9267,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128388228</v>
+        <v>128389187</v>
       </c>
       <c r="B90" t="n">
-        <v>98643</v>
+        <v>79084</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9338,10 +9302,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>470788</v>
+        <v>471196</v>
       </c>
       <c r="R90" t="n">
-        <v>6866725</v>
+        <v>6866706</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9400,10 +9364,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128388690</v>
+        <v>128389329</v>
       </c>
       <c r="B91" t="n">
-        <v>79029</v>
+        <v>79084</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9411,21 +9375,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9435,10 +9399,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>470982</v>
+        <v>471172</v>
       </c>
       <c r="R91" t="n">
-        <v>6866703</v>
+        <v>6866632</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9497,10 +9461,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128388173</v>
+        <v>128501083</v>
       </c>
       <c r="B92" t="n">
-        <v>78695</v>
+        <v>79084</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9508,21 +9472,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9532,10 +9496,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>470786</v>
+        <v>471219</v>
       </c>
       <c r="R92" t="n">
-        <v>6866737</v>
+        <v>6866725</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9562,12 +9526,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9594,10 +9558,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128389587</v>
+        <v>128501209</v>
       </c>
       <c r="B93" t="n">
-        <v>80135</v>
+        <v>79084</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9605,21 +9569,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9629,10 +9593,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471274</v>
+        <v>471244</v>
       </c>
       <c r="R93" t="n">
-        <v>6866626</v>
+        <v>6866687</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9659,12 +9623,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9691,10 +9655,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128389918</v>
+        <v>128502509</v>
       </c>
       <c r="B94" t="n">
-        <v>79029</v>
+        <v>79084</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9702,21 +9666,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9726,13 +9690,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471210</v>
+        <v>471315</v>
       </c>
       <c r="R94" t="n">
-        <v>6866755</v>
+        <v>6866670</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9756,12 +9720,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9788,10 +9752,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128389286</v>
+        <v>128502607</v>
       </c>
       <c r="B95" t="n">
-        <v>80134</v>
+        <v>79084</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9799,21 +9763,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9823,10 +9787,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471168</v>
+        <v>471349</v>
       </c>
       <c r="R95" t="n">
-        <v>6866647</v>
+        <v>6866695</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9853,12 +9817,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9885,10 +9849,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128502381</v>
+        <v>128373940</v>
       </c>
       <c r="B96" t="n">
-        <v>79066</v>
+        <v>80432</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9896,21 +9860,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9920,10 +9884,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471311</v>
+        <v>471083</v>
       </c>
       <c r="R96" t="n">
-        <v>6866616</v>
+        <v>6866852</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9950,12 +9914,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -9982,10 +9946,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128502263</v>
+        <v>128373989</v>
       </c>
       <c r="B97" t="n">
-        <v>79034</v>
+        <v>80432</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9993,21 +9957,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10017,10 +9981,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471328</v>
+        <v>471102</v>
       </c>
       <c r="R97" t="n">
-        <v>6866612</v>
+        <v>6866857</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10047,12 +10011,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10079,10 +10043,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128501285</v>
+        <v>128387227</v>
       </c>
       <c r="B98" t="n">
-        <v>79066</v>
+        <v>80432</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10090,21 +10054,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10114,10 +10078,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471269</v>
+        <v>470551</v>
       </c>
       <c r="R98" t="n">
-        <v>6866648</v>
+        <v>6866892</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10144,12 +10108,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10176,10 +10140,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128501083</v>
+        <v>128387286</v>
       </c>
       <c r="B99" t="n">
-        <v>78791</v>
+        <v>80432</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10187,21 +10151,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10211,10 +10175,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471219</v>
+        <v>470551</v>
       </c>
       <c r="R99" t="n">
-        <v>6866725</v>
+        <v>6866872</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10241,12 +10205,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10273,32 +10237,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128502704</v>
+        <v>128387292</v>
       </c>
       <c r="B100" t="n">
-        <v>91485</v>
+        <v>80432</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10308,10 +10272,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471366</v>
+        <v>470551</v>
       </c>
       <c r="R100" t="n">
-        <v>6866720</v>
+        <v>6866868</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10338,12 +10302,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10370,10 +10334,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128501140</v>
+        <v>128387487</v>
       </c>
       <c r="B101" t="n">
-        <v>79034</v>
+        <v>80432</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10381,21 +10345,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10405,13 +10369,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471253</v>
+        <v>470706</v>
       </c>
       <c r="R101" t="n">
-        <v>6866704</v>
+        <v>6866759</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10435,12 +10399,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10467,10 +10431,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128501794</v>
+        <v>128387736</v>
       </c>
       <c r="B102" t="n">
-        <v>79034</v>
+        <v>80432</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10478,21 +10442,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10502,13 +10466,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471329</v>
+        <v>470738</v>
       </c>
       <c r="R102" t="n">
-        <v>6866557</v>
+        <v>6866733</v>
       </c>
       <c r="S102" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10532,12 +10496,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10564,10 +10528,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128502548</v>
+        <v>128389069</v>
       </c>
       <c r="B103" t="n">
-        <v>79066</v>
+        <v>80432</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10575,21 +10539,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10599,10 +10563,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471325</v>
+        <v>471158</v>
       </c>
       <c r="R103" t="n">
-        <v>6866680</v>
+        <v>6866734</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10629,12 +10593,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10661,10 +10625,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128501127</v>
+        <v>128389213</v>
       </c>
       <c r="B104" t="n">
-        <v>79034</v>
+        <v>80432</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10672,21 +10636,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10696,10 +10660,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471245</v>
+        <v>471148</v>
       </c>
       <c r="R104" t="n">
-        <v>6866708</v>
+        <v>6866668</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10726,12 +10690,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10758,10 +10722,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128501181</v>
+        <v>128389286</v>
       </c>
       <c r="B105" t="n">
-        <v>79034</v>
+        <v>80432</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10769,21 +10733,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10793,10 +10757,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471251</v>
+        <v>471168</v>
       </c>
       <c r="R105" t="n">
-        <v>6866689</v>
+        <v>6866647</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10823,12 +10787,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10855,10 +10819,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128501480</v>
+        <v>128389420</v>
       </c>
       <c r="B106" t="n">
-        <v>79066</v>
+        <v>80432</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10866,21 +10830,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10890,13 +10854,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471273</v>
+        <v>471185</v>
       </c>
       <c r="R106" t="n">
-        <v>6866589</v>
+        <v>6866576</v>
       </c>
       <c r="S106" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10920,12 +10884,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10952,10 +10916,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128501144</v>
+        <v>128389511</v>
       </c>
       <c r="B107" t="n">
-        <v>78792</v>
+        <v>80432</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10963,21 +10927,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10987,10 +10951,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471257</v>
+        <v>471237</v>
       </c>
       <c r="R107" t="n">
-        <v>6866697</v>
+        <v>6866588</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11017,12 +10981,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11049,10 +11013,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128502100</v>
+        <v>128389641</v>
       </c>
       <c r="B108" t="n">
-        <v>79066</v>
+        <v>80432</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11060,21 +11024,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11084,10 +11048,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471347</v>
+        <v>471241</v>
       </c>
       <c r="R108" t="n">
-        <v>6866584</v>
+        <v>6866656</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11114,12 +11078,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11146,10 +11110,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128502802</v>
+        <v>128501347</v>
       </c>
       <c r="B109" t="n">
-        <v>79034</v>
+        <v>80432</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11157,21 +11121,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11181,10 +11145,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471256</v>
+        <v>471275</v>
       </c>
       <c r="R109" t="n">
-        <v>6866728</v>
+        <v>6866627</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11243,10 +11207,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128501209</v>
+        <v>128501744</v>
       </c>
       <c r="B110" t="n">
-        <v>78791</v>
+        <v>80432</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11254,21 +11218,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11278,10 +11242,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471244</v>
+        <v>471288</v>
       </c>
       <c r="R110" t="n">
-        <v>6866687</v>
+        <v>6866547</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11340,32 +11304,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128502866</v>
+        <v>129010715</v>
       </c>
       <c r="B111" t="n">
-        <v>98568</v>
+        <v>80432</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11375,10 +11339,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471139</v>
+        <v>471061</v>
       </c>
       <c r="R111" t="n">
-        <v>6866727</v>
+        <v>6866856</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11405,12 +11369,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11437,10 +11401,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128502259</v>
+        <v>128375989</v>
       </c>
       <c r="B112" t="n">
-        <v>79066</v>
+        <v>78334</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11448,21 +11412,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>185</v>
+        <v>6487</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11472,10 +11436,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>471327</v>
+        <v>471276</v>
       </c>
       <c r="R112" t="n">
-        <v>6866603</v>
+        <v>6866805</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11502,12 +11466,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11534,10 +11498,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128501973</v>
+        <v>128376736</v>
       </c>
       <c r="B113" t="n">
-        <v>79066</v>
+        <v>78334</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11545,21 +11509,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>185</v>
+        <v>6487</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11569,10 +11533,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471363</v>
+        <v>471282</v>
       </c>
       <c r="R113" t="n">
-        <v>6866544</v>
+        <v>6866783</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11599,12 +11563,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11631,10 +11595,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128501347</v>
+        <v>128389351</v>
       </c>
       <c r="B114" t="n">
-        <v>80139</v>
+        <v>78334</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11642,21 +11606,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11666,10 +11630,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471275</v>
+        <v>471215</v>
       </c>
       <c r="R114" t="n">
-        <v>6866627</v>
+        <v>6866634</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11696,12 +11660,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11728,10 +11692,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128502509</v>
+        <v>128375560</v>
       </c>
       <c r="B115" t="n">
-        <v>78791</v>
+        <v>58114</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11739,21 +11703,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11763,13 +11727,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471315</v>
+        <v>471219</v>
       </c>
       <c r="R115" t="n">
-        <v>6866670</v>
+        <v>6866779</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11793,12 +11757,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11825,10 +11794,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128501097</v>
+        <v>128389855</v>
       </c>
       <c r="B116" t="n">
-        <v>79034</v>
+        <v>58114</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11836,21 +11805,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11860,13 +11829,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471224</v>
+        <v>471241</v>
       </c>
       <c r="R116" t="n">
-        <v>6866707</v>
+        <v>6866622</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11890,12 +11859,17 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -11922,32 +11896,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128502607</v>
+        <v>128502866</v>
       </c>
       <c r="B117" t="n">
-        <v>78791</v>
+        <v>99035</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11957,10 +11931,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471349</v>
+        <v>471139</v>
       </c>
       <c r="R117" t="n">
-        <v>6866695</v>
+        <v>6866727</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12019,45 +11993,54 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128501927</v>
+        <v>128374420</v>
       </c>
       <c r="B118" t="n">
-        <v>79066</v>
+        <v>99118</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>471340</v>
+        <v>471132</v>
       </c>
       <c r="R118" t="n">
-        <v>6866563</v>
+        <v>6866856</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12084,12 +12067,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12116,45 +12099,54 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128501224</v>
+        <v>128374436</v>
       </c>
       <c r="B119" t="n">
-        <v>79066</v>
+        <v>99118</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>471253</v>
+        <v>471133</v>
       </c>
       <c r="R119" t="n">
-        <v>6866666</v>
+        <v>6866841</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12181,12 +12173,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12213,32 +12205,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128502212</v>
+        <v>128387497</v>
       </c>
       <c r="B120" t="n">
-        <v>79034</v>
+        <v>99118</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12248,10 +12240,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>471325</v>
+        <v>470693</v>
       </c>
       <c r="R120" t="n">
-        <v>6866592</v>
+        <v>6866764</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12278,12 +12270,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12310,45 +12302,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128502291</v>
+        <v>128387629</v>
       </c>
       <c r="B121" t="n">
-        <v>79066</v>
+        <v>99118</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471320</v>
+        <v>470725</v>
       </c>
       <c r="R121" t="n">
-        <v>6866609</v>
+        <v>6866764</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12375,12 +12376,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12407,45 +12408,54 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128502189</v>
+        <v>128387659</v>
       </c>
       <c r="B122" t="n">
-        <v>79066</v>
+        <v>99118</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>471327</v>
+        <v>470734</v>
       </c>
       <c r="R122" t="n">
-        <v>6866591</v>
+        <v>6866771</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12472,12 +12482,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12504,32 +12514,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128501253</v>
+        <v>128387695</v>
       </c>
       <c r="B123" t="n">
-        <v>79066</v>
+        <v>99118</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12539,10 +12549,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471267</v>
+        <v>470733</v>
       </c>
       <c r="R123" t="n">
-        <v>6866658</v>
+        <v>6866772</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12569,12 +12579,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12601,32 +12611,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128502309</v>
+        <v>128387779</v>
       </c>
       <c r="B124" t="n">
-        <v>78792</v>
+        <v>99118</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12636,10 +12646,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>471311</v>
+        <v>470744</v>
       </c>
       <c r="R124" t="n">
-        <v>6866598</v>
+        <v>6866736</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12666,12 +12676,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12698,32 +12708,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128502178</v>
+        <v>128387790</v>
       </c>
       <c r="B125" t="n">
-        <v>79034</v>
+        <v>99118</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12733,10 +12743,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>471326</v>
+        <v>470732</v>
       </c>
       <c r="R125" t="n">
-        <v>6866583</v>
+        <v>6866727</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12763,12 +12773,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12795,47 +12805,42 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129011154</v>
+        <v>128387936</v>
       </c>
       <c r="B126" t="n">
-        <v>92835</v>
+        <v>99118</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -12844,10 +12849,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>471298</v>
+        <v>470750</v>
       </c>
       <c r="R126" t="n">
-        <v>6866571</v>
+        <v>6866754</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12874,12 +12879,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -12906,45 +12911,54 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129011146</v>
+        <v>128387977</v>
       </c>
       <c r="B127" t="n">
-        <v>92847</v>
+        <v>99118</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>471277</v>
+        <v>470754</v>
       </c>
       <c r="R127" t="n">
-        <v>6866584</v>
+        <v>6866755</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12971,12 +12985,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13003,59 +13017,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129011121</v>
+        <v>128388103</v>
       </c>
       <c r="B128" t="n">
-        <v>92873</v>
+        <v>99118</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>471276</v>
+        <v>470763</v>
       </c>
       <c r="R128" t="n">
-        <v>6866578</v>
+        <v>6866753</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13082,12 +13082,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13114,32 +13114,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129012527</v>
+        <v>128388228</v>
       </c>
       <c r="B129" t="n">
-        <v>78710</v>
+        <v>99118</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13149,10 +13149,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470886</v>
+        <v>470788</v>
       </c>
       <c r="R129" t="n">
-        <v>6866737</v>
+        <v>6866725</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13179,12 +13179,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13211,10 +13211,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129010927</v>
+        <v>128388416</v>
       </c>
       <c r="B130" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13255,10 +13255,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>471189</v>
+        <v>470816</v>
       </c>
       <c r="R130" t="n">
-        <v>6866691</v>
+        <v>6866722</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13285,12 +13285,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13317,10 +13317,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129012279</v>
+        <v>129010927</v>
       </c>
       <c r="B131" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13361,10 +13361,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470794</v>
+        <v>471189</v>
       </c>
       <c r="R131" t="n">
-        <v>6866768</v>
+        <v>6866691</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13423,42 +13423,42 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129011818</v>
+        <v>129012279</v>
       </c>
       <c r="B132" t="n">
-        <v>92835</v>
+        <v>99118</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -13467,10 +13467,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>471292</v>
+        <v>470794</v>
       </c>
       <c r="R132" t="n">
-        <v>6866776</v>
+        <v>6866768</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13526,6 +13526,1170 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128375794</v>
+      </c>
+      <c r="B133" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>471241</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6866786</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>128375924</v>
+      </c>
+      <c r="B134" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>471255</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6866786</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>128376197</v>
+      </c>
+      <c r="B135" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>471280</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6866807</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>128376574</v>
+      </c>
+      <c r="B136" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>471364</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6866709</v>
+      </c>
+      <c r="S136" t="n">
+        <v>20</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>128387828</v>
+      </c>
+      <c r="B137" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>470743</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6866698</v>
+      </c>
+      <c r="S137" t="n">
+        <v>20</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>128388053</v>
+      </c>
+      <c r="B138" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>470770</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6866780</v>
+      </c>
+      <c r="S138" t="n">
+        <v>20</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>128389403</v>
+      </c>
+      <c r="B139" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>471187</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6866586</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>128501144</v>
+      </c>
+      <c r="B140" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>471257</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6866697</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>128502309</v>
+      </c>
+      <c r="B141" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>471311</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6866598</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>128376712</v>
+      </c>
+      <c r="B142" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>471282</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6866780</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>128389324</v>
+      </c>
+      <c r="B143" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>471177</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6866639</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>128502577</v>
+      </c>
+      <c r="B144" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>471347</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6866673</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY144"/>
+  <dimension ref="A1:AZ144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373928</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374500</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375151</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375275</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388646</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388804</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389227</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389459</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501224</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501253</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501285</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501480</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501927</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501973</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502100</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502189</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502259</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502291</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502381</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502548</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388173</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502518</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012527</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3014,6 +3134,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376462</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3111,6 +3236,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388766</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3208,6 +3338,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388778</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3305,6 +3440,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374859</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3402,6 +3542,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388953</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3499,6 +3644,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389262</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3596,6 +3746,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389587</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3693,6 +3848,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129010706</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3804,6 +3964,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011154</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3910,6 +4075,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011818</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4007,6 +4177,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011146</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4104,6 +4279,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502704</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4215,6 +4395,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011121</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4312,6 +4497,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373888</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4409,6 +4599,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374116</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4506,6 +4701,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374452</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4603,6 +4803,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374662</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4705,6 +4910,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374814</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4802,6 +5012,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375168</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4899,6 +5114,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375190</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4996,6 +5216,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375214</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5093,6 +5318,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375249</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5190,6 +5420,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375289</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5287,6 +5522,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375307</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5384,6 +5624,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375358</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5481,6 +5726,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375399</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5578,6 +5828,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375464</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5675,6 +5930,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375498</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5772,6 +6032,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375508</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5869,6 +6134,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375734</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5966,6 +6236,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375758</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6063,6 +6338,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375808</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6160,6 +6440,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375959</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6257,6 +6542,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376206</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6354,6 +6644,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376258</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6451,6 +6746,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376295</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6548,6 +6848,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376373</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6645,6 +6950,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376382</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6742,6 +7052,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376618</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6839,6 +7154,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376636</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6936,6 +7256,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376649</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7033,6 +7358,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376676</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7130,6 +7460,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388496</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7227,6 +7562,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388690</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7324,6 +7664,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388714</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7421,6 +7766,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388815</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7518,6 +7868,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388996</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7615,6 +7970,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389124</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7712,6 +8072,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389886</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7809,6 +8174,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389894</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7906,6 +8276,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389901</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8003,6 +8378,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389918</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8100,6 +8480,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389953</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8197,6 +8582,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501097</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8294,6 +8684,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501127</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8391,6 +8786,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501140</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8488,6 +8888,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501181</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8585,6 +8990,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501794</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8682,6 +9092,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502178</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8779,6 +9194,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502212</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8876,6 +9296,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502263</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8973,6 +9398,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502802</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9070,6 +9500,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376702</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9167,6 +9602,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374470</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9264,6 +9704,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388207</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9361,6 +9806,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389187</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9458,6 +9908,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389329</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9555,6 +10010,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501083</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9652,6 +10112,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501209</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9749,6 +10214,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502509</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9846,6 +10316,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502607</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9943,6 +10418,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373940</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10040,6 +10520,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373989</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10137,6 +10622,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387227</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10234,6 +10724,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387286</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10331,6 +10826,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387292</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10428,6 +10928,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387487</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10525,6 +11030,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387736</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10622,6 +11132,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389069</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10719,6 +11234,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389213</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10816,6 +11336,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389286</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10913,6 +11438,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389420</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11010,6 +11540,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389511</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11107,6 +11642,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389641</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11204,6 +11744,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501347</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11301,6 +11846,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501744</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11398,6 +11948,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129010715</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11495,6 +12050,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375989</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11592,6 +12152,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376736</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11689,6 +12254,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389351</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11791,6 +12361,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375560</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11893,6 +12468,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389855</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11990,6 +12570,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502866</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12096,6 +12681,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374420</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12202,6 +12792,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374436</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12299,6 +12894,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387497</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12405,6 +13005,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387629</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12511,6 +13116,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387659</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12608,6 +13218,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387695</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12705,6 +13320,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387779</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12802,6 +13422,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387790</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12908,6 +13533,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387936</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13014,6 +13644,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387977</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13111,6 +13746,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388103</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13208,6 +13848,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388228</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13314,6 +13959,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388416</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13420,6 +14070,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129010927</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13526,6 +14181,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012279</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13623,6 +14283,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375794</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13720,6 +14385,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128375924</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13817,6 +14487,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376197</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13914,6 +14589,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376574</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14011,6 +14691,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387828</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14108,6 +14793,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388053</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14205,6 +14895,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389403</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14302,6 +14997,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501144</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14399,6 +15099,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502309</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14496,6 +15201,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376712</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14593,6 +15303,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389324</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14690,8 +15405,158 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502577</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>